--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5122374.709654335</v>
+        <v>1458461.43909157</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5122374.709654335</v>
+        <v>1458461.43909157</v>
       </c>
     </row>
     <row r="8">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5122374.709654335</v>
+        <v>1458461.43909157</v>
       </c>
     </row>
     <row r="22">
@@ -625,7 +625,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-4134575.509346012</v>
+        <v>-7798488.779908777</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +660,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:42+00:00</t>
+          <t>2026-06-05T13:11:45+00:00</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -857,13 +857,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3179759.43595589</v>
+        <v>2351090.985412234</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3179759.43595589</v>
+        <v>2351090.985412234</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3179759.43595589</v>
+        <v>-2351090.985412234</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -876,12 +876,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -891,44 +891,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>555394863.220544</v>
+        <v>867900893.337617</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>677151123.07819</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>121756259.857646</v>
+        <v>266802337.679219</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>3176374.999999989</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>3176374.999999989</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>660752792.8467374</v>
+        <v>867900893.337617</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1541206.640549455</v>
+        <v>1496811.70629198</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1541206.640549455</v>
+        <v>1496811.70629198</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1635168.359450534</v>
+        <v>-3680707.375214659</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -941,12 +941,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -956,44 +956,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>555394863.220544</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>5.897868</v>
+        <v>677151123.07819</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-495610837.973555</v>
+        <v>121756259.857646</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>3176374.999999989</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0</v>
+        <v>3176374.999999989</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>479090482.6056378</v>
+        <v>660752792.8467374</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1117479.095373449</v>
+        <v>1139556.973486583</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1117479.095373449</v>
+        <v>1139556.973486583</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1117479.095373449</v>
+        <v>2036818.026513407</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1006,12 +1006,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1025,40 +1025,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>282411706.537503</v>
+        <v>495610843.871423</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>5.897868</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>395257364.636327</v>
+        <v>-495610837.973555</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>577512.137436</v>
+        <v>0</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>577512.137436</v>
+        <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>295567701.6207994</v>
+        <v>479090482.6056378</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>689412.0000724341</v>
+        <v>826255.9103718251</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>689412.0000724341</v>
+        <v>826255.9103718251</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-111899.862636434</v>
+        <v>-826255.9103718251</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1071,12 +1071,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1086,66 +1086,62 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>252839704.1525801</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>573332157.534611</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>13345131.32199552</v>
+        <v>116552055.190546</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>553112.0399323378</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>553112.0399323378</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>175088694.3056089</v>
+        <v>456780102.344065</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>408394.5785326853</v>
+        <v>787778.6618706449</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>408394.5785326853</v>
+        <v>787778.6618706449</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>144717.4613996526</v>
+        <v>-2089854.297738896</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>78177410.48970658</v>
+        <v>0</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1155,44 +1151,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>282411706.537503</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>677669071.17383</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>395257364.636327</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>577512.137436</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>577512.137436</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>159602618.1970353</v>
+        <v>295567701.6207994</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>372273.2884027411</v>
+        <v>509746.21547685</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>372273.2884027411</v>
+        <v>509746.21547685</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-372273.2884028812</v>
+        <v>67765.92195914994</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1205,77 +1201,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>252839704.1525801</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>13345131.32199552</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>553112.0399323378</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>553112.0399323378</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>175088694.3056089</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>333311.4262079922</v>
+        <v>301963.9791683741</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>298128.7285684586</v>
+        <v>301963.9791683741</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-333311.4262079922</v>
+        <v>251148.0607639638</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0</v>
+        <v>78177410.48970658</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>35182.6976395336</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1285,131 +1285,127 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>150752807.5253913</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>483436565.922284</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-2890025.391775267</v>
+        <v>483436565.922284</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>-1.400229695e-07</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>-1.400229695e-07</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>101885166.4356003</v>
+        <v>159602618.1970353</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>237647.266548075</v>
+        <v>275256.1601284592</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>237647.266548075</v>
+        <v>275256.1601284592</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>76564.53221885448</v>
+        <v>-275256.1601285993</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>48760833.18343966</v>
+        <v>0</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-1777.693204525303</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>100000076.2228826</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>233250.2914836818</v>
+        <v>246448.0427768362</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>233250.2914836818</v>
+        <v>211265.3451373026</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-223681.2800384703</v>
+        <v>-246448.0427768362</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>0</v>
+        <v>35182.6976395336</v>
       </c>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1423,193 +1419,197 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>150752807.5253913</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>865.2490320000001</v>
+        <v>-2890025.391775267</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>46285.475043</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>46285.475043</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>99998716.6593553</v>
+        <v>101885166.4356003</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>233247.1203002087</v>
+        <v>175714.6593453142</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>233247.1203002087</v>
+        <v>175714.6593453142</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-186961.6452572086</v>
+        <v>138497.1394216153</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0</v>
+        <v>48760833.18343966</v>
       </c>
       <c r="R11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>-1777.693204525303</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>100000076.2228826</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>237296.9273851892</v>
+        <v>172463.5679828415</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>212249.0430628146</v>
+        <v>172463.5679828415</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-237296.9273851892</v>
+        <v>-162894.5565376299</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>25047.88432237454</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>100000230.666889</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>100001095.915921</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>865.2490320000001</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>46285.475043</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>46285.475043</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>99998716.6593553</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>176210.3399674063</v>
+        <v>172461.2232328606</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>157610.4522210917</v>
+        <v>172461.2232328606</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-176210.3399674063</v>
+        <v>-126175.7481898606</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>18599.8877463146</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1618,105 +1618,105 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>100001961.5815342</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-23097109.59213662</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>63785944.13982024</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>148780.7872267444</v>
+        <v>175455.6211179616</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>148780.7872267444</v>
+        <v>150407.736795587</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>56006.17775281364</v>
+        <v>-175455.6211179616</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>0</v>
+        <v>25047.88432237454</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>37138817.432463</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>51670578.4489233</v>
+        <v>-36481150.80976</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57072716.55221563</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>133122.1762461383</v>
+        <v>126967.5272000634</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>133122.1762461383</v>
+        <v>126967.5272000634</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>35694.46238322573</v>
+        <v>-302106.2348262972</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1729,12 +1729,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1744,85 +1744,89 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>117582.8022866928</v>
+        <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>117582.8022866928</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>55152.6254462973</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -1831,125 +1835,117 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>130288.6429549198</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>111688.7552086052</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0</v>
+        <v>-130288.6429549198</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+        <v>18599.8877463146</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Maple syrupUSDT (ERC-4626)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>100001961.5815342</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
+        <v>-23097109.59213662</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>204786.964979558</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>204786.964979558</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0</v>
+        <v>63785944.13982024</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>110007.431284241</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>110007.431284241</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>94779.53369531705</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.154431</v>
+        <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-10000122.481897</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>0</v>
@@ -1964,37 +1960,41 @@
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9666785.220264766</v>
+        <v>0</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>22547.78751679543</v>
+        <v>0</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>22547.78751679543</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-22547.78751679543</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
+        <v>99849.35275556908</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2008,40 +2008,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-10156909.80992987</v>
+        <v>51670578.4489233</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>7104351.295236039</v>
+        <v>57072716.55221563</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>16570.90747333944</v>
+        <v>98429.56828483056</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>16570.90747333944</v>
+        <v>98429.56828483056</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>1715.275912790149</v>
+        <v>70387.07034453354</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,59 +2054,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9193.636315</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11647.64072964961</v>
+        <v>86939.86827108746</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11647.64072964961</v>
+        <v>86939.86827108746</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11647.64072964961</v>
+        <v>85795.55946190262</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2119,59 +2119,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5000000</v>
+        <v>10000122.636328</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5000000</v>
+        <v>0.154431</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>-10000122.481897</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>9666785.220264766</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11634.32758806326</v>
+        <v>16671.66999247915</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11634.32758806326</v>
+        <v>16671.66999247915</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11634.32758806284</v>
+        <v>-16671.66999247915</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2184,59 +2184,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>0.28330096818</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>566848.624341</v>
+        <v>-10156909.80992987</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>7104351.295236039</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11590.21021272623</v>
+        <v>12252.40838666043</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11590.21021272623</v>
+        <v>12252.40838666043</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11590.21021272587</v>
+        <v>6033.774999469159</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2249,17 +2249,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2268,40 +2268,40 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5000000</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2224.277443</v>
+        <v>9193.636315</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>-3e-14</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>-3e-14</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4819813.116676098</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11242.2195744719</v>
+        <v>8612.180786741585</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11242.2195744719</v>
+        <v>8612.180786741585</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11242.21957446824</v>
+        <v>-8612.180786741585</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2314,59 +2314,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>977119.890305955</v>
+        <v>5000000</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>5000000</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-273029.0857638157</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>2903718.839188301</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6772.927493752721</v>
+        <v>8602.337146742522</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6772.927493752721</v>
+        <v>8602.337146742522</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2773.497496555837</v>
+        <v>-8602.337146742098</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2379,59 +2379,59 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>427.8972157084487</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-203.1796532231052</v>
+        <v>566848.624341</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>1097625.680429284</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2560.21314753279</v>
+        <v>8569.717080494091</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2560.21314753279</v>
+        <v>8569.717080494091</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1937.220397275099</v>
+        <v>-8569.717080493736</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2444,77 +2444,77 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>4997775.722557</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>5000000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2946.286265177527</v>
+        <v>2224.277443</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>3.65681e-09</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>3.65681e-09</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>4819813.116676098</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2284.595992548921</v>
+        <v>8312.415335162012</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2043.445393696719</v>
+        <v>8312.415335162012</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2284.595992548921</v>
+        <v>-8312.415335158355</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>241.1505988522019</v>
+        <v>0</v>
       </c>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2524,44 +2524,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>37220.756204</v>
+        <v>977119.890305955</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>9229822.108306</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>9192601.352102</v>
+        <v>-273029.0857638157</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>125.378836</v>
+        <v>9546.424990308558</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>125.378836</v>
+        <v>9546.424990308558</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>343636.6219795333</v>
+        <v>2903718.839188301</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>801.5328114605254</v>
+        <v>5007.853297123951</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>801.5328114605254</v>
+        <v>5007.853297123951</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-676.1539754605254</v>
+        <v>4538.571693184606</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2574,59 +2574,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>133501.211399</v>
+        <v>427.8972157084487</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.545609</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>-203.1796532231052</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>4497.433544807889</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>4497.433544807889</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>133501.211399</v>
+        <v>1097625.680429284</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>311.391727370663</v>
+        <v>1893.002968662855</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>311.391727370663</v>
+        <v>1893.002968662855</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133811.0575173707</v>
+        <v>2604.430576145034</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2639,124 +2639,124 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3222.097566494505</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.515546237171066</v>
+        <v>1689.21365014394</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.515546237171066</v>
+        <v>1448.063051291738</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.51554622810153</v>
+        <v>-1689.21365014394</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>0</v>
+        <v>241.1505988522019</v>
       </c>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>10.263802</v>
+        <v>504861.558051</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2500.221225</v>
+        <v>1066559.875133</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2489.957423</v>
+        <v>561698.317082</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>1260.904571864759</v>
+        <v>504861.558051</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.941061347443882</v>
+        <v>870.7015927146664</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.941061347443882</v>
+        <v>870.7015927146664</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.941061342813172</v>
+        <v>-3673.959738315541</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2769,12 +2769,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2784,44 +2784,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>37220.756204</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>9229822.108306</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>98.58562175646877</v>
+        <v>9192601.352102</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>125.378836</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>125.378836</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>380.1986824877172</v>
+        <v>343636.6219795333</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.8868138591646316</v>
+        <v>592.6475274285834</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.8868138591646316</v>
+        <v>592.6475274285834</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.24227237824201</v>
+        <v>-467.2686914285835</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2834,59 +2834,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>133501.211399</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>1.545609</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>-133499.66579</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>-133499.66579</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>-133499.66579</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>133501.211399</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6621906557259715</v>
+        <v>230.2407769828742</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6621906557259715</v>
+        <v>230.2407769828742</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6621906557259715</v>
+        <v>-133729.9065669829</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2899,12 +2899,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2914,44 +2914,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>0</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>9.069536521e-09</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>9.069536521e-09</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>3222.097566494505</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2313139372492132</v>
+        <v>5.556940191404734</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2313139372492132</v>
+        <v>5.556940191404734</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1000661098778267</v>
+        <v>-5.556940182335198</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2964,59 +2964,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>10.263802</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>2500.221225</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>2489.957423</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4.63071e-09</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4.63071e-09</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>1260.904571864759</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05109717130048898</v>
+        <v>2.174599355954421</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05109717130048898</v>
+        <v>2.174599355954421</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05109131360081347</v>
+        <v>-2.174599351323711</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3029,12 +3029,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3044,44 +3044,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.05756</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.057783</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.000223</v>
+        <v>98.58562175646877</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.000223</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.000223</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.05756</v>
+        <v>380.1986824877172</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0001342587654421061</v>
+        <v>0.6557037134458001</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0001342587654421061</v>
+        <v>0.6557037134458001</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>8.874123455789391e-05</v>
+        <v>13.47338252396084</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3094,59 +3094,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.006327</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.006346</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>0</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.006327</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.475773469340176e-05</v>
+        <v>0.489618951577551</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.475773469340176e-05</v>
+        <v>0.489618951577551</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>4.242265306598241e-06</v>
+        <v>-0.489618951577551</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3159,12 +3159,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3174,44 +3174,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.339130103542555e-05</v>
+        <v>0.1710318417542014</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.339130103542555e-05</v>
+        <v>0.1710318417542014</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.028484890934055e-05</v>
+        <v>0.1603482053728386</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3224,59 +3224,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001696</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.0017</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4e-06</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4e-06</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4e-06</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001696</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.955921928245516e-06</v>
+        <v>0.03778087658651134</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.955921928245516e-06</v>
+        <v>0.03778087658651134</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>4.407807175448342e-08</v>
+        <v>-0.03777501888683583</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3289,12 +3289,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3304,44 +3304,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.05756</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.057783</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>0.000223</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>0.000223</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0</v>
+        <v>0.000223</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.05756</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.89263885393107e-06</v>
+        <v>9.926995406450302e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.89263885393107e-06</v>
+        <v>9.926995406450302e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.89263885393107e-06</v>
+        <v>0.000123730045935497</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3354,17 +3354,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3373,40 +3373,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.006327</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.006346</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>1.9e-05</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>1.9e-05</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.006327</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.213269383546006e-06</v>
+        <v>1.091176162901513e-05</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.213269383546006e-06</v>
+        <v>1.091176162901513e-05</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.048151278510056e-07</v>
+        <v>8.088238370984875e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3419,12 +3419,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3434,44 +3434,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.746956486839888e-07</v>
+        <v>9.901430526886969e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.746956486839888e-07</v>
+        <v>9.901430526886969e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.746956486839888e-07</v>
+        <v>-6.794978400801969e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3484,59 +3484,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>0.001696</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>4e-06</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>4e-06</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>1.885188333333333e-08</v>
+        <v>0.001696</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.397203930840773e-11</v>
+        <v>2.924979883485009e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.397203930840773e-11</v>
+        <v>2.924979883485009e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.310867203930841e-08</v>
+        <v>1.075020116514991e-06</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3549,12 +3549,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3589,19 +3589,19 @@
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0</v>
+        <v>2.138796116658449e-06</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0</v>
+        <v>2.138796116658449e-06</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0</v>
+        <v>-2.138796116658449e-06</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3614,12 +3614,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3629,44 +3629,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0</v>
+        <v>8.970825523076592e-07</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>8.970825523076592e-07</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0</v>
+        <v>-8.862829661265914e-08</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3679,12 +3679,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3694,14 +3694,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -3719,19 +3719,19 @@
         <v>0</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0</v>
+        <v>1.291686912435241e-07</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0</v>
+        <v>1.291686912435241e-07</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0</v>
+        <v>-1.291686912435241e-07</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3739,21 +3739,17 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3763,7 +3759,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3776,31 +3772,31 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>-1.30647e-08</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>-1.30647e-08</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0</v>
+        <v>1.885188333333333e-08</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0</v>
+        <v>3.251260584658391e-11</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0</v>
+        <v>3.251260584658391e-11</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>-1.309721260584658e-08</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3813,12 +3809,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3828,7 +3824,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3841,22 +3837,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3865,46 +3861,42 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>0</v>
       </c>
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3922,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3937,36 +3929,32 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3994,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4011,34 +3999,38 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4056,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4071,31 +4063,27 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4104,28 +4092,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>48.90651074914867</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4137,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>48.90651074914867</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4154,17 +4142,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4173,10 +4161,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4194,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4209,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4223,59 +4211,331 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>arbitrum</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Arbitrum — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>arbitrum</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>3757236.304283724</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9193831.918668702</v>
+        <v>3873038.977014722</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>3757236.304283724</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2464412.765539723</v>
+        <v>-7785205.707193702</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-9078029.245937703</v>
+        <v>-3757236.304283724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-7798488.779908777</v>
+        <v>-2477695.838254797</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T13:11:45+00:00</t>
+          <t>2026-06-08T12:38:03+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -857,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2351090.985412234</v>
+        <v>999709.8043088721</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2351090.985412234</v>
+        <v>999709.8043088721</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-2351090.985412234</v>
+        <v>-999709.8043088721</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -922,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1496811.70629198</v>
+        <v>636460.8376574647</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1496811.70629198</v>
+        <v>636460.8376574647</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-3680707.375214659</v>
+        <v>-2820356.506580144</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -987,13 +989,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1139556.973486583</v>
+        <v>484552.1870619283</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1139556.973486583</v>
+        <v>484552.1870619283</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>2036818.026513407</v>
+        <v>2691822.812938061</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1052,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>826255.9103718251</v>
+        <v>351333.1213432536</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>826255.9103718251</v>
+        <v>351333.1213432536</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-826255.9103718251</v>
+        <v>-351333.1213432536</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1117,13 +1119,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>787778.6618706449</v>
+        <v>334972.1711256192</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>787778.6618706449</v>
+        <v>334972.1711256192</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-2089854.297738896</v>
+        <v>-1637047.806993871</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1182,13 +1184,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>509746.21547685</v>
+        <v>216749.7100211961</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>509746.21547685</v>
+        <v>216749.7100211961</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>67765.92195914994</v>
+        <v>360762.4274148039</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1247,13 +1249,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>301963.9791683741</v>
+        <v>128398.4126500376</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>301963.9791683741</v>
+        <v>128398.4126500376</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>251148.0607639638</v>
+        <v>424713.6272823003</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1316,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>275256.1601284592</v>
+        <v>117041.9535799398</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>275256.1601284592</v>
+        <v>117041.9535799398</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-275256.1601285993</v>
+        <v>-117041.9535800798</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1335,35 +1337,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
@@ -1372,109 +1374,105 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>246448.0427768362</v>
+        <v>0</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>211265.3451373026</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-246448.0427768362</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>35182.6976395336</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" s="6" t="n">
-        <v>150752807.5253913</v>
+        <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-2890025.391775267</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>101885166.4356003</v>
+        <v>0</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>175714.6593453142</v>
+        <v>0</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>175714.6593453142</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>138497.1394216153</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>48760833.18343966</v>
+        <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>99849.35275556908</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>(avg excl. lending_idle)</t>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1484,62 +1482,66 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>150752807.5253913</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-1777.693204525303</v>
+        <v>-2890025.391775267</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>100000076.2228826</v>
+        <v>101885166.4356003</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>172463.5679828415</v>
+        <v>74715.81014866754</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>172463.5679828415</v>
+        <v>74715.81014866754</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-162894.5565376299</v>
+        <v>239495.9886182619</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>0</v>
+        <v>48760833.18343966</v>
       </c>
       <c r="R12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1549,44 +1551,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>865.2490320000001</v>
+        <v>-1777.693204525303</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>46285.475043</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>46285.475043</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>99998716.6593553</v>
+        <v>100000076.2228826</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>172461.2232328606</v>
+        <v>73333.41026285538</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>172461.2232328606</v>
+        <v>73333.41026285538</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-126175.7481898606</v>
+        <v>-63764.39881764386</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1599,216 +1601,212 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>100000230.666889</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>100001095.915921</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>865.2490320000001</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>46285.475043</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>46285.475043</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>99998716.6593553</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>175455.6211179616</v>
+        <v>73332.41324931609</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>150407.736795587</v>
+        <v>73332.41324931609</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-175455.6211179616</v>
+        <v>-27046.93820631609</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>25047.88432237454</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-36481150.80976</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-175138.7076262338</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-175138.7076262338</v>
+        <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>126967.5272000634</v>
+        <v>104792.4245150115</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>126967.5272000634</v>
+        <v>69609.72687547788</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-302106.2348262972</v>
+        <v>-104792.4245150115</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>0</v>
+        <v>35182.6976395336</v>
       </c>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>37138817.432463</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>-36481150.80976</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>53987.99219524934</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>53987.99219524934</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>-229126.6998214831</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1817,13 +1815,13 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>0</v>
@@ -1838,25 +1836,25 @@
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>130288.6429549198</v>
+        <v>74605.66423888269</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>111688.7552086052</v>
+        <v>49557.77991650814</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-130288.6429549198</v>
+        <v>-74605.66423888269</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>18599.8877463146</v>
+        <v>25047.88432237454</v>
       </c>
       <c r="S17" t="inlineStr"/>
     </row>
@@ -1909,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>110007.431284241</v>
+        <v>46776.37245179069</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>110007.431284241</v>
+        <v>46776.37245179069</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>94779.53369531705</v>
+        <v>158010.5925277674</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1928,73 +1926,77 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>51670578.4489233</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0</v>
+        <v>57072716.55221563</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>41853.33747557258</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>41853.33747557258</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0</v>
+        <v>126963.3011537915</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2008,40 +2010,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>51670578.4489233</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>57072716.55221563</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>98429.56828483056</v>
+        <v>36967.79037272715</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>98429.56828483056</v>
+        <v>36967.79037272715</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>70387.07034453354</v>
+        <v>135767.6373602629</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,17 +2056,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2073,46 +2075,46 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>86939.86827108746</v>
+        <v>55400.16722461872</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>86939.86827108746</v>
+        <v>36800.27947830412</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>85795.55946190262</v>
+        <v>-55400.16722461872</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>0</v>
+        <v>18599.8877463146</v>
       </c>
       <c r="S21" t="inlineStr"/>
     </row>
@@ -2165,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>16671.66999247915</v>
+        <v>7088.977861382558</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>16671.66999247915</v>
+        <v>7088.977861382558</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-16671.66999247915</v>
+        <v>-7088.977861382558</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2230,13 +2232,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>12252.40838666043</v>
+        <v>5209.859110745132</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>12252.40838666043</v>
+        <v>5209.859110745132</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>6033.774999469159</v>
+        <v>13076.32427538445</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2295,13 +2297,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>8612.180786741585</v>
+        <v>3661.99420711762</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>8612.180786741585</v>
+        <v>3661.99420711762</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-8612.180786741585</v>
+        <v>-3661.99420711762</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2360,13 +2362,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>8602.337146742522</v>
+        <v>3657.808582878401</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>8602.337146742522</v>
+        <v>3657.808582878401</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-8602.337146742098</v>
+        <v>-3657.808582877978</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2425,13 +2427,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>8569.717080494091</v>
+        <v>3643.938171121435</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>8569.717080494091</v>
+        <v>3643.938171121435</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-8569.717080493736</v>
+        <v>-3643.938171121079</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2490,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>8312.415335162012</v>
+        <v>3534.530632633866</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>8312.415335162012</v>
+        <v>3534.530632633866</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-8312.415335158355</v>
+        <v>-3534.530632630209</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2555,13 +2557,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>5007.853297123951</v>
+        <v>2129.394426135965</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>5007.853297123951</v>
+        <v>2129.394426135965</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>4538.571693184606</v>
+        <v>7417.030564172592</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2620,13 +2622,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1893.002968662855</v>
+        <v>804.9257298420712</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1893.002968662855</v>
+        <v>804.9257298420712</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>2604.430576145034</v>
+        <v>3692.507814965818</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2685,13 +2687,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>1689.21365014394</v>
+        <v>718.2722651310652</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1448.063051291738</v>
+        <v>477.1216662788634</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-1689.21365014394</v>
+        <v>-718.2722651310652</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2750,13 +2752,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>870.7015927146664</v>
+        <v>370.2319154235454</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>870.7015927146664</v>
+        <v>370.2319154235454</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-3673.959738315541</v>
+        <v>-3173.490061024419</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2815,13 +2817,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>592.6475274285834</v>
+        <v>252.0002617278051</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>592.6475274285834</v>
+        <v>252.0002617278051</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-467.2686914285835</v>
+        <v>-126.6214257278051</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2880,13 +2882,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>230.2407769828742</v>
+        <v>97.90091643820995</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>230.2407769828742</v>
+        <v>97.90091643820995</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-133729.9065669829</v>
+        <v>-133597.5667064382</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2945,13 +2947,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>5.556940191404734</v>
+        <v>2.362872226457572</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>5.556940191404734</v>
+        <v>2.362872226457572</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-5.556940182335198</v>
+        <v>-2.362872217388036</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3010,13 +3012,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>2.174599355954421</v>
+        <v>0.92466361790342</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>2.174599355954421</v>
+        <v>0.92466361790342</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-2.174599351323711</v>
+        <v>-0.9246636132727101</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3075,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.6557037134458001</v>
+        <v>0.2788124471238044</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.6557037134458001</v>
+        <v>0.2788124471238044</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>13.47338252396084</v>
+        <v>13.85027379028283</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3140,13 +3142,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.489618951577551</v>
+        <v>0.2081913755378059</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.489618951577551</v>
+        <v>0.2081913755378059</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.489618951577551</v>
+        <v>-0.2081913755378059</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3205,13 +3207,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1710318417542014</v>
+        <v>0.07272462448776693</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.1710318417542014</v>
+        <v>0.07272462448776693</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1603482053728386</v>
+        <v>0.258655422639273</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3270,13 +3272,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.03778087658651134</v>
+        <v>0.01606484520304365</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.03778087658651134</v>
+        <v>0.01606484520304365</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-0.03777501888683583</v>
+        <v>-0.01605898750336815</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3335,13 +3337,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>9.926995406450302e-05</v>
+        <v>4.221067877310344e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>9.926995406450302e-05</v>
+        <v>4.221067877310344e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.000123730045935497</v>
+        <v>0.0001807893212268966</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3400,13 +3402,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.091176162901513e-05</v>
+        <v>4.63980133074054e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.091176162901513e-05</v>
+        <v>4.63980133074054e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>8.088238370984875e-06</v>
+        <v>1.436019866925946e-05</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3465,13 +3467,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>9.901430526886969e-06</v>
+        <v>4.210197408704911e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>9.901430526886969e-06</v>
+        <v>4.210197408704911e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-6.794978400801969e-06</v>
+        <v>-1.103745282619911e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3530,13 +3532,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>2.924979883485009e-06</v>
+        <v>1.243733690048357e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>2.924979883485009e-06</v>
+        <v>1.243733690048357e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>1.075020116514991e-06</v>
+        <v>2.756266309951643e-06</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3595,13 +3597,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>2.138796116658449e-06</v>
+        <v>9.094396858768489e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>2.138796116658449e-06</v>
+        <v>9.094396858768489e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-2.138796116658449e-06</v>
+        <v>-9.094396858768489e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3660,13 +3662,13 @@
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>8.970825523076592e-07</v>
+        <v>3.814493902536686e-07</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>8.970825523076592e-07</v>
+        <v>3.814493902536686e-07</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-8.862829661265914e-08</v>
+        <v>4.270048654413314e-07</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3725,13 +3727,13 @@
         <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>1.291686912435241e-07</v>
+        <v>5.492395141111695e-08</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1.291686912435241e-07</v>
+        <v>5.492395141111695e-08</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>-1.291686912435241e-07</v>
+        <v>-5.492395141111695e-08</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3790,13 +3792,13 @@
         <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>3.251260584658391e-11</v>
+        <v>1.382471840950931e-11</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>3.251260584658391e-11</v>
+        <v>1.382471840950931e-11</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>-1.309721260584658e-08</v>
+        <v>-1.307852471840951e-08</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -4585,7 +4587,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>3757236.304283724</v>
       </c>
     </row>
     <row r="5">
@@ -4605,7 +4607,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9193831.918668702</v>
+        <v>3873038.977014722</v>
       </c>
     </row>
     <row r="8">
@@ -4632,7 +4634,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>3757236.304283724</v>
       </c>
     </row>
     <row r="12">
@@ -4642,7 +4644,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2464412.765539723</v>
+        <v>-7785205.707193702</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4937,4 +4939,1620 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3370615309.279832</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>109055951.174984</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>83934283.91579673</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>81025902.18910897</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>130060790.0037368</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2631568381.996205</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>287033.1167687731</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>367643.1987365804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3436332710.023856</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>109133547.016997</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>81070524.8666583</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>75798768.87500143</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>123404206.9728645</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2711955662.292335</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>295801.2003837845</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>374811.1942523158</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3438806780.096234</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>109105650.4924593</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>76123440.04999478</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>75714944.50432792</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>123411196.5267537</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2719481548.522698</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>296622.0715402885</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>375081.04855245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>3443341379.37429</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>109123776.7824347</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>83542493.66401881</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>75690258.91133398</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>123405060.7543267</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2716609789.262176</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>296308.840078474</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>375575.65100055</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3451767983.804127</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>109127522.7862754</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>86558535.6429214</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>74444392.75988562</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>123403918.716754</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2723263613.898291</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>297034.5928412763</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>376494.7662132959</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3445796329.989512</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>109241926.6840944</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>55515650.13090748</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>74366553.28453328</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>112927513.3486385</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2758774686.541338</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>300907.8928589656</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>375843.4198837078</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3457497551.030852</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>109305198.8012233</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>79109652.47887604</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>77054699.32011929</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>111032090.9637735</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2746025909.46686</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>299517.3452130397</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>377119.7074270885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3433737829.859045</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>109289928.5655661</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>56675900.95969198</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>74503713.8442512</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>106296252.8520661</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2752002033.63747</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>300169.1791378667</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>374528.1628302776</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3433364995.278069</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>109349782.7302168</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>54193645.98368105</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>78737127.87731043</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>106289452.9998598</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2749824985.687001</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>299931.721938254</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>374487.4966357189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3426936270.51389</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>109304061.5112718</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>51076302.50534543</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>75242537.44162388</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>106318077.1275745</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2750025291.928074</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>299953.5699453501</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>373786.2961962642</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3419054271.885073</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>109337373.1213049</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>51145031.32584467</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>73579380.95193422</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>106356377.8226287</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2743666108.663361</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>299259.9546074161</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>372926.5827841884</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3487131871.331304</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>109342328.3371183</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>51970946.78532917</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>71375240.03334759</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>106336984.9487036</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2813136371.226805</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>306837.2861040062</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>380352.012305562</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3309862747.427698</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>109046834.1026236</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>50529324.09846896</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>69510472.6803965</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>106485554.4875584</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2639320562.05865</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>287878.6704774662</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>361016.7332039318</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>3310897469.321378</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>109458620.2372267</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>49882975.1971824</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>67540680.80231147</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>106432974.8514239</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2642612218.233233</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>288237.7013647446</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>361129.5934480979</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3322146141.580943</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>109518837.8396468</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>51274439.44802884</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>66491002.67769836</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>106442587.2808068</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2653449274.334762</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>289419.731826389</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>362356.5201281199</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3319843562.749172</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>109539351.8666015</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>52169788.46302108</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>67286649.27408095</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>106455238.2665053</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2649422534.878963</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>288980.5231839987</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>362105.3708958937</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3316623360.866395</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>109507779.6615873</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>50904742.8989519</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>66799476.11261413</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>106530285.11483</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>2647911077.078412</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>288815.6639136393</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>361754.1337441778</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>3341770538.551773</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>109623263.8502044</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>50485214.99143847</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>68028126.6911139</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>106209842.7768683</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2672454090.242148</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>291492.64453534</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>364497.0124162101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>3387602107.560916</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>109342580.9053197</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>50143398.95539194</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>35619205.44664249</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>134869772.9750939</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2722657149.278468</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>296968.4439122846</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>369496.0001640103</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>3522327931.244609</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>108244438.4938705</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>50106958.71182571</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>30889433.30164777</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>166906447.5117323</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2831210653.225533</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>308808.702667203</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>384190.9529327605</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3691758011.203047</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>108452809.4223091</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>50725251.6702591</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>54316080.27749412</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>174905990.8713613</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2968387878.961623</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>323771.0372666391</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>402671.2038194818</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>3793168501.903408</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>108810545.2478995</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>50363491.24509695</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>67704870.85992657</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>191459906.6813183</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>3039859687.869167</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>331566.6834722196</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>413732.3525313746</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>3815436515.573425</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>108790788.519045</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>50461527.69762992</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>51095777.99769017</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>150458263.8530219</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>3119660157.506038</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>340270.7618751178</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>416161.1920826031</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>3824208761.850309</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>108778836.5352057</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>51229919.97055995</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>56536069.61801664</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>148940725.8800582</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>3123753209.846468</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>340717.2034642511</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>417118.0074962338</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3798298269.581012</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>109012385.0330893</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>51077651.60920416</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>58449745.30648443</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>140084321.8061661</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>3104704165.826068</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>338639.4666613437</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>414291.8717955807</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3846549224.508112</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>109013131.1815182</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>51589907.91751318</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>58099362.01924805</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>154475144.3495293</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>3138401679.040303</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>342314.9562710425</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>419554.7492775214</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3780306162.322508</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>109024047.6455294</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>59429042.91027177</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>58855219.37465746</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>130752789.7099153</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>3087275062.682134</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>336738.4217057523</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>412329.4182796553</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3902178954.302975</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>108998604.7903199</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>67003312.22578653</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>69754438.78971349</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>135699774.815579</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>3185752823.681576</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>347479.6887256267</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>425622.4520350351</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3366262659.734222</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>108996254.8996352</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>84852106.09446886</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>78406141.98836392</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>131931405.5965129</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>2627106751.155241</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>286546.473208638</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>367168.4420957019</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3929445240.830592</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>109000464.1101925</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>86309975.97272643</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>70281418.59588619</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>129864360.3284257</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>3199019021.823361</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>348926.6730511566</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>428596.4683130372</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="n">
+        <v>9256950.219000347</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>11542442.01147743</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3757236.304283724</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>3873038.977014722</v>
+        <v>8969960.81400051</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3757236.304283724</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-7785205.707193702</v>
+        <v>-2688283.870207915</v>
       </c>
     </row>
     <row r="16">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-3757236.304283724</v>
+        <v>-8854158.141269511</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2477695.838254797</v>
+        <v>-7574617.675240585</v>
       </c>
     </row>
     <row r="25">
@@ -662,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T12:38:03+00:00</t>
+          <t>2026-06-08T14:51:02+00:00</t>
         </is>
       </c>
     </row>
@@ -859,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>999709.8043088721</v>
+        <v>3102859.783190616</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>999709.8043088721</v>
+        <v>3102859.783190616</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-999709.8043088721</v>
+        <v>-3102859.783190616</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -878,12 +878,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
+          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -893,44 +893,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>867900893.337617</v>
+        <v>555394863.220544</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1134703231.016836</v>
+        <v>677151123.07819</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>266802337.679219</v>
+        <v>121756259.857646</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-2183895.668922679</v>
+        <v>3176374.999999989</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-2183895.668922679</v>
+        <v>3176374.999999989</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>867900893.337617</v>
+        <v>660752792.8467374</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>636460.8376574647</v>
+        <v>1503933.92923752</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>636460.8376574647</v>
+        <v>1503933.92923752</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-2820356.506580144</v>
+        <v>1672441.07076247</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -943,12 +943,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -958,44 +958,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>555394863.220544</v>
+        <v>495610843.871423</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>677151123.07819</v>
+        <v>5.897868</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>121756259.857646</v>
+        <v>-495610837.973555</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3176374.999999989</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>3176374.999999989</v>
+        <v>0</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>660752792.8467374</v>
+        <v>479090482.6056378</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>484552.1870619283</v>
+        <v>1090453.857729697</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>484552.1870619283</v>
+        <v>1090453.857729697</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>2691822.812938061</v>
+        <v>-1090453.857729697</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1008,12 +1008,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1027,40 +1027,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>282411706.537503</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5.897868</v>
+        <v>677669071.17383</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-495610837.973555</v>
+        <v>395257364.636327</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>577512.137436</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0</v>
+        <v>577512.137436</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>479090482.6056378</v>
+        <v>295567701.6207994</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>351333.1213432536</v>
+        <v>672739.1842555213</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>351333.1213432536</v>
+        <v>672739.1842555213</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-351333.1213432536</v>
+        <v>-95227.04681952125</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1073,12 +1073,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,62 +1088,66 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>252839704.1525801</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>116552055.190546</v>
+        <v>13345131.32199552</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>553112.0399323378</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>553112.0399323378</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>175088694.3056089</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>334972.1711256192</v>
+        <v>398517.9190202518</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>334972.1711256192</v>
+        <v>398517.9190202518</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-1637047.806993871</v>
+        <v>154594.120912086</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0</v>
+        <v>78177410.48970658</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1153,44 +1157,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>282411706.537503</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>483436565.922284</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>395257364.636327</v>
+        <v>483436565.922284</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>577512.137436</v>
+        <v>-1.400229695e-07</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>577512.137436</v>
+        <v>-1.400229695e-07</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>295567701.6207994</v>
+        <v>159602618.1970353</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>216749.7100211961</v>
+        <v>363270.1901531557</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>216749.7100211961</v>
+        <v>363270.1901531557</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>360762.4274148039</v>
+        <v>-363270.1901532957</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1203,81 +1207,77 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>252839704.1525801</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>13345131.32199552</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>553112.0399323378</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>553112.0399323378</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>175088694.3056089</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>128398.4126500376</v>
+        <v>325250.5859292409</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>128398.4126500376</v>
+        <v>290067.8882897074</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>424713.6272823003</v>
+        <v>-325250.5859292409</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>78177410.48970658</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+        <v>35182.6976395336</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1287,62 +1287,66 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>150752807.5253913</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>-2890025.391775267</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>159602618.1970353</v>
+        <v>101885166.4356003</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>117041.9535799398</v>
+        <v>231899.9788534417</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>117041.9535799398</v>
+        <v>231899.9788534417</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-117041.9535800798</v>
+        <v>82311.81991348779</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0</v>
+        <v>48760833.18343966</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1356,257 +1360,253 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>-1777.693204525303</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>100000076.2228826</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0</v>
+        <v>227609.340718769</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>227609.340718769</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0</v>
+        <v>-218040.3292735575</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>Spark PYUSD (SparkLend spToken)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E11" s="6" t="n">
-        <v>0</v>
+        <v>100000230.666889</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>100001095.915921</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>865.2490320000001</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>46285.475043</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>46285.475043</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0</v>
+        <v>99998716.6593553</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>227606.2462275466</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>227606.2462275466</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0</v>
+        <v>-181320.7711845466</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>150752807.5253913</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-2890025.391775267</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>101885166.4356003</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>74715.81014866754</v>
+        <v>231558.1123314957</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>74715.81014866754</v>
+        <v>206510.2280091212</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>239495.9886182619</v>
+        <v>-231558.1123314957</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>48760833.18343966</v>
+        <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+        <v>25047.88432237454</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-1777.693204525303</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>100000076.2228826</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>73333.41026285538</v>
+        <v>171948.8496785754</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>73333.41026285538</v>
+        <v>153348.9619322608</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-63764.39881764386</v>
+        <v>-171948.8496785754</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>18599.8877463146</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1616,44 +1616,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>100001961.5815342</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>865.2490320000001</v>
+        <v>-23097109.59213662</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>46285.475043</v>
+        <v>204786.964979558</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>46285.475043</v>
+        <v>204786.964979558</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>99998716.6593553</v>
+        <v>63785944.13982024</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>73332.41324931609</v>
+        <v>145182.6562654815</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>73332.41324931609</v>
+        <v>145182.6562654815</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-27046.93820631609</v>
+        <v>59604.30871407653</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1666,17 +1666,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1685,128 +1685,132 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>51670578.4489233</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>57072716.55221563</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>104792.4245150115</v>
+        <v>129902.7348591807</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>69609.72687547788</v>
+        <v>129902.7348591807</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-104792.4245150115</v>
+        <v>38913.90377018342</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>35182.6976395336</v>
+        <v>0</v>
       </c>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-36481150.80976</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-175138.7076262338</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>-175138.7076262338</v>
+        <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>53987.99219524934</v>
+        <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>53987.99219524934</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>-229126.6998214831</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1815,170 +1819,166 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>74605.66423888269</v>
+        <v>114739.1668327748</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>49557.77991650814</v>
+        <v>114739.1668327748</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-74605.66423888269</v>
+        <v>57996.26090021532</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>25047.88432237454</v>
+        <v>0</v>
       </c>
       <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" s="6" t="n">
-        <v>100001961.5815342</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>0</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-23097109.59213662</v>
+        <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>63785944.13982024</v>
+        <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>46776.37245179069</v>
+        <v>0</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>46776.37245179069</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>158010.5925277674</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
+        <v>99849.35275556908</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>10000122.636328</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>0.154431</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>51670578.4489233</v>
+        <v>-10000122.481897</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>57072716.55221563</v>
+        <v>9666785.220264766</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>41853.33747557258</v>
+        <v>22002.48933761242</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>41853.33747557258</v>
+        <v>22002.48933761242</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>126963.3011537915</v>
+        <v>-22002.48933761242</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1991,12 +1991,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2010,40 +2010,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>0.28330096818</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>-10156909.80992987</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>7104351.295236039</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>36967.79037272715</v>
+        <v>16170.15482007395</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>36967.79037272715</v>
+        <v>16170.15482007395</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>135767.6373602629</v>
+        <v>2116.028566055634</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2056,124 +2056,124 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>9193.636315</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0</v>
+        <v>-3e-14</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0</v>
+        <v>-3e-14</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>55400.16722461872</v>
+        <v>11365.95290210002</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>36800.27947830412</v>
+        <v>11365.95290210002</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-55400.16722461872</v>
+        <v>-11365.95290210002</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>18599.8877463146</v>
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.154431</v>
+        <v>5000000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-10000122.481897</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>9666785.220264766</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>7088.977861382558</v>
+        <v>11352.96172699757</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>7088.977861382558</v>
+        <v>11352.96172699757</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-7088.977861382558</v>
+        <v>-11352.96172699714</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2186,59 +2186,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-10156909.80992987</v>
+        <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>7104351.295236039</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>5209.859110745132</v>
+        <v>11309.91129112959</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>5209.859110745132</v>
+        <v>11309.91129112959</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>13076.32427538445</v>
+        <v>-11309.91129112923</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2251,17 +2251,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2270,40 +2270,40 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>4997775.722557</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5000000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>9193.636315</v>
+        <v>2224.277443</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-3e-14</v>
+        <v>3.65681e-09</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3e-14</v>
+        <v>3.65681e-09</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>4819813.116676098</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3661.99420711762</v>
+        <v>10970.33649683651</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3661.99420711762</v>
+        <v>10970.33649683651</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-3661.99420711762</v>
+        <v>-10970.33649683286</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2316,59 +2316,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5000000</v>
+        <v>977119.890305955</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5000000</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>-273029.0857638157</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>9546.424990308558</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>9546.424990308558</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>2903718.839188301</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>3657.808582878401</v>
+        <v>6609.130268533579</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>3657.808582878401</v>
+        <v>6609.130268533579</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-3657.808582877978</v>
+        <v>2937.294721774979</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2381,59 +2381,59 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>427.8972157084487</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>566848.624341</v>
+        <v>-203.1796532231052</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4497.433544807889</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4497.433544807889</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>1097625.680429284</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>3643.938171121435</v>
+        <v>2498.296670511259</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>3643.938171121435</v>
+        <v>2498.296670511259</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-3643.938171121079</v>
+        <v>1999.13687429663</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2446,77 +2446,77 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5000000</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2224.277443</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>4819813.116676098</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>3534.530632633866</v>
+        <v>2229.345071190106</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>3534.530632633866</v>
+        <v>1988.194472337904</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-3534.530632630209</v>
+        <v>-2229.345071190106</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>0</v>
+        <v>241.1505988522019</v>
       </c>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2526,44 +2526,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>977119.890305955</v>
+        <v>37220.756204</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>9229822.108306</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-273029.0857638157</v>
+        <v>9192601.352102</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>125.378836</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>125.378836</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>2903718.839188301</v>
+        <v>343636.6219795333</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2129.394426135965</v>
+        <v>782.1484535797669</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2129.394426135965</v>
+        <v>782.1484535797669</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>7417.030564172592</v>
+        <v>-656.7696175797669</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2576,59 +2576,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>427.8972157084487</v>
+        <v>133501.211399</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>1.545609</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-203.1796532231052</v>
+        <v>-133499.66579</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>-133499.66579</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>-133499.66579</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>1097625.680429284</v>
+        <v>133501.211399</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>804.9257298420712</v>
+        <v>303.8609955052241</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>804.9257298420712</v>
+        <v>303.8609955052241</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>3692.507814965818</v>
+        <v>-133803.5267855052</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2641,124 +2641,124 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2946.286265177527</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
+        <v>9.069536521e-09</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0</v>
+        <v>9.069536521e-09</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>3222.097566494505</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>718.2722651310652</v>
+        <v>7.33378943838793</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>477.1216662788634</v>
+        <v>7.33378943838793</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-718.2722651310652</v>
+        <v>-7.333789429318393</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>241.1505988522019</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>504861.558051</v>
+        <v>10.263802</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>2500.221225</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>561698.317082</v>
+        <v>2489.957423</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-2803.258145600874</v>
+        <v>4.63071e-09</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-2803.258145600874</v>
+        <v>4.63071e-09</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>504861.558051</v>
+        <v>1260.904571864759</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>370.2319154235454</v>
+        <v>2.86993439556747</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>370.2319154235454</v>
+        <v>2.86993439556747</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-3173.490061024419</v>
+        <v>-2.86993439093676</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2771,12 +2771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2786,44 +2786,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>37220.756204</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>9229822.108306</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>9192601.352102</v>
+        <v>98.58562175646877</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>125.378836</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>125.378836</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>343636.6219795333</v>
+        <v>380.1986824877172</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>252.0002617278051</v>
+        <v>0.8653670550240247</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>252.0002617278051</v>
+        <v>0.8653670550240247</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-126.6214257278051</v>
+        <v>13.26371918238261</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2836,59 +2836,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>133501.211399</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.545609</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>133501.211399</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>97.90091643820995</v>
+        <v>0.6461761639018665</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>97.90091643820995</v>
+        <v>0.6461761639018665</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-133597.5667064382</v>
+        <v>-0.6461761639018665</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2901,12 +2901,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2916,44 +2916,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>3222.097566494505</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>2.362872226457572</v>
+        <v>0.2257198154885884</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>2.362872226457572</v>
+        <v>0.2257198154885884</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-2.362872217388036</v>
+        <v>0.1056602316384515</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2966,59 +2966,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>10.263802</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2500.221225</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>2489.957423</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>1260.904571864759</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.92466361790342</v>
+        <v>0.04986143167633277</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.92466361790342</v>
+        <v>0.04986143167633277</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.9246636132727101</v>
+        <v>-0.04985557397665726</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3031,12 +3031,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3046,44 +3046,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>0.05756</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>0.057783</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>98.58562175646877</v>
+        <v>0.000223</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>0.000223</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>0.000223</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>380.1986824877172</v>
+        <v>0.05756</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2788124471238044</v>
+        <v>0.000131011836656725</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.2788124471238044</v>
+        <v>0.000131011836656725</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>13.85027379028283</v>
+        <v>9.1988163343275e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3096,59 +3096,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.006327</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.006346</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.006327</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2081913755378059</v>
+        <v>1.440083201054724e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.2081913755378059</v>
+        <v>1.440083201054724e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.2081913755378059</v>
+        <v>4.59916798945276e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3161,12 +3161,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3176,44 +3176,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.07272462448776693</v>
+        <v>1.306744433480383e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.07272462448776693</v>
+        <v>1.306744433480383e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.258655422639273</v>
+        <v>-9.960992208718827e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3226,59 +3226,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>0.001696</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>0.0017</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>0.001696</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.01606484520304365</v>
+        <v>3.860251476195372e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.01606484520304365</v>
+        <v>3.860251476195372e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-0.01605898750336815</v>
+        <v>1.397485238046279e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3291,12 +3291,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3306,44 +3306,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.05756</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.057783</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.000223</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.000223</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.000223</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.05756</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>4.221067877310344e-05</v>
+        <v>2.822682956976316e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>4.221067877310344e-05</v>
+        <v>2.822682956976316e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.0001807893212268966</v>
+        <v>-2.822682956976316e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3356,17 +3356,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3375,40 +3375,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.006327</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.006327</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>4.63980133074054e-06</v>
+        <v>1.18392754301228e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4.63980133074054e-06</v>
+        <v>1.18392754301228e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>1.436019866925946e-05</v>
+        <v>-3.754732873172804e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3421,12 +3421,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3436,44 +3436,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>4.210197408704911e-06</v>
+        <v>1.704707898561497e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>4.210197408704911e-06</v>
+        <v>1.704707898561497e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.103745282619911e-06</v>
+        <v>-1.704707898561497e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3486,59 +3486,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.001696</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>4e-06</v>
+        <v>-1.30647e-08</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>4e-06</v>
+        <v>-1.30647e-08</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.001696</v>
+        <v>1.885188333333333e-08</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.243733690048357e-06</v>
+        <v>4.290861466188852e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.243733690048357e-06</v>
+        <v>4.290861466188852e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>2.756266309951643e-06</v>
+        <v>-1.310760861466189e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3551,12 +3551,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3566,14 +3566,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3591,19 +3591,19 @@
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>9.094396858768489e-07</v>
+        <v>0</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>9.094396858768489e-07</v>
+        <v>0</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-9.094396858768489e-07</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3616,12 +3616,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3631,44 +3631,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>0</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>3.814493902536686e-07</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>3.814493902536686e-07</v>
+        <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>4.270048654413314e-07</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3681,12 +3681,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3696,14 +3696,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -3721,19 +3721,19 @@
         <v>0</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>5.492395141111695e-08</v>
+        <v>0</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>5.492395141111695e-08</v>
+        <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>-5.492395141111695e-08</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3741,17 +3741,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3761,7 +3765,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3774,31 +3778,31 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>1.885188333333333e-08</v>
+        <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>1.382471840950931e-11</v>
+        <v>0</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1.382471840950931e-11</v>
+        <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>-1.307852471840951e-08</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3811,12 +3815,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3826,7 +3830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3839,22 +3843,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>48.90651074914867</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3863,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3871,34 +3875,38 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3916,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3931,32 +3939,36 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3984,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4001,38 +4013,34 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4050,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4065,27 +4073,31 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4094,28 +4106,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>89900000</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4127,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>89900000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4144,17 +4156,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4163,10 +4175,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4184,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4199,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4213,50 +4225,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>116552055.190546</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>0</v>
@@ -4265,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4273,52 +4285,56 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>90000000</v>
+        <v>867900893.337617</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90000000</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>266802337.679219</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>90000000</v>
+        <v>867900893.337617</v>
       </c>
       <c r="M55" s="7" t="n">
         <v>0</v>
@@ -4330,64 +4346,64 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>89900000</v>
+        <v>504861.558051</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>89900000</v>
+        <v>1066559.875133</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>561698.317082</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>89900000</v>
+        <v>504861.558051</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -4399,64 +4415,64 @@
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>89900000</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>89900000</v>
+        <v>37138817.432463</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>-36481150.80976</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>89900000</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -4468,17 +4484,17 @@
         <v>0</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4603,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3757236.304283724</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="5">
@@ -4607,7 +4623,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3873038.977014722</v>
+        <v>8969960.81400051</v>
       </c>
     </row>
     <row r="8">
@@ -4634,7 +4650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3757236.304283724</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="12">
@@ -4644,7 +4660,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-7785205.707193702</v>
+        <v>-2688283.870207915</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9193831.918668702</v>
+        <v>8969960.81400051</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2464412.765539723</v>
+        <v>-2688283.870207915</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-9078029.245937703</v>
+        <v>-8854158.141269511</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-7798488.779908777</v>
+        <v>-7574617.675240585</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T13:11:45+00:00</t>
+          <t>2026-06-08T14:51:02+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -857,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>2351090.985412234</v>
+        <v>3102859.783190616</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2351090.985412234</v>
+        <v>3102859.783190616</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-2351090.985412234</v>
+        <v>-3102859.783190616</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -876,12 +878,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
+          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -891,44 +893,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>867900893.337617</v>
+        <v>555394863.220544</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1134703231.016836</v>
+        <v>677151123.07819</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>266802337.679219</v>
+        <v>121756259.857646</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-2183895.668922679</v>
+        <v>3176374.999999989</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-2183895.668922679</v>
+        <v>3176374.999999989</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>867900893.337617</v>
+        <v>660752792.8467374</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1496811.70629198</v>
+        <v>1503933.92923752</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1496811.70629198</v>
+        <v>1503933.92923752</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-3680707.375214659</v>
+        <v>1672441.07076247</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -941,12 +943,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -956,44 +958,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>555394863.220544</v>
+        <v>495610843.871423</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>677151123.07819</v>
+        <v>5.897868</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>121756259.857646</v>
+        <v>-495610837.973555</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3176374.999999989</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>3176374.999999989</v>
+        <v>0</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>660752792.8467374</v>
+        <v>479090482.6056378</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1139556.973486583</v>
+        <v>1090453.857729697</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1139556.973486583</v>
+        <v>1090453.857729697</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>2036818.026513407</v>
+        <v>-1090453.857729697</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1006,12 +1008,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1025,40 +1027,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>282411706.537503</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5.897868</v>
+        <v>677669071.17383</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-495610837.973555</v>
+        <v>395257364.636327</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>577512.137436</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0</v>
+        <v>577512.137436</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>479090482.6056378</v>
+        <v>295567701.6207994</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>826255.9103718251</v>
+        <v>672739.1842555213</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>826255.9103718251</v>
+        <v>672739.1842555213</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-826255.9103718251</v>
+        <v>-95227.04681952125</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1071,12 +1073,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1086,62 +1088,66 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>252839704.1525801</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>116552055.190546</v>
+        <v>13345131.32199552</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>553112.0399323378</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>553112.0399323378</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>175088694.3056089</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>787778.6618706449</v>
+        <v>398517.9190202518</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>787778.6618706449</v>
+        <v>398517.9190202518</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-2089854.297738896</v>
+        <v>154594.120912086</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0</v>
+        <v>78177410.48970658</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1151,44 +1157,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>282411706.537503</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>483436565.922284</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>395257364.636327</v>
+        <v>483436565.922284</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>577512.137436</v>
+        <v>-1.400229695e-07</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>577512.137436</v>
+        <v>-1.400229695e-07</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>295567701.6207994</v>
+        <v>159602618.1970353</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>509746.21547685</v>
+        <v>363270.1901531557</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>509746.21547685</v>
+        <v>363270.1901531557</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>67765.92195914994</v>
+        <v>-363270.1901532957</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1201,81 +1207,77 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>252839704.1525801</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>13345131.32199552</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>553112.0399323378</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>553112.0399323378</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>175088694.3056089</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>301963.9791683741</v>
+        <v>325250.5859292409</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>301963.9791683741</v>
+        <v>290067.8882897074</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>251148.0607639638</v>
+        <v>-325250.5859292409</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>78177410.48970658</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+        <v>35182.6976395336</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1285,127 +1287,131 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>150752807.5253913</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>-2890025.391775267</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>159602618.1970353</v>
+        <v>101885166.4356003</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>275256.1601284592</v>
+        <v>231899.9788534417</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>275256.1601284592</v>
+        <v>231899.9788534417</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-275256.1601285993</v>
+        <v>82311.81991348779</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0</v>
+        <v>48760833.18343966</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>-1777.693204525303</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>100000076.2228826</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>246448.0427768362</v>
+        <v>227609.340718769</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>211265.3451373026</v>
+        <v>227609.340718769</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-246448.0427768362</v>
+        <v>-218040.3292735575</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>35182.6976395336</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1419,197 +1425,193 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>150752807.5253913</v>
+        <v>100000230.666889</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>100001095.915921</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-2890025.391775267</v>
+        <v>865.2490320000001</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>46285.475043</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>46285.475043</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>101885166.4356003</v>
+        <v>99998716.6593553</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>175714.6593453142</v>
+        <v>227606.2462275466</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>175714.6593453142</v>
+        <v>227606.2462275466</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>138497.1394216153</v>
+        <v>-181320.7711845466</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>48760833.18343966</v>
+        <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-1777.693204525303</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>100000076.2228826</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>172463.5679828415</v>
+        <v>231558.1123314957</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>172463.5679828415</v>
+        <v>206510.2280091212</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-162894.5565376299</v>
+        <v>-231558.1123314957</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0</v>
+        <v>25047.88432237454</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>865.2490320000001</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>46285.475043</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>46285.475043</v>
+        <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>99998716.6593553</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>172461.2232328606</v>
+        <v>171948.8496785754</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>172461.2232328606</v>
+        <v>153348.9619322608</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-126175.7481898606</v>
+        <v>-171948.8496785754</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>18599.8877463146</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1618,105 +1620,105 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>100001961.5815342</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>-23097109.59213662</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>204786.964979558</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>204786.964979558</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>63785944.13982024</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>175455.6211179616</v>
+        <v>145182.6562654815</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>150407.736795587</v>
+        <v>145182.6562654815</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-175455.6211179616</v>
+        <v>59604.30871407653</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>25047.88432237454</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-36481150.80976</v>
+        <v>51670578.4489233</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-175138.7076262338</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>-175138.7076262338</v>
+        <v>168816.6386293641</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>73619968.24222299</v>
+        <v>57072716.55221563</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>126967.5272000634</v>
+        <v>129902.7348591807</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>126967.5272000634</v>
+        <v>129902.7348591807</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-302106.2348262972</v>
+        <v>38913.90377018342</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1798,17 +1800,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1817,135 +1819,139 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>130288.6429549198</v>
+        <v>114739.1668327748</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>111688.7552086052</v>
+        <v>114739.1668327748</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-130288.6429549198</v>
+        <v>57996.26090021532</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>18599.8877463146</v>
+        <v>0</v>
       </c>
       <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" s="6" t="n">
-        <v>100001961.5815342</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>0</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-23097109.59213662</v>
+        <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>63785944.13982024</v>
+        <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>110007.431284241</v>
+        <v>0</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>110007.431284241</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>94779.53369531705</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
+        <v>99849.35275556908</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>10000122.636328</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>0.154431</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>-10000122.481897</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>0</v>
@@ -1960,41 +1966,37 @@
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0</v>
+        <v>9666785.220264766</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>22002.48933761242</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>22002.48933761242</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0</v>
+        <v>-22002.48933761242</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2008,40 +2010,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>0.28330096818</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>51670578.4489233</v>
+        <v>-10156909.80992987</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>57072716.55221563</v>
+        <v>7104351.295236039</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>98429.56828483056</v>
+        <v>16170.15482007395</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>98429.56828483056</v>
+        <v>16170.15482007395</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>70387.07034453354</v>
+        <v>2116.028566055634</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,59 +2056,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>9193.636315</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>-3e-14</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>-3e-14</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>86939.86827108746</v>
+        <v>11365.95290210002</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>86939.86827108746</v>
+        <v>11365.95290210002</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>85795.55946190262</v>
+        <v>-11365.95290210002</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2119,59 +2121,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.154431</v>
+        <v>5000000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-10000122.481897</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>9666785.220264766</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>16671.66999247915</v>
+        <v>11352.96172699757</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>16671.66999247915</v>
+        <v>11352.96172699757</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-16671.66999247915</v>
+        <v>-11352.96172699714</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2184,59 +2186,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-10156909.80992987</v>
+        <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>7104351.295236039</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>12252.40838666043</v>
+        <v>11309.91129112959</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>12252.40838666043</v>
+        <v>11309.91129112959</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>6033.774999469159</v>
+        <v>-11309.91129112923</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2249,17 +2251,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2268,40 +2270,40 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>4997775.722557</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5000000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>9193.636315</v>
+        <v>2224.277443</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-3e-14</v>
+        <v>3.65681e-09</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-3e-14</v>
+        <v>3.65681e-09</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>4819813.116676098</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>8612.180786741585</v>
+        <v>10970.33649683651</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>8612.180786741585</v>
+        <v>10970.33649683651</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-8612.180786741585</v>
+        <v>-10970.33649683286</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2314,59 +2316,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5000000</v>
+        <v>977119.890305955</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5000000</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>-273029.0857638157</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>9546.424990308558</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>9546.424990308558</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>2903718.839188301</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>8602.337146742522</v>
+        <v>6609.130268533579</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>8602.337146742522</v>
+        <v>6609.130268533579</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-8602.337146742098</v>
+        <v>2937.294721774979</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2379,59 +2381,59 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>427.8972157084487</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>566848.624341</v>
+        <v>-203.1796532231052</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4497.433544807889</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4497.433544807889</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>1097625.680429284</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>8569.717080494091</v>
+        <v>2498.296670511259</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>8569.717080494091</v>
+        <v>2498.296670511259</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-8569.717080493736</v>
+        <v>1999.13687429663</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2444,77 +2446,77 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5000000</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2224.277443</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>4819813.116676098</v>
+        <v>979461.8988048178</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>8312.415335162012</v>
+        <v>2229.345071190106</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>8312.415335162012</v>
+        <v>1988.194472337904</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-8312.415335158355</v>
+        <v>-2229.345071190106</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>0</v>
+        <v>241.1505988522019</v>
       </c>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2524,44 +2526,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>977119.890305955</v>
+        <v>37220.756204</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>9229822.108306</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-273029.0857638157</v>
+        <v>9192601.352102</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>125.378836</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>125.378836</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>2903718.839188301</v>
+        <v>343636.6219795333</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>5007.853297123951</v>
+        <v>782.1484535797669</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>5007.853297123951</v>
+        <v>782.1484535797669</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>4538.571693184606</v>
+        <v>-656.7696175797669</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2574,59 +2576,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>427.8972157084487</v>
+        <v>133501.211399</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>1.545609</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-203.1796532231052</v>
+        <v>-133499.66579</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>-133499.66579</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>-133499.66579</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>1097625.680429284</v>
+        <v>133501.211399</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1893.002968662855</v>
+        <v>303.8609955052241</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1893.002968662855</v>
+        <v>303.8609955052241</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>2604.430576145034</v>
+        <v>-133803.5267855052</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2639,124 +2641,124 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2946.286265177527</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
+        <v>9.069536521e-09</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0</v>
+        <v>9.069536521e-09</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>979461.8988048178</v>
+        <v>3222.097566494505</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>1689.21365014394</v>
+        <v>7.33378943838793</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1448.063051291738</v>
+        <v>7.33378943838793</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-1689.21365014394</v>
+        <v>-7.333789429318393</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>241.1505988522019</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>504861.558051</v>
+        <v>10.263802</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>2500.221225</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>561698.317082</v>
+        <v>2489.957423</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-2803.258145600874</v>
+        <v>4.63071e-09</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-2803.258145600874</v>
+        <v>4.63071e-09</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>504861.558051</v>
+        <v>1260.904571864759</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>870.7015927146664</v>
+        <v>2.86993439556747</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>870.7015927146664</v>
+        <v>2.86993439556747</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-3673.959738315541</v>
+        <v>-2.86993439093676</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2769,12 +2771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2784,44 +2786,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>37220.756204</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>9229822.108306</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>9192601.352102</v>
+        <v>98.58562175646877</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>125.378836</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>125.378836</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>343636.6219795333</v>
+        <v>380.1986824877172</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>592.6475274285834</v>
+        <v>0.8653670550240247</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>592.6475274285834</v>
+        <v>0.8653670550240247</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-467.2686914285835</v>
+        <v>13.26371918238261</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2834,59 +2836,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>133501.211399</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.545609</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-133499.66579</v>
+        <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>133501.211399</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>230.2407769828742</v>
+        <v>0.6461761639018665</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>230.2407769828742</v>
+        <v>0.6461761639018665</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-133729.9065669829</v>
+        <v>-0.6461761639018665</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2899,12 +2901,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2914,44 +2916,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>3222.097566494505</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>5.556940191404734</v>
+        <v>0.2257198154885884</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>5.556940191404734</v>
+        <v>0.2257198154885884</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-5.556940182335198</v>
+        <v>0.1056602316384515</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2964,59 +2966,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>10.263802</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2500.221225</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>2489.957423</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>1260.904571864759</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>2.174599355954421</v>
+        <v>0.04986143167633277</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>2.174599355954421</v>
+        <v>0.04986143167633277</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-2.174599351323711</v>
+        <v>-0.04985557397665726</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3029,12 +3031,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3044,44 +3046,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>0.05756</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>0.057783</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>98.58562175646877</v>
+        <v>0.000223</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>0.000223</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>0.000223</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>380.1986824877172</v>
+        <v>0.05756</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.6557037134458001</v>
+        <v>0.000131011836656725</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.6557037134458001</v>
+        <v>0.000131011836656725</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>13.47338252396084</v>
+        <v>9.1988163343275e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3094,59 +3096,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.006327</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.006346</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0.006327</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.489618951577551</v>
+        <v>1.440083201054724e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.489618951577551</v>
+        <v>1.440083201054724e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.489618951577551</v>
+        <v>4.59916798945276e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3159,12 +3161,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3174,44 +3176,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.1710318417542014</v>
+        <v>1.306744433480383e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.1710318417542014</v>
+        <v>1.306744433480383e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1603482053728386</v>
+        <v>-9.960992208718827e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3224,59 +3226,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>0.001696</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>0.0017</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>0.001696</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.03778087658651134</v>
+        <v>3.860251476195372e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0.03778087658651134</v>
+        <v>3.860251476195372e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-0.03777501888683583</v>
+        <v>1.397485238046279e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3289,12 +3291,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3304,44 +3306,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.05756</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.057783</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.000223</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.000223</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.000223</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.05756</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>9.926995406450302e-05</v>
+        <v>2.822682956976316e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>9.926995406450302e-05</v>
+        <v>2.822682956976316e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.000123730045935497</v>
+        <v>-2.822682956976316e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3354,17 +3356,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3373,40 +3375,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.006327</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.006327</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.091176162901513e-05</v>
+        <v>1.18392754301228e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.091176162901513e-05</v>
+        <v>1.18392754301228e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>8.088238370984875e-06</v>
+        <v>-3.754732873172804e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3419,12 +3421,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3434,44 +3436,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>9.901430526886969e-06</v>
+        <v>1.704707898561497e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>9.901430526886969e-06</v>
+        <v>1.704707898561497e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-6.794978400801969e-06</v>
+        <v>-1.704707898561497e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3484,59 +3486,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.001696</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>4e-06</v>
+        <v>-1.30647e-08</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>4e-06</v>
+        <v>-1.30647e-08</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.001696</v>
+        <v>1.885188333333333e-08</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>2.924979883485009e-06</v>
+        <v>4.290861466188852e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>2.924979883485009e-06</v>
+        <v>4.290861466188852e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>1.075020116514991e-06</v>
+        <v>-1.310760861466189e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3549,12 +3551,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3564,14 +3566,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3589,19 +3591,19 @@
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>2.138796116658449e-06</v>
+        <v>0</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>2.138796116658449e-06</v>
+        <v>0</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-2.138796116658449e-06</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3614,12 +3616,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3629,44 +3631,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>0</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>8.970825523076592e-07</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>8.970825523076592e-07</v>
+        <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-8.862829661265914e-08</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3679,12 +3681,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3694,14 +3696,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -3719,19 +3721,19 @@
         <v>0</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>1.291686912435241e-07</v>
+        <v>0</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1.291686912435241e-07</v>
+        <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>-1.291686912435241e-07</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3739,17 +3741,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3759,7 +3765,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3772,31 +3778,31 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>1.885188333333333e-08</v>
+        <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>3.251260584658391e-11</v>
+        <v>0</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>3.251260584658391e-11</v>
+        <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>-1.309721260584658e-08</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3809,12 +3815,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3824,7 +3830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3837,22 +3843,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>48.90651074914867</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3861,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>-2.1369574e-07</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3869,34 +3875,38 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3914,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3929,32 +3939,36 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3982,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -3999,38 +4013,34 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4048,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4063,27 +4073,31 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4092,28 +4106,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>89900000</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4125,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>89900000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4142,17 +4156,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4161,10 +4175,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4182,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4197,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4211,50 +4225,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>116552055.190546</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>0</v>
@@ -4263,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0</v>
+        <v>-1302075.635868251</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4271,52 +4285,56 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>90000000</v>
+        <v>867900893.337617</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90000000</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>266802337.679219</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>90000000</v>
+        <v>867900893.337617</v>
       </c>
       <c r="M55" s="7" t="n">
         <v>0</v>
@@ -4328,64 +4346,64 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0</v>
+        <v>-2183895.668922679</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>89900000</v>
+        <v>504861.558051</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>89900000</v>
+        <v>1066559.875133</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>561698.317082</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>89900000</v>
+        <v>504861.558051</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -4397,64 +4415,64 @@
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>-2803.258145600874</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>89900000</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>89900000</v>
+        <v>37138817.432463</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>-36481150.80976</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>89900000</v>
+        <v>73619968.24222299</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -4466,17 +4484,17 @@
         <v>0</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>-175138.7076262338</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4603,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="5">
@@ -4605,7 +4623,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9193831.918668702</v>
+        <v>8969960.81400051</v>
       </c>
     </row>
     <row r="8">
@@ -4632,7 +4650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9078029.245937703</v>
+        <v>8854158.141269511</v>
       </c>
     </row>
     <row r="12">
@@ -4642,7 +4660,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2464412.765539723</v>
+        <v>-2688283.870207915</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4937,4 +4955,1620 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3370615309.279832</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>109055951.174984</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>83934283.91579673</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>81025902.18910897</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>130060790.0037368</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2631568381.996205</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>287033.1167687731</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>367643.1987365804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3436332710.023856</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>109133547.016997</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>81070524.8666583</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>75798768.87500143</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>123404206.9728645</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2711955662.292335</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>295801.2003837845</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>374811.1942523158</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3438806780.096234</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>109105650.4924593</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>76123440.04999478</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>75714944.50432792</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>123411196.5267537</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2719481548.522698</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>296622.0715402885</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>375081.04855245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>3443341379.37429</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>109123776.7824347</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>83542493.66401881</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>75690258.91133398</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>123405060.7543267</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2716609789.262176</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>296308.840078474</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>375575.65100055</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3451767983.804127</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>109127522.7862754</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>86558535.6429214</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>74444392.75988562</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>123403918.716754</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2723263613.898291</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>297034.5928412763</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>376494.7662132959</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3445796329.989512</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>109241926.6840944</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>55515650.13090748</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>74366553.28453328</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>112927513.3486385</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>2758774686.541338</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>300907.8928589656</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>375843.4198837078</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3457497551.030852</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>109305198.8012233</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>79109652.47887604</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>77054699.32011929</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>111032090.9637735</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2746025909.46686</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>299517.3452130397</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>377119.7074270885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3433737829.859045</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>109289928.5655661</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>56675900.95969198</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>74503713.8442512</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>106296252.8520661</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2752002033.63747</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>300169.1791378667</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>374528.1628302776</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3433364995.278069</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>109349782.7302168</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>54193645.98368105</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>78737127.87731043</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>106289452.9998598</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2749824985.687001</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>299931.721938254</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>374487.4966357189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3426936270.51389</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>109304061.5112718</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>51076302.50534543</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>75242537.44162388</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>106318077.1275745</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2750025291.928074</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>299953.5699453501</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>373786.2961962642</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3419054271.885073</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>109337373.1213049</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>51145031.32584467</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>73579380.95193422</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>106356377.8226287</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2743666108.663361</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>299259.9546074161</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>372926.5827841884</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3487131871.331304</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>109342328.3371183</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>51970946.78532917</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>71375240.03334759</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>106336984.9487036</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>2813136371.226805</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>306837.2861040062</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>380352.012305562</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3309862747.427698</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>109046834.1026236</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>50529324.09846896</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>69510472.6803965</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>106485554.4875584</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2639320562.05865</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>287878.6704774662</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>361016.7332039318</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>3310897469.321378</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>109458620.2372267</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>49882975.1971824</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>67540680.80231147</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>106432974.8514239</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2642612218.233233</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>288237.7013647446</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>361129.5934480979</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3322146141.580943</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>109518837.8396468</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>51274439.44802884</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>66491002.67769836</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>106442587.2808068</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2653449274.334762</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>289419.731826389</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>362356.5201281199</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3319843562.749172</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>109539351.8666015</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>52169788.46302108</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>67286649.27408095</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>106455238.2665053</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2649422534.878963</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>288980.5231839987</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>362105.3708958937</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3316623360.866395</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>109507779.6615873</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>50904742.8989519</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>66799476.11261413</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>106530285.11483</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>2647911077.078412</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>288815.6639136393</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>361754.1337441778</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>3341770538.551773</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>109623263.8502044</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>50485214.99143847</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>68028126.6911139</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>106209842.7768683</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>2672454090.242148</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>291492.64453534</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>364497.0124162101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>3387602107.560916</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>109342580.9053197</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>50143398.95539194</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>35619205.44664249</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>134869772.9750939</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>2722657149.278468</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>296968.4439122846</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>369496.0001640103</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>3522327931.244609</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>108244438.4938705</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>50106958.71182571</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>30889433.30164777</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>166906447.5117323</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2831210653.225533</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>308808.702667203</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>384190.9529327605</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3691758011.203047</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>108452809.4223091</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>50725251.6702591</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>54316080.27749412</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>174905990.8713613</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2968387878.961623</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>323771.0372666391</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>402671.2038194818</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>3793168501.903408</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>108810545.2478995</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>50363491.24509695</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>67704870.85992657</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>191459906.6813183</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>3039859687.869167</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>331566.6834722196</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>413732.3525313746</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>3815436515.573425</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>108790788.519045</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>50461527.69762992</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>51095777.99769017</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>150458263.8530219</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>3119660157.506038</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>340270.7618751178</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>416161.1920826031</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>3824208761.850309</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>108778836.5352057</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>51229919.97055995</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>56536069.61801664</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>148940725.8800582</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>3123753209.846468</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>340717.2034642511</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>417118.0074962338</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3798298269.581012</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>109012385.0330893</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>51077651.60920416</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>58449745.30648443</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>140084321.8061661</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>3104704165.826068</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>338639.4666613437</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>414291.8717955807</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3846549224.508112</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>109013131.1815182</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>51589907.91751318</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>58099362.01924805</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>154475144.3495293</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>3138401679.040303</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>342314.9562710425</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>419554.7492775214</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3780306162.322508</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>109024047.6455294</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>59429042.91027177</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>58855219.37465746</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>130752789.7099153</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>3087275062.682134</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>336738.4217057523</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>412329.4182796553</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3902178954.302975</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>108998604.7903199</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>67003312.22578653</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>69754438.78971349</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>135699774.815579</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>3185752823.681576</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>347479.6887256267</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>425622.4520350351</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3366262659.734222</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>108996254.8996352</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>84852106.09446886</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>78406141.98836392</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>131931405.5965129</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>2627106751.155241</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>286546.473208638</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>367168.4420957019</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3929445240.830592</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>109000464.1101925</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>86309975.97272643</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>70281418.59588619</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>129864360.3284257</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>3199019021.823361</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>348926.6730511566</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>428596.4683130372</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="n">
+        <v>9256950.219000347</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>11542442.01147743</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T14:51:02+00:00</t>
+          <t>2026-06-08T16:53:23+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4225,47 +4225,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>116552055.190546</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4277,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4287,276 +4279,159 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>266802337.679219</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>-2183895.668922679</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>-2183895.668922679</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>-2183895.668922679</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>504861.558051</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>1066559.875133</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>561698.317082</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>-2803.258145600874</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-2803.258145600874</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>504861.558051</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>-2803.258145600874</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S60</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>73619968.24222299</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>37138817.432463</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>-36481150.80976</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>-175138.7076262338</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-175138.7076262338</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>73619968.24222299</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>-175138.7076262338</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pricing cat.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Position SoM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Position EoM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSM_CURVE_DEDUCT</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Spark Savings V2 — spUSDC vault</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
-        </is>
+        <v>573332157.534611</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>867900893.337617</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>504861.558051</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>73619968.24222299</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>37138817.432463</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -662,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T16:53:23+00:00</t>
+          <t>2026-06-08T17:10:15+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4434,6 +4435,20 @@
         <v>37138817.432463</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>-3663913.270562765</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4539,14 +4554,14 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
         </is>
@@ -4866,7 +4881,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -6436,10 +6451,10 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="11" t="n">
         <v>9256950.219000347</v>
       </c>
-      <c r="O37" s="10" t="n">
+      <c r="O37" s="11" t="n">
         <v>11542442.01147743</v>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -662,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T14:51:02+00:00</t>
+          <t>2026-06-08T17:10:15+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4225,47 +4226,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>116552055.190546</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>456780102.344065</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4277,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-1302075.635868251</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4287,276 +4280,173 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>266802337.679219</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>-2183895.668922679</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>-2183895.668922679</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>-2183895.668922679</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>504861.558051</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>1066559.875133</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>561698.317082</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>-2803.258145600874</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-2803.258145600874</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>504861.558051</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>-2803.258145600874</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S60</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>73619968.24222299</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>37138817.432463</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>-36481150.80976</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>-175138.7076262338</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-175138.7076262338</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>73619968.24222299</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>-175138.7076262338</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pricing cat.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Position SoM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Position EoM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSM_CURVE_DEDUCT</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Spark Savings V2 — spUSDC vault</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
-        </is>
+        <v>573332157.534611</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>867900893.337617</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>504861.558051</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>73619968.24222299</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>37138817.432463</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>-3663913.270562765</v>
       </c>
     </row>
   </sheetData>
@@ -4664,14 +4554,14 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
         </is>
@@ -4991,7 +4881,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -6561,10 +6451,10 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="11" t="n">
         <v>9256950.219000347</v>
       </c>
-      <c r="O37" s="10" t="n">
+      <c r="O37" s="11" t="n">
         <v>11542442.01147743</v>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1458461.43909157</v>
+        <v>1458461.439092668</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>116038.2008889523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1458461.43909157</v>
+        <v>1574499.63998162</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>8969960.81400051</v>
+        <v>9492954.288835494</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="15">
@@ -580,13 +580,13 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>11542442.01147743</v>
+        <v>12065435.48631241</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — credited to prime_agent_revenue</t>
+          <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1458461.43909157</v>
+        <v>1458461.439092668</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-8854158.141269511</v>
+        <v>-9377151.616104495</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-7574617.675240585</v>
+        <v>-8097611.150074472</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T17:10:15+00:00</t>
+          <t>2026-06-09T14:50:03+00:00</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3102859.783190616</v>
+        <v>3282507.87432289</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3102859.783190616</v>
+        <v>3282507.87432289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3102859.783190616</v>
+        <v>-3282507.87432289</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1503933.92923752</v>
+        <v>1591008.073238561</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1503933.92923752</v>
+        <v>1591008.073238561</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1672441.07076247</v>
+        <v>1585366.926761428</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1090453.857729697</v>
+        <v>1153588.503732787</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1090453.857729697</v>
+        <v>1153588.503732787</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1090453.857729697</v>
+        <v>-1153588.503732787</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>672739.1842555213</v>
+        <v>711689.1590291519</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>672739.1842555213</v>
+        <v>711689.1590291519</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-95227.04681952125</v>
+        <v>-134177.0215931519</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>398517.9190202518</v>
+        <v>421591.1445078621</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>398517.9190202518</v>
+        <v>421591.1445078621</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>154594.120912086</v>
+        <v>131520.8954244758</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>363270.1901531557</v>
+        <v>384302.6572275028</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>363270.1901531557</v>
+        <v>384302.6572275028</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-363270.1901532957</v>
+        <v>-384302.6572276429</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>325250.5859292409</v>
+        <v>344081.8096984822</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>290067.8882897074</v>
+        <v>308899.1120589486</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-325250.5859292409</v>
+        <v>-344081.8096984822</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>231899.9788534417</v>
+        <v>245326.427821689</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>231899.9788534417</v>
+        <v>245326.427821689</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>82311.81991348779</v>
+        <v>68885.37094524053</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1388,13 +1388,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>227609.340718769</v>
+        <v>240787.3720966343</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>227609.340718769</v>
+        <v>240787.3720966343</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-218040.3292735575</v>
+        <v>-231218.3606514228</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>227606.2462275466</v>
+        <v>240784.0984418402</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>227606.2462275466</v>
+        <v>240784.0984418402</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-181320.7711845466</v>
+        <v>-194498.6233988403</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1518,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>231558.1123314957</v>
+        <v>244964.7680533893</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>206510.2280091212</v>
+        <v>219916.8837310147</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-231558.1123314957</v>
+        <v>-244964.7680533893</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>171948.8496785754</v>
+        <v>181904.2729898352</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>153348.9619322608</v>
+        <v>163304.3852435207</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-171948.8496785754</v>
+        <v>-181904.2729898352</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>145182.6562654815</v>
+        <v>153588.3815918085</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>145182.6562654815</v>
+        <v>153588.3815918085</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>59604.30871407653</v>
+        <v>51198.58338774954</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1695,31 +1695,31 @@
         <v>51670578.4489233</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>168816.6386304616</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>168816.6386304616</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57072716.55221563</v>
+        <v>57072716.55221559</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>129902.7348591807</v>
+        <v>137423.7896218669</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>129902.7348591807</v>
+        <v>137423.7896218669</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>38913.90377018342</v>
+        <v>31392.84900859464</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1732,12 +1732,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1747,66 +1747,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>121382.2876116389</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>121382.2876116389</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>51353.14012135115</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1816,52 +1812,56 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>114739.1668327748</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>114739.1668327748</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>57996.26090021532</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1973,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>22002.48933761242</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>22002.48933761242</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-22002.48933761242</v>
+        <v>-23276.3803561733</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>16170.15482007395</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>16170.15482007395</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>2116.028566055634</v>
+        <v>1179.81563678413</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11365.95290210002</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11365.95290210002</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11365.95290210002</v>
+        <v>-12024.01413768121</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11352.96172699757</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11352.96172699757</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11352.96172699714</v>
+        <v>-12010.27080490064</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11309.91129112959</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11309.91129112959</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11309.91129112923</v>
+        <v>-11964.72785271988</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>10970.33649683651</v>
+        <v>11605.49249757234</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>10970.33649683651</v>
+        <v>11605.49249757234</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-10970.33649683286</v>
+        <v>-11605.49249756869</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6609.130268533579</v>
+        <v>6991.78295661789</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6609.130268533579</v>
+        <v>6991.78295661789</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2937.294721774979</v>
+        <v>2554.642033690668</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2498.296670511259</v>
+        <v>2642.942016836885</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2498.296670511259</v>
+        <v>2642.942016836885</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1999.13687429663</v>
+        <v>1854.491527971004</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2229.345071190106</v>
+        <v>2358.418769165147</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1988.194472337904</v>
+        <v>2117.268170312945</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2229.345071190106</v>
+        <v>-2358.418769165147</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>782.1484535797669</v>
+        <v>827.4329609329093</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>782.1484535797669</v>
+        <v>827.4329609329093</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-656.7696175797669</v>
+        <v>-702.0541249329093</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>303.8609955052241</v>
+        <v>321.4538136234616</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>303.8609955052241</v>
+        <v>321.4538136234616</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133803.5267855052</v>
+        <v>-133821.1196036235</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.33378943838793</v>
+        <v>7.758398143077016</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.33378943838793</v>
+        <v>7.758398143077016</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.333789429318393</v>
+        <v>-7.758398134007479</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.86993439556747</v>
+        <v>3.036096669039071</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.86993439556747</v>
+        <v>3.036096669039071</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.86993439093676</v>
+        <v>-3.036096664408361</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.8653670550240247</v>
+        <v>0.9154697185107922</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.8653670550240247</v>
+        <v>0.9154697185107922</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.26371918238261</v>
+        <v>13.21361651889585</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6461761639018665</v>
+        <v>0.6835882039202453</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6461761639018665</v>
+        <v>0.6835882039202453</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6461761639018665</v>
+        <v>-0.6835882039202453</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2257198154885884</v>
+        <v>0.2387884479169468</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2257198154885884</v>
+        <v>0.2387884479169468</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1056602316384515</v>
+        <v>0.09259159921009311</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.04986143167633277</v>
+        <v>0.05274828820472047</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.04986143167633277</v>
+        <v>0.05274828820472047</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.04985557397665726</v>
+        <v>-0.05274243050504496</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.000131011836656725</v>
+        <v>0.0001385971057361135</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.000131011836656725</v>
+        <v>0.0001385971057361135</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>9.1988163343275e-05</v>
+        <v>8.440289426388646e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.440083201054724e-05</v>
+        <v>1.523460542029865e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.440083201054724e-05</v>
+        <v>1.523460542029865e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>4.59916798945276e-06</v>
+        <v>3.76539457970135e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.306744433480383e-05</v>
+        <v>1.382401781693225e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.306744433480383e-05</v>
+        <v>1.382401781693225e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-9.960992208718827e-06</v>
+        <v>-1.071756569084725e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.860251476195372e-06</v>
+        <v>4.083750718006403e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.860251476195372e-06</v>
+        <v>4.083750718006403e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>1.397485238046279e-07</v>
+        <v>-8.37507180064029e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.822682956976316e-06</v>
+        <v>2.986109486218629e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.822682956976316e-06</v>
+        <v>2.986109486218629e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.822682956976316e-06</v>
+        <v>-2.986109486218629e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.18392754301228e-06</v>
+        <v>1.252474089747426e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.18392754301228e-06</v>
+        <v>1.252474089747426e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.754732873172804e-07</v>
+        <v>-4.440198340524262e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.704707898561497e-07</v>
+        <v>1.803406370717327e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.704707898561497e-07</v>
+        <v>1.803406370717327e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.704707898561497e-07</v>
+        <v>-1.803406370717327e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3533,13 +3533,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.290861466188852e-11</v>
+        <v>4.53929198692647e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.290861466188852e-11</v>
+        <v>4.53929198692647e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.310760861466189e-08</v>
+        <v>-1.311009291986926e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="5">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8969960.81400051</v>
+        <v>9492954.288835494</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11542442.01147743</v>
+        <v>12065435.48631241</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="12">
@@ -4563,7 +4563,7 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -4883,7 +4883,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3370615309.279832</v>
+        <v>3523339473.817923</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>334970000</v>
@@ -4988,7 +4988,7 @@
         <v>130060790.0037368</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2631568381.996205</v>
+        <v>2784292546.534297</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.0375</v>
@@ -5006,10 +5006,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>287033.1167687731</v>
+        <v>303691.2029705925</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>367643.1987365804</v>
+        <v>384301.2849383999</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3436332710.023856</v>
+        <v>3592034560.890201</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>334970000</v>
@@ -5037,7 +5037,7 @@
         <v>123404206.9728645</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2711955662.292335</v>
+        <v>2867657513.15868</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.0375</v>
@@ -5055,10 +5055,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>295801.2003837845</v>
+        <v>312784.0718328374</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>374811.1942523158</v>
+        <v>391794.0657013687</v>
       </c>
     </row>
     <row r="8">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3438806780.096234</v>
+        <v>3594620732.240875</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>334970000</v>
@@ -5086,7 +5086,7 @@
         <v>123411196.5267537</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2719481548.522698</v>
+        <v>2875295500.667339</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.0375</v>
@@ -5104,10 +5104,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>296622.0715402885</v>
+        <v>313617.1702145669</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>375081.04855245</v>
+        <v>392076.1472267284</v>
       </c>
     </row>
     <row r="9">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3443341379.37429</v>
+        <v>3599360796.344403</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>334970000</v>
@@ -5135,7 +5135,7 @@
         <v>123405060.7543267</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2716609789.262176</v>
+        <v>2872629206.232289</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.0375</v>
@@ -5153,10 +5153,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>296308.840078474</v>
+        <v>313326.3494222396</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>375575.65100055</v>
+        <v>392593.1603443155</v>
       </c>
     </row>
     <row r="10">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3451767983.804127</v>
+        <v>3608169214.183174</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>334970000</v>
@@ -5184,7 +5184,7 @@
         <v>123403918.716754</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2723263613.898291</v>
+        <v>2879664844.277337</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.0375</v>
@@ -5202,10 +5202,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>297034.5928412763</v>
+        <v>314093.7477275024</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>376494.7662132959</v>
+        <v>393553.921099522</v>
       </c>
     </row>
     <row r="11">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3445796329.989512</v>
+        <v>3601926981.926327</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>334970000</v>
@@ -5233,7 +5233,7 @@
         <v>112927513.3486385</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2758774686.541338</v>
+        <v>2914905338.478153</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.0375</v>
@@ -5251,10 +5251,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>300907.8928589656</v>
+        <v>317937.5349367328</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>375843.4198837078</v>
+        <v>392873.0619614751</v>
       </c>
     </row>
     <row r="12">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3457497551.030852</v>
+        <v>3614158390.795003</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>334970000</v>
@@ -5282,7 +5282,7 @@
         <v>111032090.9637735</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2746025909.46686</v>
+        <v>2902686749.231011</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.0375</v>
@@ -5300,10 +5300,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>299517.3452130397</v>
+        <v>316604.8164795121</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>377119.7074270885</v>
+        <v>394207.178693561</v>
       </c>
     </row>
     <row r="13">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3433737829.859045</v>
+        <v>3589322105.485001</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>334970000</v>
@@ -5331,7 +5331,7 @@
         <v>106296252.8520661</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2752002033.63747</v>
+        <v>2907586309.263426</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.0375</v>
@@ -5349,10 +5349,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>300169.1791378667</v>
+        <v>317139.2263001047</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>374528.1628302776</v>
+        <v>391498.2099925156</v>
       </c>
     </row>
     <row r="14">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3433364995.278069</v>
+        <v>3588932377.593853</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>334970000</v>
@@ -5380,7 +5380,7 @@
         <v>106289452.9998598</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2749824985.687001</v>
+        <v>2905392368.002785</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.0375</v>
@@ -5398,10 +5398,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>299931.721938254</v>
+        <v>316899.9264960952</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>374487.4966357189</v>
+        <v>391455.7011935601</v>
       </c>
     </row>
     <row r="15">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3426936270.51389</v>
+        <v>3582212364.287801</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>334970000</v>
@@ -5429,7 +5429,7 @@
         <v>106318077.1275745</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2750025291.928074</v>
+        <v>2905301385.701985</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.0375</v>
@@ -5447,10 +5447,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>299953.5699453501</v>
+        <v>316890.0027815728</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>373786.2961962642</v>
+        <v>390722.7290324869</v>
       </c>
     </row>
     <row r="16">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3419054271.885073</v>
+        <v>3573973228.59497</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>334970000</v>
@@ -5478,7 +5478,7 @@
         <v>106356377.8226287</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2743666108.663361</v>
+        <v>2898585065.373258</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.0375</v>
@@ -5496,10 +5496,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>299259.9546074161</v>
+        <v>316157.4334246975</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>372926.5827841884</v>
+        <v>389824.0616014699</v>
       </c>
     </row>
     <row r="17">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3487131871.331304</v>
+        <v>3645135456.082426</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>334970000</v>
@@ -5527,7 +5527,7 @@
         <v>106336984.9487036</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2813136371.226805</v>
+        <v>2971139955.977927</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.0375</v>
@@ -5545,10 +5545,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>306837.2861040062</v>
+        <v>324071.2146243629</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>380352.012305562</v>
+        <v>397585.9408259187</v>
       </c>
     </row>
     <row r="18">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3309862747.427698</v>
+        <v>3459834184.822211</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>334970000</v>
@@ -5576,7 +5576,7 @@
         <v>106485554.4875584</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2639320562.05865</v>
+        <v>2789291999.453163</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.0375</v>
@@ -5594,10 +5594,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>287878.6704774662</v>
+        <v>304236.508410215</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>361016.7332039318</v>
+        <v>377374.5711366806</v>
       </c>
     </row>
     <row r="19">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3310897469.321378</v>
+        <v>3460915790.451423</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>334970000</v>
@@ -5625,7 +5625,7 @@
         <v>106432974.8514239</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2642612218.233233</v>
+        <v>2792630539.363278</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.0375</v>
@@ -5643,10 +5643,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>288237.7013647446</v>
+        <v>304600.6530482238</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>361129.5934480979</v>
+        <v>377492.5451315772</v>
       </c>
     </row>
     <row r="20">
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3322146141.580943</v>
+        <v>3472674145.340232</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>334970000</v>
@@ -5674,7 +5674,7 @@
         <v>106442587.2808068</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2653449274.334762</v>
+        <v>2803977278.094051</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.0375</v>
@@ -5692,10 +5692,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>289419.731826389</v>
+        <v>305838.276134645</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>362356.5201281199</v>
+        <v>378775.064436376</v>
       </c>
     </row>
     <row r="21">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3319843562.749172</v>
+        <v>3470267235.578913</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>334970000</v>
@@ -5723,7 +5723,7 @@
         <v>106455238.2665053</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2649422534.878963</v>
+        <v>2799846207.708704</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.0375</v>
@@ -5741,10 +5741,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>288980.5231839987</v>
+        <v>305387.6878024514</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>362105.3708958937</v>
+        <v>378512.5355143464</v>
       </c>
     </row>
     <row r="22">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3316623360.866395</v>
+        <v>3466901124.834678</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>334970000</v>
@@ -5772,7 +5772,7 @@
         <v>106530285.11483</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2647911077.078412</v>
+        <v>2798188841.046695</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.0375</v>
@@ -5790,10 +5790,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>288815.6639136393</v>
+        <v>305206.9138115948</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>361754.1337441778</v>
+        <v>378145.3836421333</v>
       </c>
     </row>
     <row r="23">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3341770538.551773</v>
+        <v>3493187732.965268</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>334970000</v>
@@ -5821,7 +5821,7 @@
         <v>106209842.7768683</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2672454090.242148</v>
+        <v>2823871284.655643</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.0375</v>
@@ -5839,10 +5839,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>291492.64453534</v>
+        <v>308008.1755556361</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>364497.0124162101</v>
+        <v>381012.5434365062</v>
       </c>
     </row>
     <row r="24">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3387602107.560916</v>
+        <v>3541095951.916372</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>334970000</v>
@@ -5870,7 +5870,7 @@
         <v>134869772.9750939</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2722657149.278468</v>
+        <v>2876150993.633924</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.0375</v>
@@ -5888,10 +5888,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>296968.4439122846</v>
+        <v>313710.4814179742</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>369496.0001640103</v>
+        <v>386238.0376697</v>
       </c>
     </row>
     <row r="25">
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3522327931.244609</v>
+        <v>3681926266.019708</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>334970000</v>
@@ -5919,7 +5919,7 @@
         <v>166906447.5117323</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2831210653.225533</v>
+        <v>2990808988.000631</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.0375</v>
@@ -5937,10 +5937,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>308808.702667203</v>
+        <v>326216.5753924609</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>384190.9529327605</v>
+        <v>401598.8256580184</v>
       </c>
     </row>
     <row r="26">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3691758011.203047</v>
+        <v>3859033302.567655</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>334970000</v>
@@ -5968,7 +5968,7 @@
         <v>174905990.8713613</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2968387878.961623</v>
+        <v>3135663170.326231</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.0375</v>
@@ -5986,10 +5986,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>323771.0372666391</v>
+        <v>342016.2588490502</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>402671.2038194818</v>
+        <v>420916.4254018929</v>
       </c>
     </row>
     <row r="27">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3793168501.903408</v>
+        <v>3965038750.285202</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>334970000</v>
@@ -6017,7 +6017,7 @@
         <v>191459906.6813183</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3039859687.869167</v>
+        <v>3211729936.25096</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.0375</v>
@@ -6035,10 +6035,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>331566.6834722196</v>
+        <v>350313.0909037557</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>413732.3525313746</v>
+        <v>432478.7599629108</v>
       </c>
     </row>
     <row r="28">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3815436515.573425</v>
+        <v>3988315738.125102</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>334970000</v>
@@ -6066,7 +6066,7 @@
         <v>150458263.8530219</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3119660157.506038</v>
+        <v>3292539380.057715</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.0375</v>
@@ -6084,10 +6084,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>340270.7618751178</v>
+        <v>359127.2211687687</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>416161.1920826031</v>
+        <v>435017.6513762539</v>
       </c>
     </row>
     <row r="29">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3824208761.850309</v>
+        <v>3997485459.005531</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>334970000</v>
@@ -6115,7 +6115,7 @@
         <v>148940725.8800582</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3123753209.846468</v>
+        <v>3297029907.00169</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.0375</v>
@@ -6133,10 +6133,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>340717.2034642511</v>
+        <v>359617.0165141915</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>417118.0074962338</v>
+        <v>436017.8205461741</v>
       </c>
     </row>
     <row r="30">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3798298269.581012</v>
+        <v>3970400950.148312</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>334970000</v>
@@ -6164,7 +6164,7 @@
         <v>140084321.8061661</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3104704165.826068</v>
+        <v>3276806846.393368</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.0375</v>
@@ -6182,10 +6182,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>338639.4666613437</v>
+        <v>357411.2261738289</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>414291.8717955807</v>
+        <v>433063.6313080659</v>
       </c>
     </row>
     <row r="31">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3846549224.508112</v>
+        <v>4020838178.53092</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>334970000</v>
@@ -6213,7 +6213,7 @@
         <v>154475144.3495293</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3138401679.040303</v>
+        <v>3312690633.063111</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.0375</v>
@@ -6231,10 +6231,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>342314.9562710425</v>
+        <v>361325.179236857</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>419554.7492775214</v>
+        <v>438564.972243336</v>
       </c>
     </row>
     <row r="32">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3780306162.322508</v>
+        <v>3951593612.049976</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>334970000</v>
@@ -6262,7 +6262,7 @@
         <v>130752789.7099153</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3087275062.682134</v>
+        <v>3258562512.409602</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.0375</v>
@@ -6280,10 +6280,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>336738.4217057523</v>
+        <v>355421.2615266787</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>412329.4182796553</v>
+        <v>431012.2581005817</v>
       </c>
     </row>
     <row r="33">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3902178954.302975</v>
+        <v>4078988517.540073</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>334970000</v>
@@ -6311,7 +6311,7 @@
         <v>135699774.815579</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3185752823.681576</v>
+        <v>3362562386.918674</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.0375</v>
@@ -6329,10 +6329,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>347479.6887256267</v>
+        <v>366764.8421564384</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>425622.4520350351</v>
+        <v>444907.6054658468</v>
       </c>
     </row>
     <row r="34">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3366262659.734222</v>
+        <v>3518789603.674771</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>334970000</v>
@@ -6360,7 +6360,7 @@
         <v>131931405.5965129</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2627106751.155241</v>
+        <v>2779633695.09579</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.0375</v>
@@ -6378,10 +6378,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>286546.473208638</v>
+        <v>303183.047963827</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>367168.4420957019</v>
+        <v>383805.0168508909</v>
       </c>
     </row>
     <row r="35">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3929445240.830592</v>
+        <v>4107490252.330956</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>334970000</v>
@@ -6409,7 +6409,7 @@
         <v>129864360.3284257</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3199019021.823361</v>
+        <v>3377064033.323725</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.0375</v>
@@ -6427,10 +6427,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>348926.6730511566</v>
+        <v>368346.5805579171</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>428596.4683130372</v>
+        <v>448016.3758197976</v>
       </c>
     </row>
     <row r="37">
@@ -6452,10 +6452,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="11" t="n">
-        <v>9256950.219000347</v>
+        <v>9779943.693835331</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>11542442.01147743</v>
+        <v>12065435.48631241</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T14:50:03+00:00</t>
+          <t>2026-06-09T15:30:14+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T15:30:14+00:00</t>
+          <t>2026-06-09T15:40:08+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T15:40:08+00:00</t>
+          <t>2026-06-09T15:57:05+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>116038.2008889523</v>
+        <v>116261.8233510476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1574499.63998162</v>
+        <v>1574723.262443715</v>
       </c>
     </row>
     <row r="8">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T15:57:05+00:00</t>
+          <t>2026-06-09T16:19:53+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T16:19:53+00:00</t>
+          <t>2026-06-09T16:37:07+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T16:37:07+00:00</t>
+          <t>2026-06-09T17:00:15+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1458461.43909157</v>
+        <v>1458461.439092668</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>116261.8233510476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1458461.43909157</v>
+        <v>1574723.262443715</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>8969960.81400051</v>
+        <v>9492954.288835494</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="15">
@@ -580,13 +580,13 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>11542442.01147743</v>
+        <v>12065435.48631241</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — credited to prime_agent_revenue</t>
+          <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1458461.43909157</v>
+        <v>1458461.439092668</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-8854158.141269511</v>
+        <v>-9377151.616104495</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-7574617.675240585</v>
+        <v>-8097611.150074472</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T17:10:15+00:00</t>
+          <t>2026-06-09T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3102859.783190616</v>
+        <v>3282507.87432289</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3102859.783190616</v>
+        <v>3282507.87432289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3102859.783190616</v>
+        <v>-3282507.87432289</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1503933.92923752</v>
+        <v>1591008.073238561</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1503933.92923752</v>
+        <v>1591008.073238561</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1672441.07076247</v>
+        <v>1585366.926761428</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1090453.857729697</v>
+        <v>1153588.503732787</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1090453.857729697</v>
+        <v>1153588.503732787</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1090453.857729697</v>
+        <v>-1153588.503732787</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>672739.1842555213</v>
+        <v>711689.1590291519</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>672739.1842555213</v>
+        <v>711689.1590291519</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-95227.04681952125</v>
+        <v>-134177.0215931519</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>398517.9190202518</v>
+        <v>421591.1445078621</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>398517.9190202518</v>
+        <v>421591.1445078621</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>154594.120912086</v>
+        <v>131520.8954244758</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>363270.1901531557</v>
+        <v>384302.6572275028</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>363270.1901531557</v>
+        <v>384302.6572275028</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-363270.1901532957</v>
+        <v>-384302.6572276429</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>325250.5859292409</v>
+        <v>344081.8096984822</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>290067.8882897074</v>
+        <v>308899.1120589486</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-325250.5859292409</v>
+        <v>-344081.8096984822</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>231899.9788534417</v>
+        <v>245326.427821689</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>231899.9788534417</v>
+        <v>245326.427821689</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>82311.81991348779</v>
+        <v>68885.37094524053</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1388,13 +1388,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>227609.340718769</v>
+        <v>240787.3720966343</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>227609.340718769</v>
+        <v>240787.3720966343</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-218040.3292735575</v>
+        <v>-231218.3606514228</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>227606.2462275466</v>
+        <v>240784.0984418402</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>227606.2462275466</v>
+        <v>240784.0984418402</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-181320.7711845466</v>
+        <v>-194498.6233988403</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1518,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>231558.1123314957</v>
+        <v>244964.7680533893</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>206510.2280091212</v>
+        <v>219916.8837310147</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-231558.1123314957</v>
+        <v>-244964.7680533893</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>171948.8496785754</v>
+        <v>181904.2729898352</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>153348.9619322608</v>
+        <v>163304.3852435207</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-171948.8496785754</v>
+        <v>-181904.2729898352</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>145182.6562654815</v>
+        <v>153588.3815918085</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>145182.6562654815</v>
+        <v>153588.3815918085</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>59604.30871407653</v>
+        <v>51198.58338774954</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1695,31 +1695,31 @@
         <v>51670578.4489233</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>168816.6386304616</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>168816.6386293641</v>
+        <v>168816.6386304616</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57072716.55221563</v>
+        <v>57072716.55221559</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>129902.7348591807</v>
+        <v>137423.7896218669</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>129902.7348591807</v>
+        <v>137423.7896218669</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>38913.90377018342</v>
+        <v>31392.84900859464</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1732,12 +1732,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1747,66 +1747,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>172735.4277329901</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>121382.2876116389</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>121382.2876116389</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>51353.14012135115</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1816,52 +1812,56 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>114739.1668327748</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>114739.1668327748</v>
+        <v>115802.6727309982</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>57996.26090021532</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1973,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>22002.48933761242</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>22002.48933761242</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-22002.48933761242</v>
+        <v>-23276.3803561733</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>16170.15482007395</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>16170.15482007395</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>2116.028566055634</v>
+        <v>1179.81563678413</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11365.95290210002</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11365.95290210002</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11365.95290210002</v>
+        <v>-12024.01413768121</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11352.96172699757</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11352.96172699757</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11352.96172699714</v>
+        <v>-12010.27080490064</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11309.91129112959</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11309.91129112959</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11309.91129112923</v>
+        <v>-11964.72785271988</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>10970.33649683651</v>
+        <v>11605.49249757234</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>10970.33649683651</v>
+        <v>11605.49249757234</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-10970.33649683286</v>
+        <v>-11605.49249756869</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6609.130268533579</v>
+        <v>6991.78295661789</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6609.130268533579</v>
+        <v>6991.78295661789</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2937.294721774979</v>
+        <v>2554.642033690668</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2498.296670511259</v>
+        <v>2642.942016836885</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2498.296670511259</v>
+        <v>2642.942016836885</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1999.13687429663</v>
+        <v>1854.491527971004</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2229.345071190106</v>
+        <v>2358.418769165147</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1988.194472337904</v>
+        <v>2117.268170312945</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2229.345071190106</v>
+        <v>-2358.418769165147</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>782.1484535797669</v>
+        <v>827.4329609329093</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>782.1484535797669</v>
+        <v>827.4329609329093</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-656.7696175797669</v>
+        <v>-702.0541249329093</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>303.8609955052241</v>
+        <v>321.4538136234616</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>303.8609955052241</v>
+        <v>321.4538136234616</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133803.5267855052</v>
+        <v>-133821.1196036235</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.33378943838793</v>
+        <v>7.758398143077016</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.33378943838793</v>
+        <v>7.758398143077016</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.333789429318393</v>
+        <v>-7.758398134007479</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.86993439556747</v>
+        <v>3.036096669039071</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.86993439556747</v>
+        <v>3.036096669039071</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.86993439093676</v>
+        <v>-3.036096664408361</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.8653670550240247</v>
+        <v>0.9154697185107922</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.8653670550240247</v>
+        <v>0.9154697185107922</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.26371918238261</v>
+        <v>13.21361651889585</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6461761639018665</v>
+        <v>0.6835882039202453</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6461761639018665</v>
+        <v>0.6835882039202453</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6461761639018665</v>
+        <v>-0.6835882039202453</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2257198154885884</v>
+        <v>0.2387884479169468</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2257198154885884</v>
+        <v>0.2387884479169468</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1056602316384515</v>
+        <v>0.09259159921009311</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.04986143167633277</v>
+        <v>0.05274828820472047</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.04986143167633277</v>
+        <v>0.05274828820472047</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.04985557397665726</v>
+        <v>-0.05274243050504496</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.000131011836656725</v>
+        <v>0.0001385971057361135</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.000131011836656725</v>
+        <v>0.0001385971057361135</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>9.1988163343275e-05</v>
+        <v>8.440289426388646e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.440083201054724e-05</v>
+        <v>1.523460542029865e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.440083201054724e-05</v>
+        <v>1.523460542029865e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>4.59916798945276e-06</v>
+        <v>3.76539457970135e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.306744433480383e-05</v>
+        <v>1.382401781693225e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.306744433480383e-05</v>
+        <v>1.382401781693225e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-9.960992208718827e-06</v>
+        <v>-1.071756569084725e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.860251476195372e-06</v>
+        <v>4.083750718006403e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.860251476195372e-06</v>
+        <v>4.083750718006403e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>1.397485238046279e-07</v>
+        <v>-8.37507180064029e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.822682956976316e-06</v>
+        <v>2.986109486218629e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.822682956976316e-06</v>
+        <v>2.986109486218629e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.822682956976316e-06</v>
+        <v>-2.986109486218629e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.18392754301228e-06</v>
+        <v>1.252474089747426e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.18392754301228e-06</v>
+        <v>1.252474089747426e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.754732873172804e-07</v>
+        <v>-4.440198340524262e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.704707898561497e-07</v>
+        <v>1.803406370717327e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.704707898561497e-07</v>
+        <v>1.803406370717327e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.704707898561497e-07</v>
+        <v>-1.803406370717327e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3533,13 +3533,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.290861466188852e-11</v>
+        <v>4.53929198692647e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.290861466188852e-11</v>
+        <v>4.53929198692647e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.310760861466189e-08</v>
+        <v>-1.311009291986926e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="5">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8969960.81400051</v>
+        <v>9492954.288835494</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11542442.01147743</v>
+        <v>12065435.48631241</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8854158.141269511</v>
+        <v>9377151.616104495</v>
       </c>
     </row>
     <row r="12">
@@ -4563,7 +4563,7 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -4883,7 +4883,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3370615309.279832</v>
+        <v>3523339473.817923</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>334970000</v>
@@ -4988,7 +4988,7 @@
         <v>130060790.0037368</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2631568381.996205</v>
+        <v>2784292546.534297</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.0375</v>
@@ -5006,10 +5006,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>287033.1167687731</v>
+        <v>303691.2029705925</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>367643.1987365804</v>
+        <v>384301.2849383999</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3436332710.023856</v>
+        <v>3592034560.890201</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>334970000</v>
@@ -5037,7 +5037,7 @@
         <v>123404206.9728645</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2711955662.292335</v>
+        <v>2867657513.15868</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.0375</v>
@@ -5055,10 +5055,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>295801.2003837845</v>
+        <v>312784.0718328374</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>374811.1942523158</v>
+        <v>391794.0657013687</v>
       </c>
     </row>
     <row r="8">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3438806780.096234</v>
+        <v>3594620732.240875</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>334970000</v>
@@ -5086,7 +5086,7 @@
         <v>123411196.5267537</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2719481548.522698</v>
+        <v>2875295500.667339</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.0375</v>
@@ -5104,10 +5104,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>296622.0715402885</v>
+        <v>313617.1702145669</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>375081.04855245</v>
+        <v>392076.1472267284</v>
       </c>
     </row>
     <row r="9">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3443341379.37429</v>
+        <v>3599360796.344403</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>334970000</v>
@@ -5135,7 +5135,7 @@
         <v>123405060.7543267</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2716609789.262176</v>
+        <v>2872629206.232289</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.0375</v>
@@ -5153,10 +5153,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>296308.840078474</v>
+        <v>313326.3494222396</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>375575.65100055</v>
+        <v>392593.1603443155</v>
       </c>
     </row>
     <row r="10">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3451767983.804127</v>
+        <v>3608169214.183174</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>334970000</v>
@@ -5184,7 +5184,7 @@
         <v>123403918.716754</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2723263613.898291</v>
+        <v>2879664844.277337</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.0375</v>
@@ -5202,10 +5202,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>297034.5928412763</v>
+        <v>314093.7477275024</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>376494.7662132959</v>
+        <v>393553.921099522</v>
       </c>
     </row>
     <row r="11">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3445796329.989512</v>
+        <v>3601926981.926327</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>334970000</v>
@@ -5233,7 +5233,7 @@
         <v>112927513.3486385</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2758774686.541338</v>
+        <v>2914905338.478153</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.0375</v>
@@ -5251,10 +5251,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>300907.8928589656</v>
+        <v>317937.5349367328</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>375843.4198837078</v>
+        <v>392873.0619614751</v>
       </c>
     </row>
     <row r="12">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3457497551.030852</v>
+        <v>3614158390.795003</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>334970000</v>
@@ -5282,7 +5282,7 @@
         <v>111032090.9637735</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2746025909.46686</v>
+        <v>2902686749.231011</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.0375</v>
@@ -5300,10 +5300,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>299517.3452130397</v>
+        <v>316604.8164795121</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>377119.7074270885</v>
+        <v>394207.178693561</v>
       </c>
     </row>
     <row r="13">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3433737829.859045</v>
+        <v>3589322105.485001</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>334970000</v>
@@ -5331,7 +5331,7 @@
         <v>106296252.8520661</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2752002033.63747</v>
+        <v>2907586309.263426</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.0375</v>
@@ -5349,10 +5349,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>300169.1791378667</v>
+        <v>317139.2263001047</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>374528.1628302776</v>
+        <v>391498.2099925156</v>
       </c>
     </row>
     <row r="14">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3433364995.278069</v>
+        <v>3588932377.593853</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>334970000</v>
@@ -5380,7 +5380,7 @@
         <v>106289452.9998598</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2749824985.687001</v>
+        <v>2905392368.002785</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.0375</v>
@@ -5398,10 +5398,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>299931.721938254</v>
+        <v>316899.9264960952</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>374487.4966357189</v>
+        <v>391455.7011935601</v>
       </c>
     </row>
     <row r="15">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3426936270.51389</v>
+        <v>3582212364.287801</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>334970000</v>
@@ -5429,7 +5429,7 @@
         <v>106318077.1275745</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2750025291.928074</v>
+        <v>2905301385.701985</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.0375</v>
@@ -5447,10 +5447,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>299953.5699453501</v>
+        <v>316890.0027815728</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>373786.2961962642</v>
+        <v>390722.7290324869</v>
       </c>
     </row>
     <row r="16">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3419054271.885073</v>
+        <v>3573973228.59497</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>334970000</v>
@@ -5478,7 +5478,7 @@
         <v>106356377.8226287</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2743666108.663361</v>
+        <v>2898585065.373258</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.0375</v>
@@ -5496,10 +5496,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>299259.9546074161</v>
+        <v>316157.4334246975</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>372926.5827841884</v>
+        <v>389824.0616014699</v>
       </c>
     </row>
     <row r="17">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3487131871.331304</v>
+        <v>3645135456.082426</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>334970000</v>
@@ -5527,7 +5527,7 @@
         <v>106336984.9487036</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2813136371.226805</v>
+        <v>2971139955.977927</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.0375</v>
@@ -5545,10 +5545,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>306837.2861040062</v>
+        <v>324071.2146243629</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>380352.012305562</v>
+        <v>397585.9408259187</v>
       </c>
     </row>
     <row r="18">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3309862747.427698</v>
+        <v>3459834184.822211</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>334970000</v>
@@ -5576,7 +5576,7 @@
         <v>106485554.4875584</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2639320562.05865</v>
+        <v>2789291999.453163</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.0375</v>
@@ -5594,10 +5594,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>287878.6704774662</v>
+        <v>304236.508410215</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>361016.7332039318</v>
+        <v>377374.5711366806</v>
       </c>
     </row>
     <row r="19">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3310897469.321378</v>
+        <v>3460915790.451423</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>334970000</v>
@@ -5625,7 +5625,7 @@
         <v>106432974.8514239</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2642612218.233233</v>
+        <v>2792630539.363278</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.0375</v>
@@ -5643,10 +5643,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>288237.7013647446</v>
+        <v>304600.6530482238</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>361129.5934480979</v>
+        <v>377492.5451315772</v>
       </c>
     </row>
     <row r="20">
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3322146141.580943</v>
+        <v>3472674145.340232</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>334970000</v>
@@ -5674,7 +5674,7 @@
         <v>106442587.2808068</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2653449274.334762</v>
+        <v>2803977278.094051</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.0375</v>
@@ -5692,10 +5692,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>289419.731826389</v>
+        <v>305838.276134645</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>362356.5201281199</v>
+        <v>378775.064436376</v>
       </c>
     </row>
     <row r="21">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3319843562.749172</v>
+        <v>3470267235.578913</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>334970000</v>
@@ -5723,7 +5723,7 @@
         <v>106455238.2665053</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2649422534.878963</v>
+        <v>2799846207.708704</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.0375</v>
@@ -5741,10 +5741,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>288980.5231839987</v>
+        <v>305387.6878024514</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>362105.3708958937</v>
+        <v>378512.5355143464</v>
       </c>
     </row>
     <row r="22">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3316623360.866395</v>
+        <v>3466901124.834678</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>334970000</v>
@@ -5772,7 +5772,7 @@
         <v>106530285.11483</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2647911077.078412</v>
+        <v>2798188841.046695</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.0375</v>
@@ -5790,10 +5790,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>288815.6639136393</v>
+        <v>305206.9138115948</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>361754.1337441778</v>
+        <v>378145.3836421333</v>
       </c>
     </row>
     <row r="23">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3341770538.551773</v>
+        <v>3493187732.965268</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>334970000</v>
@@ -5821,7 +5821,7 @@
         <v>106209842.7768683</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2672454090.242148</v>
+        <v>2823871284.655643</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.0375</v>
@@ -5839,10 +5839,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>291492.64453534</v>
+        <v>308008.1755556361</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>364497.0124162101</v>
+        <v>381012.5434365062</v>
       </c>
     </row>
     <row r="24">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3387602107.560916</v>
+        <v>3541095951.916372</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>334970000</v>
@@ -5870,7 +5870,7 @@
         <v>134869772.9750939</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2722657149.278468</v>
+        <v>2876150993.633924</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.0375</v>
@@ -5888,10 +5888,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>296968.4439122846</v>
+        <v>313710.4814179742</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>369496.0001640103</v>
+        <v>386238.0376697</v>
       </c>
     </row>
     <row r="25">
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3522327931.244609</v>
+        <v>3681926266.019708</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>334970000</v>
@@ -5919,7 +5919,7 @@
         <v>166906447.5117323</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2831210653.225533</v>
+        <v>2990808988.000631</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.0375</v>
@@ -5937,10 +5937,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>308808.702667203</v>
+        <v>326216.5753924609</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>384190.9529327605</v>
+        <v>401598.8256580184</v>
       </c>
     </row>
     <row r="26">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3691758011.203047</v>
+        <v>3859033302.567655</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>334970000</v>
@@ -5968,7 +5968,7 @@
         <v>174905990.8713613</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2968387878.961623</v>
+        <v>3135663170.326231</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.0375</v>
@@ -5986,10 +5986,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>323771.0372666391</v>
+        <v>342016.2588490502</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>402671.2038194818</v>
+        <v>420916.4254018929</v>
       </c>
     </row>
     <row r="27">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3793168501.903408</v>
+        <v>3965038750.285202</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>334970000</v>
@@ -6017,7 +6017,7 @@
         <v>191459906.6813183</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3039859687.869167</v>
+        <v>3211729936.25096</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.0375</v>
@@ -6035,10 +6035,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>331566.6834722196</v>
+        <v>350313.0909037557</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>413732.3525313746</v>
+        <v>432478.7599629108</v>
       </c>
     </row>
     <row r="28">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3815436515.573425</v>
+        <v>3988315738.125102</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>334970000</v>
@@ -6066,7 +6066,7 @@
         <v>150458263.8530219</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3119660157.506038</v>
+        <v>3292539380.057715</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.0375</v>
@@ -6084,10 +6084,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>340270.7618751178</v>
+        <v>359127.2211687687</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>416161.1920826031</v>
+        <v>435017.6513762539</v>
       </c>
     </row>
     <row r="29">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3824208761.850309</v>
+        <v>3997485459.005531</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>334970000</v>
@@ -6115,7 +6115,7 @@
         <v>148940725.8800582</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3123753209.846468</v>
+        <v>3297029907.00169</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.0375</v>
@@ -6133,10 +6133,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>340717.2034642511</v>
+        <v>359617.0165141915</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>417118.0074962338</v>
+        <v>436017.8205461741</v>
       </c>
     </row>
     <row r="30">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3798298269.581012</v>
+        <v>3970400950.148312</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>334970000</v>
@@ -6164,7 +6164,7 @@
         <v>140084321.8061661</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3104704165.826068</v>
+        <v>3276806846.393368</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.0375</v>
@@ -6182,10 +6182,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>338639.4666613437</v>
+        <v>357411.2261738289</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>414291.8717955807</v>
+        <v>433063.6313080659</v>
       </c>
     </row>
     <row r="31">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3846549224.508112</v>
+        <v>4020838178.53092</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>334970000</v>
@@ -6213,7 +6213,7 @@
         <v>154475144.3495293</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3138401679.040303</v>
+        <v>3312690633.063111</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.0375</v>
@@ -6231,10 +6231,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>342314.9562710425</v>
+        <v>361325.179236857</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>419554.7492775214</v>
+        <v>438564.972243336</v>
       </c>
     </row>
     <row r="32">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3780306162.322508</v>
+        <v>3951593612.049976</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>334970000</v>
@@ -6262,7 +6262,7 @@
         <v>130752789.7099153</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3087275062.682134</v>
+        <v>3258562512.409602</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.0375</v>
@@ -6280,10 +6280,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>336738.4217057523</v>
+        <v>355421.2615266787</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>412329.4182796553</v>
+        <v>431012.2581005817</v>
       </c>
     </row>
     <row r="33">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3902178954.302975</v>
+        <v>4078988517.540073</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>334970000</v>
@@ -6311,7 +6311,7 @@
         <v>135699774.815579</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3185752823.681576</v>
+        <v>3362562386.918674</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.0375</v>
@@ -6329,10 +6329,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>347479.6887256267</v>
+        <v>366764.8421564384</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>425622.4520350351</v>
+        <v>444907.6054658468</v>
       </c>
     </row>
     <row r="34">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3366262659.734222</v>
+        <v>3518789603.674771</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>334970000</v>
@@ -6360,7 +6360,7 @@
         <v>131931405.5965129</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2627106751.155241</v>
+        <v>2779633695.09579</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.0375</v>
@@ -6378,10 +6378,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>286546.473208638</v>
+        <v>303183.047963827</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>367168.4420957019</v>
+        <v>383805.0168508909</v>
       </c>
     </row>
     <row r="35">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3929445240.830592</v>
+        <v>4107490252.330956</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>334970000</v>
@@ -6409,7 +6409,7 @@
         <v>129864360.3284257</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3199019021.823361</v>
+        <v>3377064033.323725</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.0375</v>
@@ -6427,10 +6427,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>348926.6730511566</v>
+        <v>368346.5805579171</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>428596.4683130372</v>
+        <v>448016.3758197976</v>
       </c>
     </row>
     <row r="37">
@@ -6452,10 +6452,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="11" t="n">
-        <v>9256950.219000347</v>
+        <v>9779943.693835331</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>11542442.01147743</v>
+        <v>12065435.48631241</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T17:00:15+00:00</t>
+          <t>2026-06-09T19:10:43+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T19:10:43+00:00</t>
+          <t>2026-06-09T19:54:31+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T19:54:31+00:00</t>
+          <t>2026-06-09T20:53:47+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T20:53:47+00:00</t>
+          <t>2026-06-09T22:03:40+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1458461.439092668</v>
+        <v>2424528.411287293</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1574723.262443715</v>
+        <v>2540790.234638341</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1458461.439092668</v>
+        <v>2424528.411287293</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-8097611.150074472</v>
+        <v>-7131544.177879847</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T22:03:40+00:00</t>
+          <t>2026-06-09T22:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,13 +1236,13 @@
         <v>429848.8136485304</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>308899.1120589486</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-344081.8096984822</v>
+        <v>85767.00395004822</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>306025.5205752055</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>219916.8837310147</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-244964.7680533893</v>
+        <v>61060.75252181623</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>227246.3517057119</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>163304.3852435207</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-181904.2729898352</v>
+        <v>45342.0787158766</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         <v>2946.286265177527</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>2117.268170312945</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2358.418769165147</v>
+        <v>587.8674960123802</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1458461.439092668</v>
+        <v>5122374.709655433</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>1574723.262443715</v>
+        <v>5238636.53300648</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1458461.439092668</v>
+        <v>5122374.709655433</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-8097611.150074472</v>
+        <v>-4433697.879511707</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T17:00:15+00:00</t>
+          <t>2026-06-09T22:31:31+00:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="9" t="n">
-        <v>-3663913.270562765</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T22:31:31+00:00</t>
+          <t>2026-06-09T23:17:44+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5122374.709655433</v>
+        <v>6088441.681850058</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5238636.53300648</v>
+        <v>6204703.505201106</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5122374.709655433</v>
+        <v>6088441.681850058</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-4433697.879511707</v>
+        <v>-3467630.907317081</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:17:44+00:00</t>
+          <t>2026-06-09T23:35:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,13 +1236,13 @@
         <v>429848.8136485304</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>308899.1120589486</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-344081.8096984822</v>
+        <v>85767.00395004822</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>306025.5205752055</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>219916.8837310147</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-244964.7680533893</v>
+        <v>61060.75252181623</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>227246.3517057119</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>163304.3852435207</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-181904.2729898352</v>
+        <v>45342.0787158766</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         <v>2946.286265177527</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>2117.268170312945</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2358.418769165147</v>
+        <v>587.8674960123802</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6088441.681850058</v>
+        <v>8826893.553516615</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>6204703.505201106</v>
+        <v>8943155.376867663</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6088441.681850058</v>
+        <v>8826893.553516615</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-3467630.907317081</v>
+        <v>-729179.0356505236</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:35:10+00:00</t>
+          <t>2026-06-10T01:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>2738451.871666558</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0</v>
+        <v>2738451.871666558</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>3282507.87432289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3282507.87432289</v>
+        <v>-544056.0026563322</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8826893.553516615</v>
+        <v>10054071.20809193</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>8943155.376867663</v>
+        <v>10170333.03144298</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9492954.288835494</v>
+        <v>9388950.252778627</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8826893.553516615</v>
+        <v>10054071.20809193</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-729179.0356505236</v>
+        <v>-625174.9995936573</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T01:21:19+00:00</t>
+          <t>2026-06-10T01:53:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1797,35 +1797,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -1834,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
@@ -1846,44 +1838,52 @@
         <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0</v>
+        <v>99849.35275556908</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>10000122.636328</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>0.154431</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
+        <v>-10000122.481897</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
@@ -1898,88 +1898,84 @@
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0</v>
+        <v>9666785.220264766</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>-23276.3803561733</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.28330096818</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-10000122.481897</v>
+        <v>-10156909.80992987</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9666785.220264766</v>
+        <v>7104351.295236039</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-23276.3803561733</v>
+        <v>1179.81563678413</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1992,59 +1988,59 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-10156909.80992987</v>
+        <v>9193.636315</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>-3e-14</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>-3e-14</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>7104351.295236039</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>1179.81563678413</v>
+        <v>-12024.01413768121</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2057,17 +2053,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2076,40 +2072,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5000000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9193.636315</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12024.01413768121</v>
+        <v>-12010.27080490064</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2122,17 +2118,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2141,40 +2137,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5000000</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5000000</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>566848.624341</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12010.27080490064</v>
+        <v>-11964.72785271988</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2187,67 +2183,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>566848.624341</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>104004.0360568663</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>104004.0360568663</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>0</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11964.72785271988</v>
+        <v>104004.0360568663</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
     </row>
     <row r="6">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9492954.288835494</v>
+        <v>9388950.252778627</v>
       </c>
     </row>
     <row r="8">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T01:53:44+00:00</t>
+          <t>2026-06-10T07:58:53+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T07:58:53+00:00</t>
+          <t>2026-06-10T09:52:04+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10054071.20809193</v>
+        <v>10084324.03813204</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>10170333.03144298</v>
+        <v>10200585.86148309</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10054071.20809193</v>
+        <v>10084324.03813204</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-625174.9995936573</v>
+        <v>-594922.1695535415</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T09:52:04+00:00</t>
+          <t>2026-06-10T11:00:18+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>2738451.871666558</v>
+        <v>2768704.701706673</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2738451.871666558</v>
+        <v>2768704.701706673</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>3282507.87432289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-544056.0026563322</v>
+        <v>-513803.1726162164</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5122374.709655433</v>
+        <v>10084324.03813204</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>5238636.53300648</v>
+        <v>10200585.86148309</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9492954.288835494</v>
+        <v>9388950.252778627</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>5122374.709655433</v>
+        <v>10084324.03813204</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-4433697.879511707</v>
+        <v>-594922.1695535415</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:17:44+00:00</t>
+          <t>2026-06-10T11:00:18+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>2768704.701706673</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0</v>
+        <v>2768704.701706673</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>3282507.87432289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3282507.87432289</v>
+        <v>-513803.1726162164</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -1236,13 +1236,13 @@
         <v>429848.8136485304</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>308899.1120589486</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>-344081.8096984822</v>
+        <v>85767.00395004822</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>306025.5205752055</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>219916.8837310147</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-244964.7680533893</v>
+        <v>61060.75252181623</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>227246.3517057119</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>163304.3852435207</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-181904.2729898352</v>
+        <v>45342.0787158766</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1797,35 +1797,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -1834,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
@@ -1846,44 +1838,52 @@
         <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0</v>
+        <v>99849.35275556908</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>10000122.636328</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>0.154431</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
+        <v>-10000122.481897</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
@@ -1898,88 +1898,84 @@
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0</v>
+        <v>9666785.220264766</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>23276.3803561733</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>-23276.3803561733</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.28330096818</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-10000122.481897</v>
+        <v>-10156909.80992987</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9666785.220264766</v>
+        <v>7104351.295236039</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>17106.36774934546</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-23276.3803561733</v>
+        <v>1179.81563678413</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1992,59 +1988,59 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-10156909.80992987</v>
+        <v>9193.636315</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>-3e-14</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>-3e-14</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>7104351.295236039</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>12024.01413768121</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>1179.81563678413</v>
+        <v>-12024.01413768121</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2057,17 +2053,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2076,40 +2072,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5000000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9193.636315</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>12010.27080490107</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12024.01413768121</v>
+        <v>-12010.27080490064</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2122,17 +2118,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2141,40 +2137,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5000000</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5000000</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>566848.624341</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11964.72785272024</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12010.27080490064</v>
+        <v>-11964.72785271988</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2187,67 +2183,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>566848.624341</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>104004.0360568663</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>104004.0360568663</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>0</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11964.72785271988</v>
+        <v>104004.0360568663</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2475,13 +2475,13 @@
         <v>2946.286265177527</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>2946.286265177527</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>2117.268170312945</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-2358.418769165147</v>
+        <v>587.8674960123802</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
     </row>
     <row r="6">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9492954.288835494</v>
+        <v>9388950.252778627</v>
       </c>
     </row>
     <row r="8">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>115802.6727309982</v>
+        <v>11798.63667413196</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,10 +87,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10084324.03813204</v>
+        <v>10086500.94216282</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +501,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>116261.8233510476</v>
+        <v>115391.3077449365</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>10200585.86148309</v>
+        <v>10201892.24990776</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9377151.616104495</v>
+        <v>9029202.172316257</v>
       </c>
     </row>
     <row r="10">
@@ -536,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11798.63667413196</v>
+        <v>12598.4555305973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9388950.252778627</v>
+        <v>9041800.627846856</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9377151.616104495</v>
+        <v>9029202.172316257</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2688283.870207915</v>
+        <v>-2671293.479198225</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>12065435.48631241</v>
+        <v>11700495.65151448</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10084324.03813204</v>
+        <v>10086500.94216282</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-9377151.616104495</v>
+        <v>-9029202.172316257</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-594922.1695535415</v>
+        <v>-235529.1970209448</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T11:00:18+00:00</t>
+          <t>2026-06-23T21:11:09+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +845,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>2768704.701706673</v>
+        <v>2780948.049307498</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2768704.701706673</v>
+        <v>2780948.049307498</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -860,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3282507.87432289</v>
+        <v>3162987.351802382</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3282507.87432289</v>
+        <v>3162987.351802382</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-513803.1726162164</v>
+        <v>-382039.302494884</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1591008.073238561</v>
+        <v>1533077.3314008</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1591008.073238561</v>
+        <v>1533077.3314008</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1585366.926761428</v>
+        <v>1643297.66859919</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1153588.503732787</v>
+        <v>1111584.796196142</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1153588.503732787</v>
+        <v>1111584.796196142</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1153588.503732787</v>
+        <v>-1111584.796196142</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>711689.1590291519</v>
+        <v>685775.6004282022</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>711689.1590291519</v>
+        <v>685775.6004282022</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-134177.0215931519</v>
+        <v>-108263.4629922022</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>421591.1445078621</v>
+        <v>406240.4444301074</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>421591.1445078621</v>
+        <v>406240.4444301074</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>131520.8954244758</v>
+        <v>146871.5955022305</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1189,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>384302.6572275028</v>
+        <v>370309.6810774226</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>384302.6572275028</v>
+        <v>370309.6810774226</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-384302.6572276429</v>
+        <v>-370309.6810775626</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>344081.8096984822</v>
+        <v>331553.3286530414</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>308899.1120589486</v>
+        <v>296370.6310135078</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>85767.00395004822</v>
+        <v>98295.48499548905</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>245326.427821689</v>
+        <v>236393.7629313157</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>245326.427821689</v>
+        <v>236393.7629313157</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>68885.37094524053</v>
+        <v>77818.03583561383</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1388,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>240787.3720966343</v>
+        <v>232019.9803244923</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>240787.3720966343</v>
+        <v>232019.9803244923</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-231218.3606514228</v>
+        <v>-222450.9688792808</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>240784.0984418402</v>
+        <v>232016.8258678683</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>240784.0984418402</v>
+        <v>232016.8258678683</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-194498.6233988403</v>
+        <v>-185731.3508248682</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>244964.7680533893</v>
+        <v>236045.2716811542</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>219916.8837310147</v>
+        <v>210997.3873587797</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>61060.75252181623</v>
+        <v>69980.24889405131</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>181904.2729898352</v>
+        <v>175280.8939793758</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>163304.3852435207</v>
+        <v>156681.0062330612</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>45342.0787158766</v>
+        <v>51965.45772633608</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>153588.3815918085</v>
+        <v>147996.0222361683</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>153588.3815918085</v>
+        <v>147996.0222361683</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>51198.58338774954</v>
+        <v>56790.9427433897</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1713,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>137423.7896218669</v>
+        <v>132420.0047807591</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>137423.7896218669</v>
+        <v>132420.0047807591</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>31392.84900859464</v>
+        <v>36396.63384970245</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1778,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>121382.2876116389</v>
+        <v>116962.5954142302</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>121382.2876116389</v>
+        <v>116962.5954142302</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>51353.14012135115</v>
+        <v>55772.8323187599</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1904,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>22428.85607014862</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>22428.85607014862</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-23276.3803561733</v>
+        <v>-22428.85607014862</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1969,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>16483.50191318916</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>16483.50191318916</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1179.81563678413</v>
+        <v>1802.681472940421</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1988,82 +1991,86 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>9193.636315</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-3e-14</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-3e-14</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-12024.01413768121</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2072,40 +2079,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5000000</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5000000</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>9193.636315</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>-3e-14</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>-3e-14</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11586.20362585538</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11586.20362585538</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12010.27080490064</v>
+        <v>-11586.20362585538</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2118,17 +2125,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2137,40 +2144,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>5000000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>566848.624341</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>11572.96070628914</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>11572.96070628914</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11964.72785271988</v>
+        <v>-11572.96070628871</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2183,71 +2190,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>104004.0360568663</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>104004.0360568663</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>11529.07603419481</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>11529.07603419481</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>104004.0360568663</v>
+        <v>-11529.07603419446</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2298,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11605.49249757234</v>
+        <v>11182.9209210445</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11605.49249757234</v>
+        <v>11182.9209210445</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11605.49249756869</v>
+        <v>-11182.92092104084</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6991.78295661789</v>
+        <v>6737.202744073134</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6991.78295661789</v>
+        <v>6737.202744073134</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2554.642033690668</v>
+        <v>2809.222246235423</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2642.942016836885</v>
+        <v>2546.708946593631</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2642.942016836885</v>
+        <v>2546.708946593631</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1854.491527971004</v>
+        <v>1950.724598214259</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2358.418769165147</v>
+        <v>2272.545572693094</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2117.268170312945</v>
+        <v>2031.394973840892</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>587.8674960123802</v>
+        <v>673.7406924844335</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>827.4329609329093</v>
+        <v>797.3050149757979</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>827.4329609329093</v>
+        <v>797.3050149757979</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-702.0541249329093</v>
+        <v>-671.9261789757979</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>321.4538136234616</v>
+        <v>309.7492483211129</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>321.4538136234616</v>
+        <v>309.7492483211129</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133821.1196036235</v>
+        <v>-133809.4150383211</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.758398143077016</v>
+        <v>7.475904441466632</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.758398143077016</v>
+        <v>7.475904441466632</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.758398134007479</v>
+        <v>-7.475904432397096</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>3.036096669039071</v>
+        <v>2.925548309613985</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>3.036096669039071</v>
+        <v>2.925548309613985</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-3.036096664408361</v>
+        <v>-2.925548304983275</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9154697185107922</v>
+        <v>0.8821362359123132</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9154697185107922</v>
+        <v>0.8821362359123132</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.21361651889585</v>
+        <v>13.24695000149432</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6835882039202453</v>
+        <v>0.658697838855011</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6835882039202453</v>
+        <v>0.658697838855011</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6835882039202453</v>
+        <v>-0.658697838855011</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2387884479169468</v>
+        <v>0.230093839660209</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2387884479169468</v>
+        <v>0.230093839660209</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09259159921009311</v>
+        <v>0.1012862074668309</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05274828820472047</v>
+        <v>0.05082765215153476</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05274828820472047</v>
+        <v>0.05082765215153476</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05274243050504496</v>
+        <v>-0.05082179445185925</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0001385971057361135</v>
+        <v>0.0001335505988786616</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0001385971057361135</v>
+        <v>0.0001335505988786616</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>8.440289426388646e-05</v>
+        <v>8.944940112133838e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.523460542029865e-05</v>
+        <v>1.467989296569305e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.523460542029865e-05</v>
+        <v>1.467989296569305e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>3.76539457970135e-06</v>
+        <v>4.320107034306949e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.382401781693225e-05</v>
+        <v>1.33206667524193e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.382401781693225e-05</v>
+        <v>1.33206667524193e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.071756569084725e-05</v>
+        <v>-1.02142146263343e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>4.083750718006403e-06</v>
+        <v>3.935055866890377e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>4.083750718006403e-06</v>
+        <v>3.935055866890377e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-8.37507180064029e-08</v>
+        <v>6.4944133109623e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.986109486218629e-06</v>
+        <v>2.877381227289496e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.986109486218629e-06</v>
+        <v>2.877381227289496e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.986109486218629e-06</v>
+        <v>-2.877381227289496e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.252474089747426e-06</v>
+        <v>1.206869825148095e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.252474089747426e-06</v>
+        <v>1.206869825148095e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.440198340524262e-07</v>
+        <v>-3.984155694530947e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3468,13 +3471,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.803406370717327e-07</v>
+        <v>1.737741921461616e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.803406370717327e-07</v>
+        <v>1.737741921461616e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.803406370717327e-07</v>
+        <v>-1.737741921461616e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3533,13 +3536,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.53929198692647e-11</v>
+        <v>4.374010266082916e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.53929198692647e-11</v>
+        <v>4.374010266082916e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.311009291986926e-08</v>
+        <v>-1.310844010266083e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4460,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4475,195 +4478,388 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>9377151.616104495</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>11798.63667413196</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2988806180.523181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>9388950.252778627</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1988806180.523181</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.04028621767610686</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (effr), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.0364</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>12065435.48631241</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.03688895040288687</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>9377151.616104495</v>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.0391410605085019</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-2688283.870207915</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>-11.45157167604957</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>270879.183003302</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>178920.973062644</v>
+        <v>9702873.433050396</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>9431994.250047093</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>270879.183003302</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1000000000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Rate (APY)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0.03688895040288687</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2977531.418973385</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1988806180.523181</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>0.04028621767610686</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>6454462.831073041</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>9029202.172316257</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>12598.4555305973</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>9041800.627846856</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>11700495.65151448</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>9029202.172316257</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-2671293.479198225</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>178920.973062644</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ramp_months</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B41" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ref_rate_kind</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>effr</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>3 (SoM) → 3 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -4836,10 +5032,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>12598.4555305973</v>
       </c>
     </row>
   </sheetData>
@@ -4881,7 +5077,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4991,25 +5187,25 @@
         <v>2784292546.534297</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>303691.2029705925</v>
+        <v>293968.6389684683</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>384301.2849383999</v>
+        <v>374578.727875959</v>
       </c>
     </row>
     <row r="7">
@@ -5040,25 +5236,25 @@
         <v>2867657513.15868</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>312784.0718328374</v>
+        <v>303061.5086135139</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>391794.0657013687</v>
+        <v>382071.5092839777</v>
       </c>
     </row>
     <row r="8">
@@ -5089,25 +5285,25 @@
         <v>2875295500.667339</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>313617.1702145669</v>
+        <v>303894.6070669644</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>392076.1472267284</v>
+        <v>382353.5908336217</v>
       </c>
     </row>
     <row r="9">
@@ -5138,25 +5334,25 @@
         <v>2872629206.232289</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>313326.3494222396</v>
+        <v>303603.7862496005</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>392593.1603443155</v>
+        <v>382870.6039957182</v>
       </c>
     </row>
     <row r="10">
@@ -5187,25 +5383,25 @@
         <v>2879664844.277337</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>314093.7477275024</v>
+        <v>304371.1846209283</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>393553.921099522</v>
+        <v>383831.3648336361</v>
       </c>
     </row>
     <row r="11">
@@ -5236,25 +5432,25 @@
         <v>2914905338.478153</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>317937.5349367328</v>
+        <v>308214.9721610684</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>392873.0619614751</v>
+        <v>383150.5056369744</v>
       </c>
     </row>
     <row r="12">
@@ -5285,25 +5481,25 @@
         <v>2902686749.231011</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>316604.8164795121</v>
+        <v>306882.2535891147</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>394207.178693561</v>
+        <v>384484.6224839138</v>
       </c>
     </row>
     <row r="13">
@@ -5334,25 +5530,25 @@
         <v>2907586309.263426</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>317139.2263001047</v>
+        <v>307416.6634557144</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>391498.2099925156</v>
+        <v>381775.6535496546</v>
       </c>
     </row>
     <row r="14">
@@ -5383,25 +5579,25 @@
         <v>2905392368.002785</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>316899.9264960952</v>
+        <v>307177.3636311037</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>391455.7011935601</v>
+        <v>381733.1447470395</v>
       </c>
     </row>
     <row r="15">
@@ -5432,25 +5628,25 @@
         <v>2905301385.701985</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>316890.0027815728</v>
+        <v>307167.4399157268</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>390722.7290324869</v>
+        <v>381000.1725228651</v>
       </c>
     </row>
     <row r="16">
@@ -5481,25 +5677,25 @@
         <v>2898585065.373258</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>316157.4334246975</v>
+        <v>306434.870495785</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>389824.0616014699</v>
+        <v>380101.5050144822</v>
       </c>
     </row>
     <row r="17">
@@ -5530,25 +5726,25 @@
         <v>2971139955.977927</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>324071.2146243629</v>
+        <v>314348.6523767441</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>397585.9408259187</v>
+        <v>387863.3849071475</v>
       </c>
     </row>
     <row r="18">
@@ -5579,25 +5775,25 @@
         <v>2789291999.453163</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>304236.508410215</v>
+        <v>294513.9444550358</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>377374.5711366806</v>
+        <v>367652.0134779223</v>
       </c>
     </row>
     <row r="19">
@@ -5628,25 +5824,25 @@
         <v>2792630539.363278</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>304600.6530482238</v>
+        <v>294878.0891243936</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>377492.5451315772</v>
+        <v>367769.9874829751</v>
       </c>
     </row>
     <row r="20">
@@ -5677,25 +5873,25 @@
         <v>2803977278.094051</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>305838.276134645</v>
+        <v>296115.7123173613</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>378775.064436376</v>
+        <v>369052.5068981854</v>
       </c>
     </row>
     <row r="21">
@@ -5726,25 +5922,25 @@
         <v>2799846207.708704</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>305387.6878024514</v>
+        <v>295665.1239463767</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>378512.5355143464</v>
+        <v>368789.9779535549</v>
       </c>
     </row>
     <row r="22">
@@ -5775,25 +5971,25 @@
         <v>2798188841.046695</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K22" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>305206.9138115948</v>
+        <v>295484.3499399574</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>378145.3836421333</v>
+        <v>368422.8260497338</v>
       </c>
     </row>
     <row r="23">
@@ -5824,25 +6020,25 @@
         <v>2823871284.655643</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>308008.1755556361</v>
+        <v>298285.611925158</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>381012.5434365062</v>
+        <v>371289.9860909391</v>
       </c>
     </row>
     <row r="24">
@@ -5873,25 +6069,25 @@
         <v>2876150993.633924</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K24" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>313710.4814179742</v>
+        <v>303987.9182784049</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>386238.0376697</v>
+        <v>376515.4807739933</v>
       </c>
     </row>
     <row r="25">
@@ -5922,25 +6118,25 @@
         <v>2990808988.000631</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>326216.5753924609</v>
+        <v>316494.0133295352</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>401598.8256580184</v>
+        <v>391876.2700847145</v>
       </c>
     </row>
     <row r="26">
@@ -5971,25 +6167,25 @@
         <v>3135663170.326231</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>342016.2588490502</v>
+        <v>332293.6981463116</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>420916.4254018929</v>
+        <v>411193.871491632</v>
       </c>
     </row>
     <row r="27">
@@ -6020,25 +6216,25 @@
         <v>3211729936.25096</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>350313.0909037557</v>
+        <v>334415.2492646032</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>432478.7599629108</v>
+        <v>414590.4869628215</v>
       </c>
     </row>
     <row r="28">
@@ -6069,25 +6265,25 @@
         <v>3292539380.057715</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>359127.2211687687</v>
+        <v>343015.8606536701</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>435017.6513762539</v>
+        <v>417067.874719601</v>
       </c>
     </row>
     <row r="29">
@@ -6118,25 +6314,25 @@
         <v>3297029907.00169</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>359617.0165141915</v>
+        <v>343493.7908974375</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>436017.8205461741</v>
+        <v>418043.8151805623</v>
       </c>
     </row>
     <row r="30">
@@ -6167,25 +6363,25 @@
         <v>3276806846.393368</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>357411.2261738289</v>
+        <v>341341.4349697607</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>433063.6313080659</v>
+        <v>415161.1900272233</v>
       </c>
     </row>
     <row r="31">
@@ -6216,25 +6412,25 @@
         <v>3312690633.063111</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>361325.179236857</v>
+        <v>345160.5740428209</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>438564.972243336</v>
+        <v>420529.2631189993</v>
       </c>
     </row>
     <row r="32">
@@ -6265,25 +6461,25 @@
         <v>3258562512.409602</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>355421.2615266787</v>
+        <v>339399.6764418596</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>431012.2581005817</v>
+        <v>413159.5105374671</v>
       </c>
     </row>
     <row r="33">
@@ -6314,25 +6510,25 @@
         <v>3362562386.918674</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>366764.8421564384</v>
+        <v>350468.4632448382</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>444907.6054658468</v>
+        <v>426718.2485197183</v>
       </c>
     </row>
     <row r="34">
@@ -6363,25 +6559,25 @@
         <v>2779633695.09579</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>303183.047963827</v>
+        <v>288426.9132758148</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>383805.0168508909</v>
+        <v>367095.8463379316</v>
       </c>
     </row>
     <row r="35">
@@ -6412,25 +6608,25 @@
         <v>3377064033.323725</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>368346.5805579171</v>
+        <v>352011.8846490217</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>448016.3758197976</v>
+        <v>429751.7101215186</v>
       </c>
     </row>
     <row r="37">
@@ -6451,11 +6647,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="11" t="n">
-        <v>9779943.693835331</v>
-      </c>
-      <c r="O37" s="11" t="n">
-        <v>12065435.48631241</v>
+      <c r="N37" s="12" t="n">
+        <v>9431994.250047093</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>11700495.65151448</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23T21:11:09+00:00</t>
+          <t>2026-06-23T21:45:49+00:00</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>270879.183003302</v>
+        <v>270879.1830035028</v>
       </c>
     </row>
     <row r="15">
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9702873.433050396</v>
+        <v>9702873.433050597</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>270879.183003302</v>
+        <v>270879.1830035028</v>
       </c>
     </row>
     <row r="19">
@@ -4629,11 +4629,6 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Rate (APY)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
           <t>CoF (USD)</t>
         </is>
       </c>
@@ -4647,11 +4642,8 @@
       <c r="B20" s="6" t="n">
         <v>1000000000</v>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>0.03688895040288687</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>2977531.418973385</v>
+      <c r="C20" s="3" t="n">
+        <v>2977531.418973944</v>
       </c>
     </row>
     <row r="21">
@@ -4663,11 +4655,8 @@
       <c r="B21" s="6" t="n">
         <v>1988806180.523181</v>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>0.04028621767610686</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>6454462.831073041</v>
+      <c r="C21" s="3" t="n">
+        <v>6454462.831073149</v>
       </c>
     </row>
     <row r="23">

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,10 +87,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10084324.03813204</v>
+        <v>10086500.94216282</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +501,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>116261.8233510476</v>
+        <v>115391.3077449365</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>10200585.86148309</v>
+        <v>10201892.24990776</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9377151.616104495</v>
+        <v>9029202.172316257</v>
       </c>
     </row>
     <row r="10">
@@ -536,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11798.63667413196</v>
+        <v>12598.4555305973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9388950.252778627</v>
+        <v>9041800.627846856</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9377151.616104495</v>
+        <v>9029202.172316257</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2688283.870207915</v>
+        <v>-2671293.479198225</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>12065435.48631241</v>
+        <v>11700495.65151448</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>10084324.03813204</v>
+        <v>10086500.94216282</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-9377151.616104495</v>
+        <v>-9029202.172316257</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-594922.1695535415</v>
+        <v>-235529.1970209448</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T11:00:18+00:00</t>
+          <t>2026-06-23T21:45:49+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +845,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>2768704.701706673</v>
+        <v>2780948.049307498</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2768704.701706673</v>
+        <v>2780948.049307498</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -860,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3282507.87432289</v>
+        <v>3162987.351802382</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3282507.87432289</v>
+        <v>3162987.351802382</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-513803.1726162164</v>
+        <v>-382039.302494884</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1591008.073238561</v>
+        <v>1533077.3314008</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1591008.073238561</v>
+        <v>1533077.3314008</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1585366.926761428</v>
+        <v>1643297.66859919</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1153588.503732787</v>
+        <v>1111584.796196142</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1153588.503732787</v>
+        <v>1111584.796196142</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1153588.503732787</v>
+        <v>-1111584.796196142</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>711689.1590291519</v>
+        <v>685775.6004282022</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>711689.1590291519</v>
+        <v>685775.6004282022</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-134177.0215931519</v>
+        <v>-108263.4629922022</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>421591.1445078621</v>
+        <v>406240.4444301074</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>421591.1445078621</v>
+        <v>406240.4444301074</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>131520.8954244758</v>
+        <v>146871.5955022305</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1189,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>384302.6572275028</v>
+        <v>370309.6810774226</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>384302.6572275028</v>
+        <v>370309.6810774226</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-384302.6572276429</v>
+        <v>-370309.6810775626</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>344081.8096984822</v>
+        <v>331553.3286530414</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>308899.1120589486</v>
+        <v>296370.6310135078</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>85767.00395004822</v>
+        <v>98295.48499548905</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>245326.427821689</v>
+        <v>236393.7629313157</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>245326.427821689</v>
+        <v>236393.7629313157</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>68885.37094524053</v>
+        <v>77818.03583561383</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1388,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>240787.3720966343</v>
+        <v>232019.9803244923</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>240787.3720966343</v>
+        <v>232019.9803244923</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-231218.3606514228</v>
+        <v>-222450.9688792808</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1453,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>240784.0984418402</v>
+        <v>232016.8258678683</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>240784.0984418402</v>
+        <v>232016.8258678683</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-194498.6233988403</v>
+        <v>-185731.3508248682</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1518,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>244964.7680533893</v>
+        <v>236045.2716811542</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>219916.8837310147</v>
+        <v>210997.3873587797</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>61060.75252181623</v>
+        <v>69980.24889405131</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1583,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>181904.2729898352</v>
+        <v>175280.8939793758</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>163304.3852435207</v>
+        <v>156681.0062330612</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>45342.0787158766</v>
+        <v>51965.45772633608</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1648,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>153588.3815918085</v>
+        <v>147996.0222361683</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>153588.3815918085</v>
+        <v>147996.0222361683</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>51198.58338774954</v>
+        <v>56790.9427433897</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1713,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>137423.7896218669</v>
+        <v>132420.0047807591</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>137423.7896218669</v>
+        <v>132420.0047807591</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>31392.84900859464</v>
+        <v>36396.63384970245</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1778,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>121382.2876116389</v>
+        <v>116962.5954142302</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>121382.2876116389</v>
+        <v>116962.5954142302</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>51353.14012135115</v>
+        <v>55772.8323187599</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1904,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>22428.85607014862</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>23276.3803561733</v>
+        <v>22428.85607014862</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-23276.3803561733</v>
+        <v>-22428.85607014862</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1969,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>16483.50191318916</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>17106.36774934546</v>
+        <v>16483.50191318916</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1179.81563678413</v>
+        <v>1802.681472940421</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1988,82 +1991,86 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>9193.636315</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-3e-14</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-3e-14</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12024.01413768121</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-12024.01413768121</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2072,40 +2079,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5000000</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5000000</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>9193.636315</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>-3e-14</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>-3e-14</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>4993627.032029667</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11586.20362585538</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12010.27080490107</v>
+        <v>11586.20362585538</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12010.27080490064</v>
+        <v>-11586.20362585538</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2118,17 +2125,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2137,40 +2144,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>5000000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>566848.624341</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4.24e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>4.24e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>4987919.364249567</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>11572.96070628914</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11964.72785272024</v>
+        <v>11572.96070628914</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11964.72785271988</v>
+        <v>-11572.96070628871</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2183,71 +2190,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>3.55e-10</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>104004.0360568663</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>104004.0360568663</v>
+        <v>3.55e-10</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>4969005.171823935</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>11529.07603419481</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>11529.07603419481</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>104004.0360568663</v>
+        <v>-11529.07603419446</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2298,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11605.49249757234</v>
+        <v>11182.9209210445</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11605.49249757234</v>
+        <v>11182.9209210445</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11605.49249756869</v>
+        <v>-11182.92092104084</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6991.78295661789</v>
+        <v>6737.202744073134</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6991.78295661789</v>
+        <v>6737.202744073134</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2554.642033690668</v>
+        <v>2809.222246235423</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2642.942016836885</v>
+        <v>2546.708946593631</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2642.942016836885</v>
+        <v>2546.708946593631</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1854.491527971004</v>
+        <v>1950.724598214259</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2358.418769165147</v>
+        <v>2272.545572693094</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2117.268170312945</v>
+        <v>2031.394973840892</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>587.8674960123802</v>
+        <v>673.7406924844335</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>827.4329609329093</v>
+        <v>797.3050149757979</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>827.4329609329093</v>
+        <v>797.3050149757979</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-702.0541249329093</v>
+        <v>-671.9261789757979</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>321.4538136234616</v>
+        <v>309.7492483211129</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>321.4538136234616</v>
+        <v>309.7492483211129</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133821.1196036235</v>
+        <v>-133809.4150383211</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.758398143077016</v>
+        <v>7.475904441466632</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.758398143077016</v>
+        <v>7.475904441466632</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.758398134007479</v>
+        <v>-7.475904432397096</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>3.036096669039071</v>
+        <v>2.925548309613985</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>3.036096669039071</v>
+        <v>2.925548309613985</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-3.036096664408361</v>
+        <v>-2.925548304983275</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9154697185107922</v>
+        <v>0.8821362359123132</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9154697185107922</v>
+        <v>0.8821362359123132</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.21361651889585</v>
+        <v>13.24695000149432</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6835882039202453</v>
+        <v>0.658697838855011</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6835882039202453</v>
+        <v>0.658697838855011</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6835882039202453</v>
+        <v>-0.658697838855011</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2387884479169468</v>
+        <v>0.230093839660209</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2387884479169468</v>
+        <v>0.230093839660209</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.09259159921009311</v>
+        <v>0.1012862074668309</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05274828820472047</v>
+        <v>0.05082765215153476</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05274828820472047</v>
+        <v>0.05082765215153476</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05274243050504496</v>
+        <v>-0.05082179445185925</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0001385971057361135</v>
+        <v>0.0001335505988786616</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0001385971057361135</v>
+        <v>0.0001335505988786616</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>8.440289426388646e-05</v>
+        <v>8.944940112133838e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.523460542029865e-05</v>
+        <v>1.467989296569305e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.523460542029865e-05</v>
+        <v>1.467989296569305e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>3.76539457970135e-06</v>
+        <v>4.320107034306949e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.382401781693225e-05</v>
+        <v>1.33206667524193e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.382401781693225e-05</v>
+        <v>1.33206667524193e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.071756569084725e-05</v>
+        <v>-1.02142146263343e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>4.083750718006403e-06</v>
+        <v>3.935055866890377e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>4.083750718006403e-06</v>
+        <v>3.935055866890377e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-8.37507180064029e-08</v>
+        <v>6.4944133109623e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.986109486218629e-06</v>
+        <v>2.877381227289496e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.986109486218629e-06</v>
+        <v>2.877381227289496e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.986109486218629e-06</v>
+        <v>-2.877381227289496e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.252474089747426e-06</v>
+        <v>1.206869825148095e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.252474089747426e-06</v>
+        <v>1.206869825148095e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.440198340524262e-07</v>
+        <v>-3.984155694530947e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3468,13 +3471,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.803406370717327e-07</v>
+        <v>1.737741921461616e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.803406370717327e-07</v>
+        <v>1.737741921461616e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.803406370717327e-07</v>
+        <v>-1.737741921461616e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3533,13 +3536,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.53929198692647e-11</v>
+        <v>4.374010266082916e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.53929198692647e-11</v>
+        <v>4.374010266082916e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.311009291986926e-08</v>
+        <v>-1.310844010266083e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4460,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4475,195 +4478,377 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>9377151.616104495</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>11798.63667413196</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2988806180.523181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>9388950.252778627</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1988806180.523181</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.04028621767610686</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (effr), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.0364</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>12065435.48631241</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.03688895040288687</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>9377151.616104495</v>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.0391410605085019</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-2688283.870207915</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>-11.45157167604957</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>270879.1830035028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>178920.973062644</v>
+        <v>9702873.433050597</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>9431994.250047093</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>270879.1830035028</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1000000000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2977531.418973944</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1988806180.523181</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6454462.831073149</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>9029202.172316257</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>12598.4555305973</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>9041800.627846856</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>11700495.65151448</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>9029202.172316257</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-2671293.479198225</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>178920.973062644</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ramp_months</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B41" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ref_rate_kind</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>effr</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>3 (SoM) → 3 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -4836,10 +5021,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>11798.63667413196</v>
+        <v>12598.4555305973</v>
       </c>
     </row>
   </sheetData>
@@ -4881,7 +5066,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4991,25 +5176,25 @@
         <v>2784292546.534297</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>303691.2029705925</v>
+        <v>293968.6389684683</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>384301.2849383999</v>
+        <v>374578.727875959</v>
       </c>
     </row>
     <row r="7">
@@ -5040,25 +5225,25 @@
         <v>2867657513.15868</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>312784.0718328374</v>
+        <v>303061.5086135139</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>391794.0657013687</v>
+        <v>382071.5092839777</v>
       </c>
     </row>
     <row r="8">
@@ -5089,25 +5274,25 @@
         <v>2875295500.667339</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>313617.1702145669</v>
+        <v>303894.6070669644</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>392076.1472267284</v>
+        <v>382353.5908336217</v>
       </c>
     </row>
     <row r="9">
@@ -5138,25 +5323,25 @@
         <v>2872629206.232289</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>313326.3494222396</v>
+        <v>303603.7862496005</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>392593.1603443155</v>
+        <v>382870.6039957182</v>
       </c>
     </row>
     <row r="10">
@@ -5187,25 +5372,25 @@
         <v>2879664844.277337</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>314093.7477275024</v>
+        <v>304371.1846209283</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>393553.921099522</v>
+        <v>383831.3648336361</v>
       </c>
     </row>
     <row r="11">
@@ -5236,25 +5421,25 @@
         <v>2914905338.478153</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>317937.5349367328</v>
+        <v>308214.9721610684</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>392873.0619614751</v>
+        <v>383150.5056369744</v>
       </c>
     </row>
     <row r="12">
@@ -5285,25 +5470,25 @@
         <v>2902686749.231011</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>316604.8164795121</v>
+        <v>306882.2535891147</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>394207.178693561</v>
+        <v>384484.6224839138</v>
       </c>
     </row>
     <row r="13">
@@ -5334,25 +5519,25 @@
         <v>2907586309.263426</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>317139.2263001047</v>
+        <v>307416.6634557144</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>391498.2099925156</v>
+        <v>381775.6535496546</v>
       </c>
     </row>
     <row r="14">
@@ -5383,25 +5568,25 @@
         <v>2905392368.002785</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>316899.9264960952</v>
+        <v>307177.3636311037</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>391455.7011935601</v>
+        <v>381733.1447470395</v>
       </c>
     </row>
     <row r="15">
@@ -5432,25 +5617,25 @@
         <v>2905301385.701985</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>316890.0027815728</v>
+        <v>307167.4399157268</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>390722.7290324869</v>
+        <v>381000.1725228651</v>
       </c>
     </row>
     <row r="16">
@@ -5481,25 +5666,25 @@
         <v>2898585065.373258</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>316157.4334246975</v>
+        <v>306434.870495785</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>389824.0616014699</v>
+        <v>380101.5050144822</v>
       </c>
     </row>
     <row r="17">
@@ -5530,25 +5715,25 @@
         <v>2971139955.977927</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>324071.2146243629</v>
+        <v>314348.6523767441</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>397585.9408259187</v>
+        <v>387863.3849071475</v>
       </c>
     </row>
     <row r="18">
@@ -5579,25 +5764,25 @@
         <v>2789291999.453163</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>304236.508410215</v>
+        <v>294513.9444550358</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>377374.5711366806</v>
+        <v>367652.0134779223</v>
       </c>
     </row>
     <row r="19">
@@ -5628,25 +5813,25 @@
         <v>2792630539.363278</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>304600.6530482238</v>
+        <v>294878.0891243936</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>377492.5451315772</v>
+        <v>367769.9874829751</v>
       </c>
     </row>
     <row r="20">
@@ -5677,25 +5862,25 @@
         <v>2803977278.094051</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>305838.276134645</v>
+        <v>296115.7123173613</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>378775.064436376</v>
+        <v>369052.5068981854</v>
       </c>
     </row>
     <row r="21">
@@ -5726,25 +5911,25 @@
         <v>2799846207.708704</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>305387.6878024514</v>
+        <v>295665.1239463767</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>378512.5355143464</v>
+        <v>368789.9779535549</v>
       </c>
     </row>
     <row r="22">
@@ -5775,25 +5960,25 @@
         <v>2798188841.046695</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K22" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>305206.9138115948</v>
+        <v>295484.3499399574</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>378145.3836421333</v>
+        <v>368422.8260497338</v>
       </c>
     </row>
     <row r="23">
@@ -5824,25 +6009,25 @@
         <v>2823871284.655643</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>308008.1755556361</v>
+        <v>298285.611925158</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>381012.5434365062</v>
+        <v>371289.9860909391</v>
       </c>
     </row>
     <row r="24">
@@ -5873,25 +6058,25 @@
         <v>2876150993.633924</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K24" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>313710.4814179742</v>
+        <v>303987.9182784049</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>386238.0376697</v>
+        <v>376515.4807739933</v>
       </c>
     </row>
     <row r="25">
@@ -5922,25 +6107,25 @@
         <v>2990808988.000631</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>326216.5753924609</v>
+        <v>316494.0133295352</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>401598.8256580184</v>
+        <v>391876.2700847145</v>
       </c>
     </row>
     <row r="26">
@@ -5971,25 +6156,25 @@
         <v>3135663170.326231</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03750000355548933</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.04061250356615579</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03692656294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>342016.2588490502</v>
+        <v>332293.6981463116</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>420916.4254018929</v>
+        <v>411193.871491632</v>
       </c>
     </row>
     <row r="27">
@@ -6020,25 +6205,25 @@
         <v>3211729936.25096</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>350313.0909037557</v>
+        <v>334415.2492646032</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>432478.7599629108</v>
+        <v>414590.4869628215</v>
       </c>
     </row>
     <row r="28">
@@ -6069,25 +6254,25 @@
         <v>3292539380.057715</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>359127.2211687687</v>
+        <v>343015.8606536701</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>435017.6513762539</v>
+        <v>417067.874719601</v>
       </c>
     </row>
     <row r="29">
@@ -6118,25 +6303,25 @@
         <v>3297029907.00169</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>359617.0165141915</v>
+        <v>343493.7908974375</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>436017.8205461741</v>
+        <v>418043.8151805623</v>
       </c>
     </row>
     <row r="30">
@@ -6167,25 +6352,25 @@
         <v>3276806846.393368</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>357411.2261738289</v>
+        <v>341341.4349697607</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>433063.6313080659</v>
+        <v>415161.1900272233</v>
       </c>
     </row>
     <row r="31">
@@ -6216,25 +6401,25 @@
         <v>3312690633.063111</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>361325.179236857</v>
+        <v>345160.5740428209</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>438564.972243336</v>
+        <v>420529.2631189993</v>
       </c>
     </row>
     <row r="32">
@@ -6265,25 +6450,25 @@
         <v>3258562512.409602</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>355421.2615266787</v>
+        <v>339399.6764418596</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>431012.2581005817</v>
+        <v>413159.5105374671</v>
       </c>
     </row>
     <row r="33">
@@ -6314,25 +6499,25 @@
         <v>3362562386.918674</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>366764.8421564384</v>
+        <v>350468.4632448382</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>444907.6054658468</v>
+        <v>426718.2485197183</v>
       </c>
     </row>
     <row r="34">
@@ -6363,25 +6548,25 @@
         <v>2779633695.09579</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>303183.047963827</v>
+        <v>288426.9132758148</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>383805.0168508909</v>
+        <v>367095.8463379316</v>
       </c>
     </row>
     <row r="35">
@@ -6412,25 +6597,25 @@
         <v>3377064033.323725</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03680118780282747</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>368346.5805579171</v>
+        <v>352011.8846490217</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>448016.3758197976</v>
+        <v>429751.7101215186</v>
       </c>
     </row>
     <row r="37">
@@ -6451,11 +6636,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="11" t="n">
-        <v>9779943.693835331</v>
-      </c>
-      <c r="O37" s="11" t="n">
-        <v>12065435.48631241</v>
+      <c r="N37" s="12" t="n">
+        <v>9431994.250047093</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>11700495.65151448</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9029202.172316257</v>
+        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9041800.627846856</v>
+        <v>9265671.732515046</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9029202.172316257</v>
+        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2671293.479198225</v>
+        <v>-2447422.374530034</v>
       </c>
     </row>
     <row r="16">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-9029202.172316257</v>
+        <v>-9253073.276984449</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-235529.1970209448</v>
+        <v>-459400.3016891367</v>
       </c>
     </row>
     <row r="25">
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23T21:45:49+00:00</t>
+          <t>2026-06-25T11:44:13+00:00</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -863,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3162987.351802382</v>
+        <v>3239887.004567656</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3162987.351802382</v>
+        <v>3239887.004567656</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-382039.302494884</v>
+        <v>-458938.9552601578</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1533077.3314008</v>
+        <v>1570350.042712735</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1533077.3314008</v>
+        <v>1570350.042712735</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1643297.66859919</v>
+        <v>1606024.957287254</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1111584.796196142</v>
+        <v>1138610.033839894</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1111584.796196142</v>
+        <v>1138610.033839894</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1111584.796196142</v>
+        <v>-1138610.033839894</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>685775.6004282022</v>
+        <v>702448.416245115</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>685775.6004282022</v>
+        <v>702448.416245115</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-108263.4629922022</v>
+        <v>-124936.278809115</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1123,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>406240.4444301074</v>
+        <v>416117.1039425409</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>406240.4444301074</v>
+        <v>416117.1039425409</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>146871.5955022305</v>
+        <v>136994.935989797</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1192,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>370309.6810774226</v>
+        <v>379312.7793270081</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>370309.6810774226</v>
+        <v>379312.7793270081</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-370309.6810775626</v>
+        <v>-379312.7793271481</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>331553.3286530414</v>
+        <v>339614.1689317927</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>296370.6310135078</v>
+        <v>304431.4712922591</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>98295.48499548905</v>
+        <v>90234.64471673773</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1322,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>236393.7629313157</v>
+        <v>242141.050625949</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>236393.7629313157</v>
+        <v>242141.050625949</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>77818.03583561383</v>
+        <v>72070.74814098052</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>232019.9803244923</v>
+        <v>237660.9310894051</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>232019.9803244923</v>
+        <v>237660.9310894051</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-222450.9688792808</v>
+        <v>-228091.9196441936</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>232016.8258678683</v>
+        <v>237657.6999405303</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>232016.8258678683</v>
+        <v>237657.6999405303</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-185731.3508248682</v>
+        <v>-191372.2248975303</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>236045.2716811542</v>
+        <v>241784.0867348476</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>210997.3873587797</v>
+        <v>216736.2024124731</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>69980.24889405131</v>
+        <v>64241.43384035787</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>175280.8939793758</v>
+        <v>179542.3842682067</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>156681.0062330612</v>
+        <v>160942.4965218921</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>51965.45772633608</v>
+        <v>47703.96743750521</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>147996.0222361683</v>
+        <v>151594.1531974312</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>147996.0222361683</v>
+        <v>151594.1531974312</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>56790.9427433897</v>
+        <v>53192.81178212681</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>132420.0047807591</v>
+        <v>135639.4461677168</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>132420.0047807591</v>
+        <v>135639.4461677168</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>36396.63384970245</v>
+        <v>33177.19246274477</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>116962.5954142302</v>
+        <v>119806.2308681482</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>116962.5954142302</v>
+        <v>119806.2308681482</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>55772.8323187599</v>
+        <v>52929.19686484189</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22428.85607014862</v>
+        <v>22974.15424933163</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22428.85607014862</v>
+        <v>22974.15424933163</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-22428.85607014862</v>
+        <v>-22974.15424933163</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>16483.50191318916</v>
+        <v>16884.25456645465</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>16483.50191318916</v>
+        <v>16884.25456645465</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1802.681472940421</v>
+        <v>1401.928819674936</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11586.20362585538</v>
+        <v>11867.89145340497</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11586.20362585538</v>
+        <v>11867.89145340497</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11586.20362585538</v>
+        <v>-11867.89145340497</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2171,13 +2171,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11572.96070628914</v>
+        <v>11854.32656735484</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11572.96070628914</v>
+        <v>11854.32656735484</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11572.96070628871</v>
+        <v>-11854.32656735441</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2236,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11529.07603419481</v>
+        <v>11809.37495579145</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11529.07603419481</v>
+        <v>11809.37495579145</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11529.07603419446</v>
+        <v>-11809.3749557911</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11182.9209210445</v>
+        <v>11454.80399867989</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11182.9209210445</v>
+        <v>11454.80399867989</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11182.92092104084</v>
+        <v>-11454.80399867623</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2366,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6737.202744073134</v>
+        <v>6900.999969292277</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6737.202744073134</v>
+        <v>6900.999969292277</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2809.222246235423</v>
+        <v>2645.42502101628</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2546.708946593631</v>
+        <v>2608.625423615162</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2546.708946593631</v>
+        <v>2608.625423615162</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1950.724598214259</v>
+        <v>1888.808121192727</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2496,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2272.545572693094</v>
+        <v>2327.796494051909</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2031.394973840892</v>
+        <v>2086.645895199707</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>673.7406924844335</v>
+        <v>618.4897711256187</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>797.3050149757979</v>
+        <v>816.6893728565566</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>797.3050149757979</v>
+        <v>816.6893728565566</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-671.9261789757979</v>
+        <v>-691.3105368565565</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2626,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>309.7492483211129</v>
+        <v>317.2799801865517</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>309.7492483211129</v>
+        <v>317.2799801865517</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133809.4150383211</v>
+        <v>-133816.9457701865</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.475904441466632</v>
+        <v>7.657661240249769</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.475904441466632</v>
+        <v>7.657661240249769</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.475904432397096</v>
+        <v>-7.657661231180232</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2756,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.925548309613985</v>
+        <v>2.996675261490397</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.925548309613985</v>
+        <v>2.996675261490397</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.925548304983275</v>
+        <v>-2.996675256859687</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.8821362359123132</v>
+        <v>0.9035830400529201</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.8821362359123132</v>
+        <v>0.9035830400529201</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.24695000149432</v>
+        <v>13.22550319735372</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2886,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.658697838855011</v>
+        <v>0.674712330679116</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.658697838855011</v>
+        <v>0.674712330679116</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.658697838855011</v>
+        <v>-0.674712330679116</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.230093839660209</v>
+        <v>0.2356879614208338</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.230093839660209</v>
+        <v>0.2356879614208338</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1012862074668309</v>
+        <v>0.0956920857062061</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3016,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05082765215153476</v>
+        <v>0.05206339177569098</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05082765215153476</v>
+        <v>0.05206339177569098</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05082179445185925</v>
+        <v>-0.05205753407601547</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0001335505988786616</v>
+        <v>0.0001367975276640427</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0001335505988786616</v>
+        <v>0.0001367975276640427</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>8.944940112133838e-05</v>
+        <v>8.620247233595731e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.467989296569305e-05</v>
+        <v>1.503679564854757e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.467989296569305e-05</v>
+        <v>1.503679564854757e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>4.320107034306949e-06</v>
+        <v>3.96320435145243e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3211,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.33206667524193e-05</v>
+        <v>1.364452345304103e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.33206667524193e-05</v>
+        <v>1.364452345304103e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.02142146263343e-05</v>
+        <v>-1.053807132695603e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.935055866890377e-06</v>
+        <v>4.030726318940522e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.935055866890377e-06</v>
+        <v>4.030726318940522e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>6.4944133109623e-08</v>
+        <v>-3.072631894052152e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3341,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.877381227289496e-06</v>
+        <v>2.947337124244251e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.877381227289496e-06</v>
+        <v>2.947337124244251e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.877381227289496e-06</v>
+        <v>-2.947337124244251e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.206869825148095e-06</v>
+        <v>1.23621166568182e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.206869825148095e-06</v>
+        <v>1.23621166568182e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.984155694530947e-07</v>
+        <v>-4.277574099868199e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3471,13 +3471,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.737741921461616e-07</v>
+        <v>1.779990509740007e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.737741921461616e-07</v>
+        <v>1.779990509740007e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.737741921461616e-07</v>
+        <v>-1.779990509740007e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3536,13 +3536,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.374010266082916e-11</v>
+        <v>4.480352730734837e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.374010266082916e-11</v>
+        <v>4.480352730734837e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.310844010266083e-08</v>
+        <v>-1.310950352730735e-08</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9029202.172316257</v>
+        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9041800.627846856</v>
+        <v>9265671.732515046</v>
       </c>
     </row>
     <row r="28">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9029202.172316257</v>
+        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="32">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2671293.479198225</v>
+        <v>-2447422.374530034</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T11:44:13+00:00</t>
+          <t>2026-06-25T22:35:55+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>10201892.24990776</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1493041.19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>11694933.43990776</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>9253073.276984449</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>12598.4555305973</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>9265671.732515046</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9253073.276984449</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2447422.374530034</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>11700495.65151448</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>178920.973062644</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>10086500.94216282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>10086500.94216282</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-9253073.276984449</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>-459400.3016891367</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-01 → 2026-04-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=458085623, avalanche_c=84298393, base=45402126, ethereum=24996367, optimism=150997411, unichain=46845240</t>
+          <t>2026-04-01 → 2026-04-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T22:35:55+00:00</t>
+          <t>arbitrum=458085623, avalanche_c=84298393, base=45402126, ethereum=24996367, optimism=150997411, unichain=46845240</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:35:55+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>10201892.24990776</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1493041.19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>11694933.43990776</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>9253073.276984449</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>12598.4555305973</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>9265671.732515046</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>9253073.276984449</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>9253073.276984449</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2447422.374530034</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>11700495.65151448</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>178920.973062644</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>10086500.94216282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>10086500.94216282</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-9253073.276984449</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>-459400.3016891367</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-01 → 2026-04-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=458085623, avalanche_c=84298393, base=45402126, ethereum=24996367, optimism=150997411, unichain=46845240</t>
+          <t>2026-04-01 → 2026-04-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T11:44:13+00:00</t>
+          <t>arbitrum=458085623, avalanche_c=84298393, base=45402126, ethereum=24996367, optimism=150997411, unichain=46845240</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:35:55+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1493041.19</v>
+        <v>1506065.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11694933.43990776</v>
+        <v>11707957.62990776</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10086500.94216282</v>
+        <v>10086500.94216305</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11707957.62990776</v>
+        <v>11707957.62990799</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10086500.94216282</v>
+        <v>10086500.94216305</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>-459400.3016891367</v>
+        <v>-459400.3016889081</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25T22:35:55+00:00</t>
+          <t>2026-07-03T07:23:28+00:00</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>2780948.049307498</v>
+        <v>2780948.049307554</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2780948.049307498</v>
+        <v>2780948.049307554</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>3239887.004567656</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-458938.9552601578</v>
+        <v>-458938.9552601014</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -1184,13 +1184,13 @@
         <v>483436565.922284</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>-1.029929695e-07</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>-1.029929695e-07</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>379312.7793270081</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-379312.7793271481</v>
+        <v>-379312.779327111</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>179542.3842682067</v>
+        <v>179542.3842682066</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>160942.4965218921</v>
@@ -1708,31 +1708,31 @@
         <v>51670578.4489233</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>168816.6386304616</v>
+        <v>168816.6386304617</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>168816.6386304616</v>
+        <v>168816.6386304617</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57072716.55221559</v>
+        <v>57072716.55221562</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>135639.4461677168</v>
+        <v>135639.4461677169</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>135639.4461677168</v>
+        <v>135639.4461677169</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>33177.19246274477</v>
+        <v>33177.19246274478</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>5304002.847619672</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>172735.4277329785</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>172735.4277329785</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
@@ -1797,7 +1797,7 @@
         <v>119806.2308681482</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52929.19686484189</v>
+        <v>52929.19686483028</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -2163,13 +2163,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>4.44e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>4.44e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>11854.32656735484</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11854.32656735441</v>
+        <v>-11854.32656735439</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2228,13 +2228,13 @@
         <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>-7.25e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>-7.25e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>11809.37495579145</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11809.3749557911</v>
+        <v>-11809.37495579218</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2293,31 +2293,31 @@
         <v>2224.277443</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>-2.584619e-08</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>-2.584619e-08</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4819813.116676098</v>
+        <v>4819813.11667611</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11454.80399867989</v>
+        <v>11454.80399867992</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11454.80399867989</v>
+        <v>11454.80399867992</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11454.80399867623</v>
+        <v>-11454.80399870576</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2358,31 +2358,31 @@
         <v>-273029.0857638157</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>9546.424990317191</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>9546.424990317191</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>2903718.839188301</v>
+        <v>2903718.839188297</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6900.999969292277</v>
+        <v>6900.999969292268</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6900.999969292277</v>
+        <v>6900.999969292268</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2645.42502101628</v>
+        <v>2645.425021024923</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2423,31 +2423,31 @@
         <v>-203.1796532231052</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>4497.433544839263</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>4497.433544839263</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>1097625.680429284</v>
+        <v>1097625.680429272</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2608.625423615162</v>
+        <v>2608.625423615132</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2608.625423615162</v>
+        <v>2608.625423615132</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1888.808121192727</v>
+        <v>1888.808121224131</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2683,31 +2683,31 @@
         <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>-1.4761558479e-08</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>-1.4761558479e-08</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3222.097566494505</v>
+        <v>3222.097566510731</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.657661240249769</v>
+        <v>7.657661240288332</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.657661240249769</v>
+        <v>7.657661240288332</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.657661231180232</v>
+        <v>-7.65766125504989</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2748,31 +2748,31 @@
         <v>2489.957423</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>3.63071e-09</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>3.63071e-09</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>1260.904571864759</v>
+        <v>1260.904571865159</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.996675261490397</v>
+        <v>2.996675261491348</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.996675261490397</v>
+        <v>2.996675261491348</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.996675256859687</v>
+        <v>-2.996675257860638</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -3292,7 +3292,7 @@
         <v>4.030726318940522e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.072631894052152e-08</v>
+        <v>-3.07263189405215e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3528,31 +3528,31 @@
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>-1.7787e-09</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>-1.7787e-09</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>1.885188333333333e-08</v>
+        <v>1.903535e-08</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.480352730734837e-11</v>
+        <v>4.523955556323376e-11</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.480352730734837e-11</v>
+        <v>4.523955556323376e-11</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.310950352730735e-08</v>
+        <v>-1.823939555563234e-09</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>48.90651071720747</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="11">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>12598.4555305973</v>
+        <v>12587.56221525919</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9265671.732515046</v>
+        <v>9264231.53101651</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2447422.374530034</v>
+        <v>-2448851.682713232</v>
       </c>
     </row>
     <row r="17">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9253073.276984449</v>
+        <v>-9251643.968801251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>-459400.3016889081</v>
+        <v>-457970.9935057093</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-03T07:23:28+00:00</t>
+          <t>2026-07-07T00:31:51+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3239887.004567656</v>
+        <v>3239396.037664422</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3239887.004567656</v>
+        <v>3239396.037664422</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-458938.9552601014</v>
+        <v>-458447.9883568673</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1570350.042712735</v>
+        <v>1570112.074568668</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1570350.042712735</v>
+        <v>1570112.074568668</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1606024.957287254</v>
+        <v>1606262.925431321</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1138610.033839894</v>
+        <v>1138437.490834068</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1138610.033839894</v>
+        <v>1138437.490834068</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1138610.033839894</v>
+        <v>-1138437.490834068</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>702448.416245115</v>
+        <v>702341.968420509</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>702448.416245115</v>
+        <v>702341.968420509</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-124936.278809115</v>
+        <v>-124829.830984509</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>416117.1039425409</v>
+        <v>416054.0462724378</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>416117.1039425409</v>
+        <v>416054.0462724378</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>136994.935989797</v>
+        <v>137057.9936599001</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>379312.7793270081</v>
+        <v>379255.2989209443</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>379312.7793270081</v>
+        <v>379255.2989209443</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-379312.779327111</v>
+        <v>-379255.2989210472</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>339614.1689317927</v>
+        <v>339562.7043848564</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>304431.4712922591</v>
+        <v>304380.0067453228</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>90234.64471673773</v>
+        <v>90286.10926367404</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>242141.050625949</v>
+        <v>242104.3569876819</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>242141.050625949</v>
+        <v>242104.3569876819</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>72070.74814098052</v>
+        <v>72107.44177924756</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>237660.9310894051</v>
+        <v>237624.9163607457</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>237660.9310894051</v>
+        <v>237624.9163607457</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-228091.9196441936</v>
+        <v>-228055.9049155342</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237657.6999405303</v>
+        <v>237621.6857015136</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237657.6999405303</v>
+        <v>237621.6857015136</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-191372.2248975303</v>
+        <v>-191336.2106585136</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>241784.0867348476</v>
+        <v>241747.4471902746</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>216736.2024124731</v>
+        <v>216699.5628679</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>64241.43384035787</v>
+        <v>64278.07338493092</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>179542.3842682066</v>
+        <v>179515.1767241537</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>160942.4965218921</v>
+        <v>160915.2889778391</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>47703.96743750521</v>
+        <v>47731.17498155818</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>151594.1531974312</v>
+        <v>151571.1808802366</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>151594.1531974312</v>
+        <v>151571.1808802366</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>53192.81178212681</v>
+        <v>53215.78409932146</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>135639.4461677169</v>
+        <v>135618.8915993793</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>135639.4461677169</v>
+        <v>135618.8915993793</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>33177.19246274478</v>
+        <v>33197.74703108234</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>119806.2308681482</v>
+        <v>119788.0756380199</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>119806.2308681482</v>
+        <v>119788.0756380199</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52929.19686483028</v>
+        <v>52947.35209495854</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22974.15424933163</v>
+        <v>22970.67278551813</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22974.15424933163</v>
+        <v>22970.67278551813</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-22974.15424933163</v>
+        <v>-22970.67278551813</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>16884.25456645465</v>
+        <v>16881.6959555629</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>16884.25456645465</v>
+        <v>16881.6959555629</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1401.928819674936</v>
+        <v>1404.487430566681</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11867.89145340497</v>
+        <v>11866.09301354994</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11867.89145340497</v>
+        <v>11866.09301354994</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11867.89145340497</v>
+        <v>-11866.09301354994</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11854.32656735484</v>
+        <v>11852.53018309931</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11854.32656735484</v>
+        <v>11852.53018309931</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11854.32656735439</v>
+        <v>-11852.53018309886</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11809.37495579145</v>
+        <v>11807.58538342581</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11809.37495579145</v>
+        <v>11807.58538342581</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11809.37495579218</v>
+        <v>-11807.58538342653</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11454.80399867992</v>
+        <v>11453.06815738716</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11454.80399867992</v>
+        <v>11453.06815738716</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11454.80399870576</v>
+        <v>-11453.06815741301</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6900.999969292268</v>
+        <v>6899.954203628415</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6900.999969292268</v>
+        <v>6899.954203628415</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2645.425021024923</v>
+        <v>2646.470786688777</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2608.625423615132</v>
+        <v>2608.230117005944</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2608.625423615132</v>
+        <v>2608.230117005944</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1888.808121224131</v>
+        <v>1889.203427833319</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2327.796494051909</v>
+        <v>2327.443743775608</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2086.645895199707</v>
+        <v>2086.293144923406</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>618.4897711256187</v>
+        <v>618.8425214019194</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>816.6893728565566</v>
+        <v>816.5656131539095</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>816.6893728565566</v>
+        <v>816.5656131539095</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-691.3105368565565</v>
+        <v>-691.1867771539094</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>317.2799801865517</v>
+        <v>317.2319001241573</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>317.2799801865517</v>
+        <v>317.2319001241573</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133816.9457701865</v>
+        <v>-133816.8976901242</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2655,12 +2655,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2670,67 +2670,71 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>219995.8104343477</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-1.4761558479e-08</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-1.4761558479e-08</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3222.097566510731</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.657661240288332</v>
+        <v>0</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.657661240288332</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.65766125504989</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="R30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2739,40 +2743,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>10.263802</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2500.221225</v>
+        <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2489.957423</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3.63071e-09</v>
+        <v>-1.4761558479e-08</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>3.63071e-09</v>
+        <v>-1.4761558479e-08</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>1260.904571865159</v>
+        <v>3222.097566510731</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.996675261491348</v>
+        <v>7.656500811477123</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.996675261491348</v>
+        <v>7.656500811477123</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.996675257860638</v>
+        <v>-7.656500826238681</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2785,59 +2789,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>10.263802</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>2500.221225</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>98.58562175646877</v>
+        <v>2489.957423</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>3.63071e-09</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>3.63071e-09</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>380.1986824877172</v>
+        <v>1260.904571865159</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9035830400529201</v>
+        <v>2.996221150477273</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9035830400529201</v>
+        <v>2.996221150477273</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.22550319735372</v>
+        <v>-2.996221146846563</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2850,17 +2854,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2869,40 +2873,40 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>98.58562175646877</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>380.1986824877172</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.674712330679116</v>
+        <v>0.9034461126334254</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.674712330679116</v>
+        <v>0.9034461126334254</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.674712330679116</v>
+        <v>13.22564012477321</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2915,17 +2919,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2934,40 +2938,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2356879614208338</v>
+        <v>0.6746100859332034</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2356879614208338</v>
+        <v>0.6746100859332034</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0956920857062061</v>
+        <v>-0.6746100859332034</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2980,12 +2984,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2995,62 +2999,66 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05206339177569098</v>
+        <v>0</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05206339177569098</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05205753407601547</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="R35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3060,44 +3068,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.05756</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.057783</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.000223</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.000223</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.000223</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.05756</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0001367975276640427</v>
+        <v>0.235652245672604</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0001367975276640427</v>
+        <v>0.235652245672604</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>8.620247233595731e-05</v>
+        <v>0.09572780145443598</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3110,59 +3118,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.006327</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.006346</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.006327</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.503679564854757e-05</v>
+        <v>0.0520555021788637</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.503679564854757e-05</v>
+        <v>0.0520555021788637</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>3.96320435145243e-06</v>
+        <v>-0.0520496444791882</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3175,12 +3183,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3194,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>0.05756</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>0.057783</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.000223</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.000223</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.000223</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>0.05756</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.364452345304103e-05</v>
+        <v>0.0001367767976020274</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.364452345304103e-05</v>
+        <v>0.0001367767976020274</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.053807132695603e-05</v>
+        <v>8.622320239797261e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3240,17 +3248,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3259,40 +3267,40 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001696</v>
+        <v>0.006327</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.006346</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.9e-05</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.9e-05</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001696</v>
+        <v>0.006327</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>4.030726318940522e-06</v>
+        <v>1.503451699840214e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>4.030726318940522e-06</v>
+        <v>1.503451699840214e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.07263189405215e-08</v>
+        <v>3.965483001597859e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3305,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3320,44 +3328,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.947337124244251e-06</v>
+        <v>1.364245578542904e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.947337124244251e-06</v>
+        <v>1.364245578542904e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.947337124244251e-06</v>
+        <v>-1.053600365934404e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3370,17 +3378,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3389,40 +3397,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.001696</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.0017</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.001696</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.23621166568182e-06</v>
+        <v>4.030115509608034e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.23621166568182e-06</v>
+        <v>4.030115509608034e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.277574099868199e-07</v>
+        <v>-3.011550960803407e-08</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3435,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,14 +3458,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -3475,19 +3483,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.779990509740007e-07</v>
+        <v>2.94689048984662e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.779990509740007e-07</v>
+        <v>2.94689048984662e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.779990509740007e-07</v>
+        <v>-2.94689048984662e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3500,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3515,44 +3523,44 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-1.7787e-09</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-1.7787e-09</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>1.903535e-08</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.523955556323376e-11</v>
+        <v>1.236024332292604e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.523955556323376e-11</v>
+        <v>1.236024332292604e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.823939555563234e-09</v>
+        <v>-4.275700765976042e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3565,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3580,14 +3588,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3605,19 +3613,19 @@
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0</v>
+        <v>1.779720773040202e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0</v>
+        <v>1.779720773040202e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0</v>
+        <v>-1.779720773040202e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3630,12 +3638,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3645,7 +3653,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
@@ -3658,31 +3666,31 @@
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0</v>
+        <v>-1.7787e-09</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0</v>
+        <v>-1.7787e-09</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0</v>
+        <v>1.903535e-08</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0</v>
+        <v>4.523270003880736e-11</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>4.523270003880736e-11</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0</v>
+        <v>-1.823932700038807e-09</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3695,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3738,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3755,21 +3763,17 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3829,12 +3833,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3844,7 +3848,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3857,19 +3861,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-6.258474e-08</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-6.258474e-08</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>48.90651071720747</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3881,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-6.258474e-08</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3891,36 +3895,36 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>SDE (fixed)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3938,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3953,36 +3957,32 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3995,22 +3995,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>48.90651071720747</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4027,22 +4027,26 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4087,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4101,29 +4105,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4141,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4156,31 +4160,27 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,168 +4239,250 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>456780102.344065</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>573332157.534611</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>1134703231.016836</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4414,51 +4496,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>504861.558051</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>573332157.534611</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>867900893.337617</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>504861.558051</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>73619968.24222299</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>37138817.432463</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2988806180.523181</v>
+        <v>2988366178.220075</v>
       </c>
     </row>
     <row r="6">
@@ -4533,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1988806180.523181</v>
+        <v>1988366178.220075</v>
       </c>
     </row>
     <row r="8">
@@ -4543,7 +4681,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.04028621767610686</v>
+        <v>0.04028621393822291</v>
       </c>
     </row>
     <row r="9">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.0391410605085019</v>
+        <v>0.03914088815949029</v>
       </c>
     </row>
     <row r="12">
@@ -4583,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-11.45157167604957</v>
+        <v>-11.45325778732615</v>
       </c>
     </row>
     <row r="13">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9702873.433050597</v>
+        <v>9701444.124867398</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9431994.250047093</v>
+        <v>9430564.941863894</v>
       </c>
     </row>
     <row r="17">
@@ -4663,10 +4801,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1988806180.523181</v>
+        <v>1988366178.220075</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6454462.831073149</v>
+        <v>6453033.52288995</v>
       </c>
     </row>
     <row r="23">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>12598.4555305973</v>
+        <v>12587.56221525919</v>
       </c>
     </row>
     <row r="26">
@@ -4708,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9265671.732515046</v>
+        <v>9264231.53101651</v>
       </c>
     </row>
     <row r="28">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="32">
@@ -4745,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2447422.374530034</v>
+        <v>-2448851.682713232</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4875,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5035,6 +5173,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>12598.4555305973</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2431931968307834</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2431931968307834</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-11.1365085349426</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-11.1365085349426</v>
       </c>
     </row>
   </sheetData>
@@ -5174,16 +5392,16 @@
         <v>109055951.174984</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>83934283.91579673</v>
+        <v>84160428.00919972</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>81025902.18910897</v>
+        <v>81239757.97065578</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>130060790.0037368</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2784292546.534297</v>
+        <v>2783852546.659347</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5201,7 +5419,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>293968.6389684683</v>
+        <v>293920.6468481718</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>374578.727875959</v>
@@ -5223,16 +5441,16 @@
         <v>109133547.016997</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>81070524.8666583</v>
+        <v>81298220.43761531</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>75798768.87500143</v>
+        <v>76011072.11242218</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>123404206.9728645</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2867657513.15868</v>
+        <v>2867217514.350302</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5250,7 +5468,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>303061.5086135139</v>
+        <v>303013.5166095516</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>382071.5092839777</v>
@@ -5272,16 +5490,16 @@
         <v>109105650.4924593</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>76123440.04999478</v>
+        <v>76350330.16833378</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>75714944.50432792</v>
+        <v>75928052.36207461</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>123411196.5267537</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2875295500.667339</v>
+        <v>2874855502.691253</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5299,7 +5517,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>303894.6070669644</v>
+        <v>303846.6151537827</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>382353.5908336217</v>
@@ -5321,16 +5539,16 @@
         <v>109123776.7824347</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>83542493.66401881</v>
+        <v>83779654.8388468</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>75690258.91133398</v>
+        <v>75893095.51486818</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>123405060.7543267</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2872629206.232289</v>
+        <v>2872189208.453927</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5348,7 +5566,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>303603.7862496005</v>
+        <v>303555.7943579851</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>382870.6039957182</v>
@@ -5370,16 +5588,16 @@
         <v>109127522.7862754</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>86558535.6429214</v>
+        <v>86806841.8404364</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>74444392.75988562</v>
+        <v>74636086.29818742</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>123403918.716754</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2879664844.277337</v>
+        <v>2879224844.541521</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5397,7 +5615,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>304371.1846209283</v>
+        <v>304323.1925158073</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>383831.3648336361</v>
@@ -5419,16 +5637,16 @@
         <v>109241926.6840944</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>55515650.13090748</v>
+        <v>55735869.73527548</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>74366553.28453328</v>
+        <v>74586331.02769235</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>112927513.3486385</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2914905338.478153</v>
+        <v>2914465341.130626</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5446,7 +5664,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>308214.9721610684</v>
+        <v>308166.9803164455</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>383150.5056369744</v>
@@ -5468,16 +5686,16 @@
         <v>109305198.8012233</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>79109652.47887604</v>
+        <v>79336065.29467803</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>77054699.32011929</v>
+        <v>77268285.11342053</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>111032090.9637735</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2902686749.231011</v>
+        <v>2902246750.621908</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5495,7 +5713,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>306882.2535891147</v>
+        <v>306834.2616068879</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>384484.6224839138</v>
@@ -5517,16 +5735,16 @@
         <v>109289928.5655661</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>56675900.95969198</v>
+        <v>56886236.73001598</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>74503713.8442512</v>
+        <v>74733377.00458194</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>106296252.8520661</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2907586309.263426</v>
+        <v>2907146310.332771</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5544,7 +5762,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>307416.6634557144</v>
+        <v>307368.671438415</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>381775.6535496546</v>
@@ -5566,16 +5784,16 @@
         <v>109349782.7302168</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>54193645.98368105</v>
+        <v>54395587.57499404</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>78737127.87731043</v>
+        <v>78975186.58280288</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>106289452.9998598</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2905392368.002785</v>
+        <v>2904952367.705979</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5593,7 +5811,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>307177.3636311037</v>
+        <v>307129.371464794</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>381733.1447470395</v>
@@ -5615,16 +5833,16 @@
         <v>109304061.5112718</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>51076302.50534543</v>
+        <v>51259235.19849242</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>75242537.44162388</v>
+        <v>75499611.29075068</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>106318077.1275745</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2905301385.701985</v>
+        <v>2904861379.159712</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5642,7 +5860,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>307167.4399157268</v>
+        <v>307119.447068205</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>381000.1725228651</v>
@@ -5664,16 +5882,16 @@
         <v>109337373.1213049</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>51145031.32584467</v>
+        <v>51334636.13208666</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>73579380.95193422</v>
+        <v>73829781.30064061</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>106356377.8226287</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2898585065.373258</v>
+        <v>2898145060.218309</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5691,7 +5909,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>306434.870495785</v>
+        <v>306386.877799583</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>380101.5050144822</v>
@@ -5713,16 +5931,16 @@
         <v>109342328.3371183</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>51970946.78532917</v>
+        <v>52179667.35163317</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>71375240.03334759</v>
+        <v>71606519.76113771</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>106336984.9487036</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2971139955.977927</v>
+        <v>2970699955.683833</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5740,7 +5958,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>314348.6523767441</v>
+        <v>314300.6602107302</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>387863.3849071475</v>
@@ -5762,16 +5980,16 @@
         <v>109046834.1026236</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>50529324.09846896</v>
+        <v>50727024.80344096</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>69510472.6803965</v>
+        <v>69752778.95967042</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>106485554.4875584</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2789291999.453163</v>
+        <v>2788851992.468917</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5789,7 +6007,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>294513.9444550358</v>
+        <v>294465.9515593068</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>367652.0134779223</v>
@@ -5811,16 +6029,16 @@
         <v>109458620.2372267</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>49882975.1971824</v>
+        <v>50066401.91310941</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>67540680.80231147</v>
+        <v>67797269.16444007</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>106432974.8514239</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2792630539.363278</v>
+        <v>2792190524.285223</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5838,7 +6056,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>294878.0891243936</v>
+        <v>294830.0953458483</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>367769.9874829751</v>
@@ -5860,16 +6078,16 @@
         <v>109518837.8396468</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>51274439.44802884</v>
+        <v>51485609.60263484</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>66491002.67769836</v>
+        <v>66719834.4557837</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>106442587.2808068</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2803977278.094051</v>
+        <v>2803537276.16136</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5887,7 +6105,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>296115.7123173613</v>
+        <v>296067.7199726206</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>369052.5068981854</v>
@@ -5909,16 +6127,16 @@
         <v>109539351.8666015</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>52169788.46302108</v>
+        <v>52383239.81585507</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>67286649.27408095</v>
+        <v>67513198.04280752</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>106455238.2665053</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2799846207.708704</v>
+        <v>2799406207.587144</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5936,7 +6154,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>295665.1239463767</v>
+        <v>295617.1317991815</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>368789.9779535549</v>
@@ -5958,16 +6176,16 @@
         <v>109507779.6615873</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>50904742.8989519</v>
+        <v>51111523.9698009</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>66799476.11261413</v>
+        <v>67032698.6111996</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>106530285.11483</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2798188841.046695</v>
+        <v>2797748837.47726</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5985,7 +6203,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>295484.3499399574</v>
+        <v>295436.3574166922</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>368422.8260497338</v>
@@ -6007,16 +6225,16 @@
         <v>109623263.8502044</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>50485214.99143847</v>
+        <v>50679725.96653047</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>68028126.6911139</v>
+        <v>68273622.92989354</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>106209842.7768683</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2823871284.655643</v>
+        <v>2823431277.441771</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6034,7 +6252,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>298285.611925158</v>
+        <v>298237.619004383</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>371289.9860909391</v>
@@ -6056,16 +6274,16 @@
         <v>109342580.9053197</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>50143398.95539194</v>
+        <v>50370029.34486293</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>35619205.44664249</v>
+        <v>35832584.38892286</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>134869772.9750939</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2876150993.633924</v>
+        <v>2875710984.302173</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6083,7 +6301,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>303987.9182784049</v>
+        <v>303939.9251266263</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>376515.4807739933</v>
@@ -6105,16 +6323,16 @@
         <v>108244438.4938705</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>50106958.71182571</v>
+        <v>50344611.05061571</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>30889433.30164777</v>
+        <v>31091792.80012321</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>166906447.5117323</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2990808988.000631</v>
+        <v>2990368976.163366</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6132,7 +6350,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>316494.0133295352</v>
+        <v>316446.0199044726</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>391876.2700847145</v>
@@ -6154,16 +6372,16 @@
         <v>108452809.4223091</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>50725251.6702591</v>
+        <v>50944392.4217291</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>54316080.27749412</v>
+        <v>54536944.43641728</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>174905990.8713613</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3135663170.326231</v>
+        <v>3135223165.415838</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6181,7 +6399,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>332293.6981463116</v>
+        <v>332245.705476784</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>411193.871491632</v>
@@ -6203,16 +6421,16 @@
         <v>108810545.2478995</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>50363491.24509695</v>
+        <v>50565289.64839695</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>67704870.85992657</v>
+        <v>67943080.25770484</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>191459906.6813183</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3211729936.25096</v>
+        <v>3211289928.449882</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6230,7 +6448,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>334415.2492646032</v>
+        <v>334368.4188951939</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>414590.4869628215</v>
@@ -6252,16 +6470,16 @@
         <v>108790788.519045</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>50461527.69762992</v>
+        <v>50684526.19835092</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>51095777.99769017</v>
+        <v>51312784.48707948</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>150458263.8530219</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3292539380.057715</v>
+        <v>3292099375.067605</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6279,7 +6497,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>343015.8606536701</v>
+        <v>342969.0305834343</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>417067.874719601</v>
@@ -6301,16 +6519,16 @@
         <v>108778836.5352057</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>51229919.97055995</v>
+        <v>51443892.32589994</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>56536069.61801664</v>
+        <v>56762100.0283076</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>148940725.8800582</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3297029907.00169</v>
+        <v>3296589904.23606</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6328,7 +6546,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>343493.7908974375</v>
+        <v>343446.9610639547</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>418043.8151805623</v>
@@ -6350,16 +6568,16 @@
         <v>109012385.0330893</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>51077651.60920416</v>
+        <v>51294807.23677015</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>58449745.30648443</v>
+        <v>58672592.76287633</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>140084321.8061661</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3276806846.393368</v>
+        <v>3276366843.30941</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6377,7 +6595,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>341341.4349697607</v>
+        <v>341294.6051023981</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>415161.1900272233</v>
@@ -6399,16 +6617,16 @@
         <v>109013131.1815182</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>51589907.91751318</v>
+        <v>51815665.60647119</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>58099362.01924805</v>
+        <v>58313605.34159191</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>154475144.3495293</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3312690633.063111</v>
+        <v>3312250632.051809</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6426,7 +6644,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>345160.5740428209</v>
+        <v>345113.7443960527</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>420529.2631189993</v>
@@ -6448,16 +6666,16 @@
         <v>109024047.6455294</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>59429042.91027177</v>
+        <v>59681133.32946277</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>58855219.37465746</v>
+        <v>59043123.38174734</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>130752789.7099153</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3258562512.409602</v>
+        <v>3258122517.983321</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6475,7 +6693,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>339399.6764418596</v>
+        <v>339352.8474959402</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>413159.5105374671</v>
@@ -6497,16 +6715,16 @@
         <v>108998604.7903199</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>67003312.22578653</v>
+        <v>67253573.46902853</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>69754438.78971349</v>
+        <v>69944172.19441128</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>135699774.815579</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3362562386.918674</v>
+        <v>3362122392.270734</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6524,7 +6742,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>350468.4632448382</v>
+        <v>350421.6342753276</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>426718.2485197183</v>
@@ -6546,16 +6764,16 @@
         <v>108996254.8996352</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>84852106.09446886</v>
+        <v>85087299.19721687</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>78406141.98836392</v>
+        <v>78610948.4058989</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>131931405.5965129</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2779633695.09579</v>
+        <v>2779193695.575507</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6573,7 +6791,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>288426.9132758148</v>
+        <v>288380.0837877369</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>367095.8463379316</v>
@@ -6595,16 +6813,16 @@
         <v>109000464.1101925</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>86309975.97272643</v>
+        <v>86560462.48908544</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>70281418.59588619</v>
+        <v>70470930.59786333</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>129864360.3284257</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3377064033.323725</v>
+        <v>3376624034.805389</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6622,7 +6840,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>352011.8846490217</v>
+        <v>351965.0552675817</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>429751.7101215186</v>
@@ -6647,7 +6865,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9431994.250047093</v>
+        <v>9430564.941863894</v>
       </c>
       <c r="O37" s="12" t="n">
         <v>11700495.65151448</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10086500.94216282</v>
+        <v>10086500.94216305</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11707957.62990776</v>
+        <v>11707957.62990799</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="11">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>12598.4555305973</v>
+        <v>12587.56221525919</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9265671.732515046</v>
+        <v>9264231.53101651</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2447422.374530034</v>
+        <v>-2448851.682713232</v>
       </c>
     </row>
     <row r="17">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10086500.94216282</v>
+        <v>10086500.94216305</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9253073.276984449</v>
+        <v>-9251643.968801251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>-459400.3016891367</v>
+        <v>-457970.9935057093</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25T22:35:55+00:00</t>
+          <t>2026-07-07T00:31:51+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -855,13 +855,13 @@
         <v>351891839.0803402</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>2780948.049307498</v>
+        <v>2780948.049307554</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>2780948.049307498</v>
+        <v>2780948.049307554</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3239887.004567656</v>
+        <v>3239396.037664422</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3239887.004567656</v>
+        <v>3239396.037664422</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-458938.9552601578</v>
+        <v>-458447.9883568673</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1570350.042712735</v>
+        <v>1570112.074568668</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1570350.042712735</v>
+        <v>1570112.074568668</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1606024.957287254</v>
+        <v>1606262.925431321</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1138610.033839894</v>
+        <v>1138437.490834068</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1138610.033839894</v>
+        <v>1138437.490834068</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1138610.033839894</v>
+        <v>-1138437.490834068</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>702448.416245115</v>
+        <v>702341.968420509</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>702448.416245115</v>
+        <v>702341.968420509</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-124936.278809115</v>
+        <v>-124829.830984509</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>416117.1039425409</v>
+        <v>416054.0462724378</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>416117.1039425409</v>
+        <v>416054.0462724378</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>136994.935989797</v>
+        <v>137057.9936599001</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1184,13 +1184,13 @@
         <v>483436565.922284</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>-1.029929695e-07</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-1.400229695e-07</v>
+        <v>-1.029929695e-07</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>379312.7793270081</v>
+        <v>379255.2989209443</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>379312.7793270081</v>
+        <v>379255.2989209443</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-379312.7793271481</v>
+        <v>-379255.2989210472</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>339614.1689317927</v>
+        <v>339562.7043848564</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>304431.4712922591</v>
+        <v>304380.0067453228</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>90234.64471673773</v>
+        <v>90286.10926367404</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>242141.050625949</v>
+        <v>242104.3569876819</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>242141.050625949</v>
+        <v>242104.3569876819</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>72070.74814098052</v>
+        <v>72107.44177924756</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>237660.9310894051</v>
+        <v>237624.9163607457</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>237660.9310894051</v>
+        <v>237624.9163607457</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-228091.9196441936</v>
+        <v>-228055.9049155342</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237657.6999405303</v>
+        <v>237621.6857015136</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237657.6999405303</v>
+        <v>237621.6857015136</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-191372.2248975303</v>
+        <v>-191336.2106585136</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>241784.0867348476</v>
+        <v>241747.4471902746</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>216736.2024124731</v>
+        <v>216699.5628679</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>64241.43384035787</v>
+        <v>64278.07338493092</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>179542.3842682067</v>
+        <v>179515.1767241537</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>160942.4965218921</v>
+        <v>160915.2889778391</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>47703.96743750521</v>
+        <v>47731.17498155818</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>151594.1531974312</v>
+        <v>151571.1808802366</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>151594.1531974312</v>
+        <v>151571.1808802366</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>53192.81178212681</v>
+        <v>53215.78409932146</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1708,31 +1708,31 @@
         <v>51670578.4489233</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>168816.6386304616</v>
+        <v>168816.6386304617</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>168816.6386304616</v>
+        <v>168816.6386304617</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57072716.55221559</v>
+        <v>57072716.55221562</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>135639.4461677168</v>
+        <v>135618.8915993793</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>135639.4461677168</v>
+        <v>135618.8915993793</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>33177.19246274477</v>
+        <v>33197.74703108234</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>5304002.847619672</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>172735.4277329785</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>172735.4277329901</v>
+        <v>172735.4277329785</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>119806.2308681482</v>
+        <v>119788.0756380199</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>119806.2308681482</v>
+        <v>119788.0756380199</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52929.19686484189</v>
+        <v>52947.35209495854</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22974.15424933163</v>
+        <v>22970.67278551813</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22974.15424933163</v>
+        <v>22970.67278551813</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-22974.15424933163</v>
+        <v>-22970.67278551813</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>16884.25456645465</v>
+        <v>16881.6959555629</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>16884.25456645465</v>
+        <v>16881.6959555629</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1401.928819674936</v>
+        <v>1404.487430566681</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11867.89145340497</v>
+        <v>11866.09301354994</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11867.89145340497</v>
+        <v>11866.09301354994</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11867.89145340497</v>
+        <v>-11866.09301354994</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2163,13 +2163,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>4.44e-10</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4.24e-10</v>
+        <v>4.44e-10</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11854.32656735484</v>
+        <v>11852.53018309931</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11854.32656735484</v>
+        <v>11852.53018309931</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11854.32656735441</v>
+        <v>-11852.53018309886</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2228,13 +2228,13 @@
         <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>-7.25e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.55e-10</v>
+        <v>-7.25e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11809.37495579145</v>
+        <v>11807.58538342581</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11809.37495579145</v>
+        <v>11807.58538342581</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11809.3749557911</v>
+        <v>-11807.58538342653</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2293,31 +2293,31 @@
         <v>2224.277443</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>-2.584619e-08</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>3.65681e-09</v>
+        <v>-2.584619e-08</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4819813.116676098</v>
+        <v>4819813.11667611</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11454.80399867989</v>
+        <v>11453.06815738716</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11454.80399867989</v>
+        <v>11453.06815738716</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11454.80399867623</v>
+        <v>-11453.06815741301</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2358,31 +2358,31 @@
         <v>-273029.0857638157</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>9546.424990317191</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>9546.424990308558</v>
+        <v>9546.424990317191</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>2903718.839188301</v>
+        <v>2903718.839188297</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6900.999969292277</v>
+        <v>6899.954203628415</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6900.999969292277</v>
+        <v>6899.954203628415</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2645.42502101628</v>
+        <v>2646.470786688777</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2423,31 +2423,31 @@
         <v>-203.1796532231052</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>4497.433544839263</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4497.433544807889</v>
+        <v>4497.433544839263</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>1097625.680429284</v>
+        <v>1097625.680429272</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2608.625423615162</v>
+        <v>2608.230117005944</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2608.625423615162</v>
+        <v>2608.230117005944</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1888.808121192727</v>
+        <v>1889.203427833319</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2327.796494051909</v>
+        <v>2327.443743775608</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2086.645895199707</v>
+        <v>2086.293144923406</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>618.4897711256187</v>
+        <v>618.8425214019194</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>816.6893728565566</v>
+        <v>816.5656131539095</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>816.6893728565566</v>
+        <v>816.5656131539095</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-691.3105368565565</v>
+        <v>-691.1867771539094</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>317.2799801865517</v>
+        <v>317.2319001241573</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>317.2799801865517</v>
+        <v>317.2319001241573</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133816.9457701865</v>
+        <v>-133816.8976901242</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2655,12 +2655,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2670,67 +2670,71 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>219995.8104343477</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>9.069536521e-09</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3222.097566494505</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>7.657661240249769</v>
+        <v>0</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>7.657661240249769</v>
+        <v>-11.1365085349426</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-7.657661231180232</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0</v>
+        <v>220006.9469428827</v>
       </c>
       <c r="R30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2739,40 +2743,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>10.263802</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2500.221225</v>
+        <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2489.957423</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>-1.4761558479e-08</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4.63071e-09</v>
+        <v>-1.4761558479e-08</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>1260.904571864759</v>
+        <v>3222.097566510731</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>2.996675261490397</v>
+        <v>7.656500811477123</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>2.996675261490397</v>
+        <v>7.656500811477123</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-2.996675256859687</v>
+        <v>-7.656500826238681</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2785,59 +2789,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>10.263802</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>2500.221225</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>98.58562175646877</v>
+        <v>2489.957423</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>3.63071e-09</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>3.63071e-09</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>380.1986824877172</v>
+        <v>1260.904571865159</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9035830400529201</v>
+        <v>2.996221150477273</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9035830400529201</v>
+        <v>2.996221150477273</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.22550319735372</v>
+        <v>-2.996221146846563</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2850,17 +2854,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2869,40 +2873,40 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>98.58562175646877</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>380.1986824877172</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.674712330679116</v>
+        <v>0.9034461126334254</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.674712330679116</v>
+        <v>0.9034461126334254</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.674712330679116</v>
+        <v>13.22564012477321</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2915,17 +2919,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2934,40 +2938,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2356879614208338</v>
+        <v>0.6746100859332034</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2356879614208338</v>
+        <v>0.6746100859332034</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0956920857062061</v>
+        <v>-0.6746100859332034</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2980,12 +2984,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2995,62 +2999,66 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>5.857699675505699e-06</v>
+        <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.9066008120297</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.05206339177569098</v>
+        <v>0</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.05206339177569098</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.05205753407601547</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="R35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3060,44 +3068,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.05756</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.057783</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.000223</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.000223</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.000223</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.05756</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0001367975276640427</v>
+        <v>0.235652245672604</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0001367975276640427</v>
+        <v>0.235652245672604</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>8.620247233595731e-05</v>
+        <v>0.09572780145443598</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3110,59 +3118,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.006327</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.006346</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.9e-05</v>
+        <v>5.857699675505699e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.006327</v>
+        <v>21.9066008120297</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.503679564854757e-05</v>
+        <v>0.0520555021788637</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.503679564854757e-05</v>
+        <v>0.0520555021788637</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>3.96320435145243e-06</v>
+        <v>-0.0520496444791882</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3175,12 +3183,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3194,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>0.05756</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>0.057783</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.000223</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.000223</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.106452126085e-06</v>
+        <v>0.000223</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.005741176637971351</v>
+        <v>0.05756</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.364452345304103e-05</v>
+        <v>0.0001367767976020274</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.364452345304103e-05</v>
+        <v>0.0001367767976020274</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.053807132695603e-05</v>
+        <v>8.622320239797261e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3240,17 +3248,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3259,40 +3267,40 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001696</v>
+        <v>0.006327</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.006346</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.9e-05</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.9e-05</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001696</v>
+        <v>0.006327</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>4.030726318940522e-06</v>
+        <v>1.503451699840214e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>4.030726318940522e-06</v>
+        <v>1.503451699840214e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-3.072631894052152e-08</v>
+        <v>3.965483001597859e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3305,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3320,44 +3328,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0</v>
+        <v>3.106452126085e-06</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005741176637971351</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.947337124244251e-06</v>
+        <v>1.364245578542904e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.947337124244251e-06</v>
+        <v>1.364245578542904e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.947337124244251e-06</v>
+        <v>-1.053600365934404e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3370,17 +3378,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3389,40 +3397,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.001696</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.0017</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>8.08454255695e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.000520158110250329</v>
+        <v>0.001696</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.23621166568182e-06</v>
+        <v>4.030115509608034e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.23621166568182e-06</v>
+        <v>4.030115509608034e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.277574099868199e-07</v>
+        <v>-3.011550960803407e-08</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3435,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,14 +3458,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -3475,19 +3483,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.779990509740007e-07</v>
+        <v>2.94689048984662e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.779990509740007e-07</v>
+        <v>2.94689048984662e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.779990509740007e-07</v>
+        <v>-2.94689048984662e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3500,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3515,44 +3523,44 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>-1.30647e-08</v>
+        <v>8.08454255695e-07</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>1.885188333333333e-08</v>
+        <v>0.000520158110250329</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>4.480352730734837e-11</v>
+        <v>1.236024332292604e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>4.480352730734837e-11</v>
+        <v>1.236024332292604e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.310950352730735e-08</v>
+        <v>-4.275700765976042e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3565,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3580,14 +3588,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -3605,19 +3613,19 @@
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0</v>
+        <v>1.779720773040202e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0</v>
+        <v>1.779720773040202e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0</v>
+        <v>-1.779720773040202e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3630,12 +3638,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3645,7 +3653,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
@@ -3658,31 +3666,31 @@
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0</v>
+        <v>-1.7787e-09</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0</v>
+        <v>-1.7787e-09</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0</v>
+        <v>1.903535e-08</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0</v>
+        <v>4.523270003880736e-11</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>4.523270003880736e-11</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0</v>
+        <v>-1.823932700038807e-09</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3695,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3738,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3755,21 +3763,17 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3829,12 +3833,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3844,7 +3848,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3857,19 +3861,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>48.90651074914867</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3881,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.1369574e-07</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3891,36 +3895,36 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>SDE (fixed)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3938,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3953,36 +3957,32 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3995,22 +3995,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>48.90651071720747</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>-6.258474e-08</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4027,22 +4027,26 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4087,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4101,29 +4105,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4141,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4156,31 +4160,27 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,168 +4239,250 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>456780102.344065</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>573332157.534611</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>867900893.337617</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>1134703231.016836</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4414,51 +4496,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>504861.558051</v>
+        <v>456780102.344065</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>573332157.534611</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>867900893.337617</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>504861.558051</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>73619968.24222299</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>37138817.432463</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2988806180.523181</v>
+        <v>2988366178.220075</v>
       </c>
     </row>
     <row r="6">
@@ -4533,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1988806180.523181</v>
+        <v>1988366178.220075</v>
       </c>
     </row>
     <row r="8">
@@ -4543,7 +4681,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.04028621767610686</v>
+        <v>0.04028621393822291</v>
       </c>
     </row>
     <row r="9">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.0391410605085019</v>
+        <v>0.03914088815949029</v>
       </c>
     </row>
     <row r="12">
@@ -4583,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-11.45157167604957</v>
+        <v>-11.45325778732615</v>
       </c>
     </row>
     <row r="13">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9702873.433050597</v>
+        <v>9701444.124867398</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9431994.250047093</v>
+        <v>9430564.941863894</v>
       </c>
     </row>
     <row r="17">
@@ -4663,10 +4801,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1988806180.523181</v>
+        <v>1988366178.220075</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6454462.831073149</v>
+        <v>6453033.52288995</v>
       </c>
     </row>
     <row r="23">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>12598.4555305973</v>
+        <v>12587.56221525919</v>
       </c>
     </row>
     <row r="26">
@@ -4708,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9265671.732515046</v>
+        <v>9264231.53101651</v>
       </c>
     </row>
     <row r="28">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9253073.276984449</v>
+        <v>9251643.968801251</v>
       </c>
     </row>
     <row r="32">
@@ -4745,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2447422.374530034</v>
+        <v>-2448851.682713232</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4875,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5035,6 +5173,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>12598.4555305973</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2431931968307834</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2431931968307834</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-11.1365085349426</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-11.1365085349426</v>
       </c>
     </row>
   </sheetData>
@@ -5174,16 +5392,16 @@
         <v>109055951.174984</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>83934283.91579673</v>
+        <v>84160428.00919972</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>81025902.18910897</v>
+        <v>81239757.97065578</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>130060790.0037368</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2784292546.534297</v>
+        <v>2783852546.659347</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5201,7 +5419,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>293968.6389684683</v>
+        <v>293920.6468481718</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>374578.727875959</v>
@@ -5223,16 +5441,16 @@
         <v>109133547.016997</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>81070524.8666583</v>
+        <v>81298220.43761531</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>75798768.87500143</v>
+        <v>76011072.11242218</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>123404206.9728645</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2867657513.15868</v>
+        <v>2867217514.350302</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5250,7 +5468,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>303061.5086135139</v>
+        <v>303013.5166095516</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>382071.5092839777</v>
@@ -5272,16 +5490,16 @@
         <v>109105650.4924593</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>76123440.04999478</v>
+        <v>76350330.16833378</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>75714944.50432792</v>
+        <v>75928052.36207461</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>123411196.5267537</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2875295500.667339</v>
+        <v>2874855502.691253</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5299,7 +5517,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>303894.6070669644</v>
+        <v>303846.6151537827</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>382353.5908336217</v>
@@ -5321,16 +5539,16 @@
         <v>109123776.7824347</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>83542493.66401881</v>
+        <v>83779654.8388468</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>75690258.91133398</v>
+        <v>75893095.51486818</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>123405060.7543267</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2872629206.232289</v>
+        <v>2872189208.453927</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5348,7 +5566,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>303603.7862496005</v>
+        <v>303555.7943579851</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>382870.6039957182</v>
@@ -5370,16 +5588,16 @@
         <v>109127522.7862754</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>86558535.6429214</v>
+        <v>86806841.8404364</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>74444392.75988562</v>
+        <v>74636086.29818742</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>123403918.716754</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2879664844.277337</v>
+        <v>2879224844.541521</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5397,7 +5615,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>304371.1846209283</v>
+        <v>304323.1925158073</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>383831.3648336361</v>
@@ -5419,16 +5637,16 @@
         <v>109241926.6840944</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>55515650.13090748</v>
+        <v>55735869.73527548</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>74366553.28453328</v>
+        <v>74586331.02769235</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>112927513.3486385</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2914905338.478153</v>
+        <v>2914465341.130626</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5446,7 +5664,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>308214.9721610684</v>
+        <v>308166.9803164455</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>383150.5056369744</v>
@@ -5468,16 +5686,16 @@
         <v>109305198.8012233</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>79109652.47887604</v>
+        <v>79336065.29467803</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>77054699.32011929</v>
+        <v>77268285.11342053</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>111032090.9637735</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2902686749.231011</v>
+        <v>2902246750.621908</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5495,7 +5713,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>306882.2535891147</v>
+        <v>306834.2616068879</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>384484.6224839138</v>
@@ -5517,16 +5735,16 @@
         <v>109289928.5655661</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>56675900.95969198</v>
+        <v>56886236.73001598</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>74503713.8442512</v>
+        <v>74733377.00458194</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>106296252.8520661</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2907586309.263426</v>
+        <v>2907146310.332771</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5544,7 +5762,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>307416.6634557144</v>
+        <v>307368.671438415</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>381775.6535496546</v>
@@ -5566,16 +5784,16 @@
         <v>109349782.7302168</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>54193645.98368105</v>
+        <v>54395587.57499404</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>78737127.87731043</v>
+        <v>78975186.58280288</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>106289452.9998598</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2905392368.002785</v>
+        <v>2904952367.705979</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5593,7 +5811,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>307177.3636311037</v>
+        <v>307129.371464794</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>381733.1447470395</v>
@@ -5615,16 +5833,16 @@
         <v>109304061.5112718</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>51076302.50534543</v>
+        <v>51259235.19849242</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>75242537.44162388</v>
+        <v>75499611.29075068</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>106318077.1275745</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2905301385.701985</v>
+        <v>2904861379.159712</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5642,7 +5860,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>307167.4399157268</v>
+        <v>307119.447068205</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>381000.1725228651</v>
@@ -5664,16 +5882,16 @@
         <v>109337373.1213049</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>51145031.32584467</v>
+        <v>51334636.13208666</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>73579380.95193422</v>
+        <v>73829781.30064061</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>106356377.8226287</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2898585065.373258</v>
+        <v>2898145060.218309</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5691,7 +5909,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>306434.870495785</v>
+        <v>306386.877799583</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>380101.5050144822</v>
@@ -5713,16 +5931,16 @@
         <v>109342328.3371183</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>51970946.78532917</v>
+        <v>52179667.35163317</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>71375240.03334759</v>
+        <v>71606519.76113771</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>106336984.9487036</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2971139955.977927</v>
+        <v>2970699955.683833</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5740,7 +5958,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>314348.6523767441</v>
+        <v>314300.6602107302</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>387863.3849071475</v>
@@ -5762,16 +5980,16 @@
         <v>109046834.1026236</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>50529324.09846896</v>
+        <v>50727024.80344096</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>69510472.6803965</v>
+        <v>69752778.95967042</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>106485554.4875584</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>2789291999.453163</v>
+        <v>2788851992.468917</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5789,7 +6007,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>294513.9444550358</v>
+        <v>294465.9515593068</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>367652.0134779223</v>
@@ -5811,16 +6029,16 @@
         <v>109458620.2372267</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>49882975.1971824</v>
+        <v>50066401.91310941</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>67540680.80231147</v>
+        <v>67797269.16444007</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>106432974.8514239</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2792630539.363278</v>
+        <v>2792190524.285223</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5838,7 +6056,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>294878.0891243936</v>
+        <v>294830.0953458483</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>367769.9874829751</v>
@@ -5860,16 +6078,16 @@
         <v>109518837.8396468</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>51274439.44802884</v>
+        <v>51485609.60263484</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>66491002.67769836</v>
+        <v>66719834.4557837</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>106442587.2808068</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2803977278.094051</v>
+        <v>2803537276.16136</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5887,7 +6105,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>296115.7123173613</v>
+        <v>296067.7199726206</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>369052.5068981854</v>
@@ -5909,16 +6127,16 @@
         <v>109539351.8666015</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>52169788.46302108</v>
+        <v>52383239.81585507</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>67286649.27408095</v>
+        <v>67513198.04280752</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>106455238.2665053</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2799846207.708704</v>
+        <v>2799406207.587144</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5936,7 +6154,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>295665.1239463767</v>
+        <v>295617.1317991815</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>368789.9779535549</v>
@@ -5958,16 +6176,16 @@
         <v>109507779.6615873</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>50904742.8989519</v>
+        <v>51111523.9698009</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>66799476.11261413</v>
+        <v>67032698.6111996</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>106530285.11483</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2798188841.046695</v>
+        <v>2797748837.47726</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -5985,7 +6203,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>295484.3499399574</v>
+        <v>295436.3574166922</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>368422.8260497338</v>
@@ -6007,16 +6225,16 @@
         <v>109623263.8502044</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>50485214.99143847</v>
+        <v>50679725.96653047</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>68028126.6911139</v>
+        <v>68273622.92989354</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>106209842.7768683</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2823871284.655643</v>
+        <v>2823431277.441771</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6034,7 +6252,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>298285.611925158</v>
+        <v>298237.619004383</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>371289.9860909391</v>
@@ -6056,16 +6274,16 @@
         <v>109342580.9053197</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>50143398.95539194</v>
+        <v>50370029.34486293</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>35619205.44664249</v>
+        <v>35832584.38892286</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>134869772.9750939</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2876150993.633924</v>
+        <v>2875710984.302173</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6083,7 +6301,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>303987.9182784049</v>
+        <v>303939.9251266263</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>376515.4807739933</v>
@@ -6105,16 +6323,16 @@
         <v>108244438.4938705</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>50106958.71182571</v>
+        <v>50344611.05061571</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>30889433.30164777</v>
+        <v>31091792.80012321</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>166906447.5117323</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2990808988.000631</v>
+        <v>2990368976.163366</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6132,7 +6350,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>316494.0133295352</v>
+        <v>316446.0199044726</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>391876.2700847145</v>
@@ -6154,16 +6372,16 @@
         <v>108452809.4223091</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>50725251.6702591</v>
+        <v>50944392.4217291</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>54316080.27749412</v>
+        <v>54536944.43641728</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>174905990.8713613</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3135663170.326231</v>
+        <v>3135223165.415838</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.03750000355548933</v>
@@ -6181,7 +6399,7 @@
         <v>0.03692656294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>332293.6981463116</v>
+        <v>332245.705476784</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>411193.871491632</v>
@@ -6203,16 +6421,16 @@
         <v>108810545.2478995</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>50363491.24509695</v>
+        <v>50565289.64839695</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>67704870.85992657</v>
+        <v>67943080.25770484</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>191459906.6813183</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3211729936.25096</v>
+        <v>3211289928.449882</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6230,7 +6448,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>334415.2492646032</v>
+        <v>334368.4188951939</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>414590.4869628215</v>
@@ -6252,16 +6470,16 @@
         <v>108790788.519045</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>50461527.69762992</v>
+        <v>50684526.19835092</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>51095777.99769017</v>
+        <v>51312784.48707948</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>150458263.8530219</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3292539380.057715</v>
+        <v>3292099375.067605</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6279,7 +6497,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>343015.8606536701</v>
+        <v>342969.0305834343</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>417067.874719601</v>
@@ -6301,16 +6519,16 @@
         <v>108778836.5352057</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>51229919.97055995</v>
+        <v>51443892.32589994</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>56536069.61801664</v>
+        <v>56762100.0283076</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>148940725.8800582</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3297029907.00169</v>
+        <v>3296589904.23606</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6328,7 +6546,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>343493.7908974375</v>
+        <v>343446.9610639547</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>418043.8151805623</v>
@@ -6350,16 +6568,16 @@
         <v>109012385.0330893</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>51077651.60920416</v>
+        <v>51294807.23677015</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>58449745.30648443</v>
+        <v>58672592.76287633</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>140084321.8061661</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3276806846.393368</v>
+        <v>3276366843.30941</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6377,7 +6595,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>341341.4349697607</v>
+        <v>341294.6051023981</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>415161.1900272233</v>
@@ -6399,16 +6617,16 @@
         <v>109013131.1815182</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>51589907.91751318</v>
+        <v>51815665.60647119</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>58099362.01924805</v>
+        <v>58313605.34159191</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>154475144.3495293</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3312690633.063111</v>
+        <v>3312250632.051809</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6426,7 +6644,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>345160.5740428209</v>
+        <v>345113.7443960527</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>420529.2631189993</v>
@@ -6448,16 +6666,16 @@
         <v>109024047.6455294</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>59429042.91027177</v>
+        <v>59681133.32946277</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>58855219.37465746</v>
+        <v>59043123.38174734</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>130752789.7099153</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3258562512.409602</v>
+        <v>3258122517.983321</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6475,7 +6693,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>339399.6764418596</v>
+        <v>339352.8474959402</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>413159.5105374671</v>
@@ -6497,16 +6715,16 @@
         <v>108998604.7903199</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>67003312.22578653</v>
+        <v>67253573.46902853</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>69754438.78971349</v>
+        <v>69944172.19441128</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>135699774.815579</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3362562386.918674</v>
+        <v>3362122392.270734</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6524,7 +6742,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>350468.4632448382</v>
+        <v>350421.6342753276</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>426718.2485197183</v>
@@ -6546,16 +6764,16 @@
         <v>108996254.8996352</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>84852106.09446886</v>
+        <v>85087299.19721687</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>78406141.98836392</v>
+        <v>78610948.4058989</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>131931405.5965129</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2779633695.09579</v>
+        <v>2779193695.575507</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6573,7 +6791,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>288426.9132758148</v>
+        <v>288380.0837877369</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>367095.8463379316</v>
@@ -6595,16 +6813,16 @@
         <v>109000464.1101925</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>86309975.97272643</v>
+        <v>86560462.48908544</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>70281418.59588619</v>
+        <v>70470930.59786333</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>129864360.3284257</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3377064033.323725</v>
+        <v>3376624034.805389</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6622,7 +6840,7 @@
         <v>0.03680118780282747</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>352011.8846490217</v>
+        <v>351965.0552675817</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>429751.7101215186</v>
@@ -6647,7 +6865,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9431994.250047093</v>
+        <v>9430564.941863894</v>
       </c>
       <c r="O37" s="12" t="n">
         <v>11700495.65151448</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T00:31:51+00:00</t>
+          <t>2026-07-07T14:46:07+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10086500.94216305</v>
+        <v>10086500.94216324</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11707957.62990799</v>
+        <v>11707957.62990818</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10086500.94216305</v>
+        <v>10086500.94216324</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>-457970.9935057093</v>
+        <v>-457970.9935055195</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T14:46:07+00:00</t>
+          <t>2026-07-10T11:11:53+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3239396.037664422</v>
+        <v>3361195.353300516</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3239396.037664422</v>
+        <v>3361195.353300516</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-458447.9883568673</v>
+        <v>-580247.303992962</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1570112.074568668</v>
+        <v>1629147.33111986</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1570112.074568668</v>
+        <v>1629147.33111986</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1606262.925431321</v>
+        <v>1547227.668880129</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1138437.490834068</v>
+        <v>1181242.046271518</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1138437.490834068</v>
+        <v>1181242.046271518</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1138437.490834068</v>
+        <v>-1181242.046271518</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>702341.968420509</v>
+        <v>728749.5981457718</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>702341.968420509</v>
+        <v>728749.5981457718</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-124829.830984509</v>
+        <v>-151237.4607097718</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>416054.0462724378</v>
+        <v>431697.4247029885</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>416054.0462724378</v>
+        <v>431697.4247029885</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>137057.9936599001</v>
+        <v>121414.6152293494</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1156,142 +1156,146 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-1.029929695e-07</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-1.029929695e-07</v>
+        <v>429848.8136485304</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>159602618.1970353</v>
+        <v>142898719.7175219</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>379255.2989209443</v>
+        <v>352330.0550047689</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>379255.2989209443</v>
+        <v>317147.3573652353</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-379255.2989210472</v>
+        <v>77518.75864376151</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0</v>
+        <v>35182.6976395336</v>
       </c>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>150752807.5253913</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>-2890025.391775267</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>429848.8136485304</v>
+        <v>314211.7987669295</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>142898719.7175219</v>
+        <v>101885166.4356003</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>339562.7043848564</v>
+        <v>251207.3331754521</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>304380.0067453228</v>
+        <v>251207.3331754521</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>90286.10926367404</v>
+        <v>63004.46559147734</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0</v>
+        <v>48760833.18343966</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>35182.6976395336</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1301,66 +1305,62 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>150752807.5253913</v>
+        <v>100000454.4463709</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-2890025.391775267</v>
+        <v>-1777.693204525303</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>314211.7987669295</v>
+        <v>9569.011445211523</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>101885166.4356003</v>
+        <v>100000076.2228826</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>242104.3569876819</v>
+        <v>246559.468312501</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>242104.3569876819</v>
+        <v>246559.468312501</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>72107.44177924756</v>
+        <v>-236990.4568672895</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>48760833.18343966</v>
+        <v>0</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1370,44 +1370,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>100000454.4463709</v>
+        <v>100000230.666889</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>100001095.915921</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-1777.693204525303</v>
+        <v>865.2490320000001</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>46285.475043</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9569.011445211523</v>
+        <v>46285.475043</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>100000076.2228826</v>
+        <v>99998716.6593553</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>237624.9163607457</v>
+        <v>246556.1161824518</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>237624.9163607457</v>
+        <v>246556.1161824518</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-228055.9049155342</v>
+        <v>-200270.6411394519</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1420,82 +1420,82 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>100000230.666889</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>865.2490320000001</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>46285.475043</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>46285.475043</v>
+        <v>306025.5205752055</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>99998716.6593553</v>
+        <v>101734967.5107904</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237621.6857015136</v>
+        <v>250837.0037873055</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237621.6857015136</v>
+        <v>225789.1194649309</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-191336.2106585136</v>
+        <v>55188.51678790002</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>25047.88432237454</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1504,63 +1504,63 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>306025.5205752055</v>
+        <v>227246.3517057119</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>101734967.5107904</v>
+        <v>75545660.91178264</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>241747.4471902746</v>
+        <v>186264.8379008275</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>216699.5628679</v>
+        <v>167664.9501545129</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>64278.07338493092</v>
+        <v>40981.51380488437</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>25047.88432237454</v>
+        <v>18599.8877463146</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1569,58 +1569,58 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>100001961.5815342</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>-23097109.59213662</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>204786.964979558</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>227246.3517057119</v>
+        <v>204786.964979558</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>75545660.91178264</v>
+        <v>63785944.13982024</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>179515.1767241537</v>
+        <v>157270.1648533966</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>160915.2889778391</v>
+        <v>157270.1648533966</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>47731.17498155818</v>
+        <v>47516.80012616146</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>18599.8877463146</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1634,40 +1634,40 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>100001961.5815342</v>
+        <v>40001.50457793332</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-23097109.59213662</v>
+        <v>51670578.4489233</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>168816.6386304617</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>204786.964979558</v>
+        <v>168816.6386304617</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>63785944.13982024</v>
+        <v>57072716.55221562</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>151571.1808802366</v>
+        <v>140718.0792232673</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>151571.1808802366</v>
+        <v>140718.0792232673</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>53215.78409932146</v>
+        <v>28098.55940719439</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1680,12 +1680,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1699,40 +1699,40 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>40001.50457793332</v>
+        <v>100002159.2601167</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>51670578.4489233</v>
+        <v>5304002.847619672</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>168816.6386304617</v>
+        <v>172735.4277329785</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>168816.6386304617</v>
+        <v>172735.4277329785</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>57072716.55221562</v>
+        <v>50410608.77727573</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>135618.8915993793</v>
+        <v>124292.0342353747</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>135618.8915993793</v>
+        <v>124292.0342353747</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>33197.74703108234</v>
+        <v>48443.39349760379</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1745,89 +1745,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" s="6" t="n">
-        <v>100002159.2601167</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5304002.847619672</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>172735.4277329785</v>
+        <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>172735.4277329785</v>
+        <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>50410608.77727573</v>
+        <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>119788.0756380199</v>
+        <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>119788.0756380199</v>
+        <v>-99849.35275556908</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52947.35209495854</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
+        <v>99849.35275556908</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>483436565.922284</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>483436565.922284</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>0</v>
@@ -1842,31 +1846,27 @@
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0</v>
+        <v>16114552.19740947</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>39731.9239340555</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>-99849.35275556908</v>
+        <v>39731.9239340555</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0</v>
+        <v>-39731.9239340555</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>99849.35275556908</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22970.67278551813</v>
+        <v>23834.35607476299</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22970.67278551813</v>
+        <v>23834.35607476299</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-22970.67278551813</v>
+        <v>-23834.35607476299</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>16881.6959555629</v>
+        <v>17516.43742905272</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>16881.6959555629</v>
+        <v>17516.43742905272</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>1404.487430566681</v>
+        <v>769.7459570768644</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2070,17 +2070,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2089,40 +2089,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5000000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9193.636315</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>-3e-14</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4993627.032029667</v>
+        <v>5000000</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11866.09301354994</v>
+        <v>12327.96401889551</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11866.09301354994</v>
+        <v>12327.96401889551</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11866.09301354994</v>
+        <v>-12327.96401889551</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2154,40 +2154,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5000000</v>
+        <v>4997775.722557</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>5000000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>2224.277443</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4.44e-10</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4.44e-10</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4987919.364249567</v>
+        <v>4997849.865138433</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11852.53018309931</v>
+        <v>12322.66266185368</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11852.53018309931</v>
+        <v>12322.66266185368</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11852.53018309886</v>
+        <v>-12322.66266185368</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2200,17 +2200,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2219,40 +2219,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>566848.624341</v>
+        <v>9193.636315</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-7.25e-10</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>-7.25e-10</v>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4969005.171823935</v>
+        <v>4987427.101210834</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11807.58538342581</v>
+        <v>12296.9643701183</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11807.58538342581</v>
+        <v>12296.9643701183</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11807.58538342653</v>
+        <v>-12296.9643701183</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2265,17 +2265,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2284,40 +2284,40 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5000000</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2224.277443</v>
+        <v>566848.624341</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-2.584619e-08</v>
+        <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>-2.584619e-08</v>
+        <v>0</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4819813.11667611</v>
+        <v>4461648.5934257</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11453.06815738716</v>
+        <v>11000.60866494156</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11453.06815738716</v>
+        <v>11000.60866494156</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11453.06815741301</v>
+        <v>-11000.60866494156</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6899.954203628415</v>
+        <v>7159.388274100473</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6899.954203628415</v>
+        <v>7159.388274100473</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2646.470786688777</v>
+        <v>2387.036716216719</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2608.230117005944</v>
+        <v>2706.297978909553</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2608.230117005944</v>
+        <v>2706.297978909553</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1889.203427833319</v>
+        <v>1791.13556592971</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2327.443743775608</v>
+        <v>2414.954209268974</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2086.293144923406</v>
+        <v>2173.803610416772</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>618.8425214019194</v>
+        <v>531.3320559085532</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>816.5656131539095</v>
+        <v>847.267982267697</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>816.5656131539095</v>
+        <v>847.267982267697</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-691.1867771539094</v>
+        <v>-721.889146267697</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>317.2319001241573</v>
+        <v>329.159626121167</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>317.2319001241573</v>
+        <v>329.159626121167</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133816.8976901242</v>
+        <v>-133828.8254161212</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>7.656500811477123</v>
+        <v>7.944380573063015</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>7.656500811477123</v>
+        <v>7.944380573063015</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-7.656500826238681</v>
+        <v>-7.944380587824574</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2789,59 +2789,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>10.263802</v>
+        <v>359.9872090112888</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2500.221225</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2489.957423</v>
+        <v>98.58562175646877</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3.63071e-09</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>3.63071e-09</v>
+        <v>14.12908623740664</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>1260.904571865159</v>
+        <v>380.1986824877172</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>2.996221150477273</v>
+        <v>0.9374151355480113</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>2.996221150477273</v>
+        <v>0.9374151355480113</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-2.996221146846563</v>
+        <v>13.19167110185863</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2854,17 +2854,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2873,40 +2873,40 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>359.9872090112888</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>98.58562175646877</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>14.12908623740664</v>
+        <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>380.1986824877172</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.9034461126334254</v>
+        <v>0.6999750137878145</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.9034461126334254</v>
+        <v>0.6999750137878145</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>13.22564012477321</v>
+        <v>-0.6999750137878145</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2919,17 +2919,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2938,40 +2938,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0</v>
+        <v>0.3313800471270399</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>99.16991404040614</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.6746100859332034</v>
+        <v>0.2445126264094175</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.6746100859332034</v>
+        <v>0.2445126264094175</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.6746100859332034</v>
+        <v>0.08686742071762242</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3053,59 +3053,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>10.263802</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>2500.221225</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>2489.957423</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.3313800471270399</v>
+        <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>99.16991404040614</v>
+        <v>93.26238276666666</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.235652245672604</v>
+        <v>0.2299470598127855</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.235652245672604</v>
+        <v>0.2299470598127855</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.09572780145443598</v>
+        <v>-0.2299470598127855</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0520555021788637</v>
+        <v>0.05401275731740186</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0520555021788637</v>
+        <v>0.05401275731740186</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.0520496444791882</v>
+        <v>-0.05400689961772635</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0001367767976020274</v>
+        <v>0.0001419195217855251</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0001367767976020274</v>
+        <v>0.0001419195217855251</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>8.622320239797261e-05</v>
+        <v>8.108047821447487e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.503451699840214e-05</v>
+        <v>1.559980566951038e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.503451699840214e-05</v>
+        <v>1.559980566951038e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>3.965483001597859e-06</v>
+        <v>3.40019433048962e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.364245578542904e-05</v>
+        <v>1.415540380380686e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.364245578542904e-05</v>
+        <v>1.415540380380686e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.053600365934404e-05</v>
+        <v>-1.104895167772186e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>4.030115509608034e-06</v>
+        <v>4.181645395209357e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4.030115509608034e-06</v>
+        <v>4.181645395209357e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-3.011550960803407e-08</v>
+        <v>-1.816453952093573e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>2.94689048984662e-06</v>
+        <v>3.057691775254322e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>2.94689048984662e-06</v>
+        <v>3.057691775254322e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-2.94689048984662e-06</v>
+        <v>-3.057691775254322e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.236024332292604e-06</v>
+        <v>1.282498093460548e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.236024332292604e-06</v>
+        <v>1.282498093460548e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-4.275700765976042e-07</v>
+        <v>-4.74043837765548e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>1.779720773040202e-07</v>
+        <v>1.846637188834773e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.779720773040202e-07</v>
+        <v>1.846637188834773e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.779720773040202e-07</v>
+        <v>-1.846637188834773e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3638,12 +3638,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
@@ -3666,31 +3666,31 @@
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-1.7787e-09</v>
+        <v>0</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>-1.7787e-09</v>
+        <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>1.903535e-08</v>
+        <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>4.523270003880736e-11</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>4.523270003880736e-11</v>
+        <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-1.823932700038807e-09</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3703,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3768,12 +3768,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>0</v>
@@ -3828,17 +3828,21 @@
       <c r="R47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3876,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3893,21 +3897,17 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
@@ -3995,19 +3995,19 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-6.258474e-08</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-6.258474e-08</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>48.90651071720747</v>
+        <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>-6.258474e-08</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10086500.94216324</v>
+        <v>10558759.94985224</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>11707957.62990818</v>
+        <v>12180216.63759718</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10086500.94216324</v>
+        <v>10558759.94985224</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>-457970.9935055195</v>
+        <v>14288.01418348054</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10T11:11:53+00:00</t>
+          <t>2026-07-13T18:32:08+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3361195.353300516</v>
+        <v>3576251.285220429</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3361195.353300516</v>
+        <v>3576251.285220429</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-580247.303992962</v>
+        <v>-795303.2359128748</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1629147.33111986</v>
+        <v>1733383.402130962</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1629147.33111986</v>
+        <v>1733383.402130962</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1547227.668880129</v>
+        <v>1442991.597869027</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -957,12 +957,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -976,40 +976,40 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>495610843.871423</v>
+        <v>282411706.537503</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>5.897868</v>
+        <v>677669071.17383</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-495610837.973555</v>
+        <v>395257364.636327</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>577512.1374370001</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0</v>
+        <v>577512.1374370001</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>479090482.6056378</v>
+        <v>295567701.6207994</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1181242.046271518</v>
+        <v>775376.4399363294</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1181242.046271518</v>
+        <v>775376.4399363294</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-1181242.046271518</v>
+        <v>-197864.3024993294</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1022,12 +1022,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1041,40 +1041,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>282411706.537503</v>
+        <v>495610843.871423</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>5.897868</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>395257364.636327</v>
+        <v>-495610837.973555</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>577512.137436</v>
+        <v>467640.351562</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>577512.137436</v>
+        <v>467640.351562</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>295567701.6207994</v>
+        <v>256422375.9369288</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>728749.5981457718</v>
+        <v>672684.6941790461</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>728749.5981457718</v>
+        <v>672684.6941790461</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-151237.4607097718</v>
+        <v>-205044.3426170461</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>431697.4247029885</v>
+        <v>459318.2804458017</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>431697.4247029885</v>
+        <v>459318.2804458017</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>121414.6152293494</v>
+        <v>93793.75948653622</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>352330.0550047689</v>
+        <v>374872.8293329679</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>317147.3573652353</v>
+        <v>339690.1316934343</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>77518.75864376151</v>
+        <v>54975.98431556249</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>251207.3331754521</v>
+        <v>267280.0755967204</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>251207.3331754521</v>
+        <v>267280.0755967204</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>63004.46559147734</v>
+        <v>46931.7231702091</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>246559.468312501</v>
+        <v>262334.8311397631</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>246559.468312501</v>
+        <v>262334.8311397631</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-236990.4568672895</v>
+        <v>-252765.8196945516</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1383,31 +1383,31 @@
         <v>865.2490320000001</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>46285.475043</v>
+        <v>46285.475044</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>46285.475043</v>
+        <v>46285.475044</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>99998716.6593553</v>
+        <v>99998716.65935527</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>246556.1161824518</v>
+        <v>262331.264533798</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>246556.1161824518</v>
+        <v>262331.264533798</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-200270.6411394519</v>
+        <v>-216045.7894897981</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>250837.0037873055</v>
+        <v>266886.0518012829</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>225789.1194649309</v>
+        <v>241838.1674789083</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>55188.51678790002</v>
+        <v>39139.46877392263</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>186264.8379008275</v>
+        <v>198182.4309259814</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>167664.9501545129</v>
+        <v>179582.5431796668</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>40981.51380488437</v>
+        <v>29063.92077973047</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>157270.1648533966</v>
+        <v>167332.6213043536</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>157270.1648533966</v>
+        <v>167332.6213043536</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>47516.80012616146</v>
+        <v>37454.34367520444</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>140718.0792232673</v>
+        <v>149721.500472087</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>140718.0792232673</v>
+        <v>149721.500472087</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>28098.55940719439</v>
+        <v>19095.1381583747</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>124292.0342353747</v>
+        <v>132244.4846118347</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>124292.0342353747</v>
+        <v>132244.4846118347</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>48443.39349760379</v>
+        <v>40490.94312114381</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>39731.9239340555</v>
+        <v>42274.0510735028</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>39731.9239340555</v>
+        <v>42274.0510735028</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-39731.9239340555</v>
+        <v>-42274.0510735028</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1871,59 +1871,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>10000122.636328</v>
+        <v>10156910.09323084</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.28330096818</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-10000122.481897</v>
+        <v>-10156909.80992987</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>18286.18338612959</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>9666785.220264766</v>
+        <v>7104351.295236039</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>23834.35607476299</v>
+        <v>18637.17376814196</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>23834.35607476299</v>
+        <v>18637.17376814196</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-23834.35607476299</v>
+        <v>-350.9903820123725</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1936,59 +1936,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>10156910.09323084</v>
+        <v>5000000</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>5000000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-10156909.80992987</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>18286.18338612959</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>7104351.295236039</v>
+        <v>5000000</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>17516.43742905272</v>
+        <v>13116.73155903726</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>17516.43742905272</v>
+        <v>13116.73155903726</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>769.7459570768644</v>
+        <v>-13116.73155903726</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2001,86 +2001,82 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>50000879.85586481</v>
+        <v>4997775.722557</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>5000000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>1535.4070347212</v>
+        <v>2224.277443</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>12598.4555305973</v>
+        <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>103204.2172004009</v>
+        <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>103204.2172004009</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>12598.4555305973</v>
+        <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>4997849.865138433</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0</v>
+        <v>13111.09101067828</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>12598.4555305973</v>
+        <v>13111.09101067828</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>103204.2172004009</v>
+        <v>-13111.09101067828</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>49997070.94700827</v>
+        <v>0</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2089,13 +2085,13 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5000000</v>
+        <v>4987120.646667</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5000000</v>
+        <v>4996314.282982</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>9193.636315</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>0</v>
@@ -2110,19 +2106,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>5000000</v>
+        <v>4987427.101210834</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>12327.96401889551</v>
+        <v>13083.74849136997</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>12327.96401889551</v>
+        <v>13083.74849136997</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-12327.96401889551</v>
+        <v>-13083.74849136997</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2135,82 +2131,86 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4997775.722557</v>
+        <v>50000879.85586481</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>5000000</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2224.277443</v>
+        <v>1535.4070347212</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4997849.865138433</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12322.66266185368</v>
+        <v>0</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>12322.66266185368</v>
+        <v>12598.4555305973</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-12322.66266185368</v>
+        <v>103204.2172004009</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0</v>
+        <v>49997070.94700827</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4987120.646667</v>
+        <v>4442753.639281</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5009602.263622</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>9193.636315</v>
+        <v>566848.624341</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>0</v>
@@ -2240,19 +2240,19 @@
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4987427.101210834</v>
+        <v>4461648.5934257</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>12296.9643701183</v>
+        <v>11704.44938214422</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>12296.9643701183</v>
+        <v>11704.44938214422</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-12296.9643701183</v>
+        <v>-11704.44938214422</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2265,59 +2265,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4442753.639281</v>
+        <v>977119.890305955</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>566848.624341</v>
+        <v>-273029.0857638157</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>9546.424990317191</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0</v>
+        <v>9546.424990317191</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4461648.5934257</v>
+        <v>2903718.839188297</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>11000.60866494156</v>
+        <v>7617.460107310435</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>11000.60866494156</v>
+        <v>7617.460107310435</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-11000.60866494156</v>
+        <v>1928.964883006757</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2330,59 +2330,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>977119.890305955</v>
+        <v>10000122.636328</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>0.154431</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-273029.0857638157</v>
+        <v>-10000122.481897</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9546.424990317191</v>
+        <v>4618.656125</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>9546.424990317191</v>
+        <v>4618.656125</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>2903718.839188297</v>
+        <v>2328579.222917333</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>7159.388274100473</v>
+        <v>6108.669716191649</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>7159.388274100473</v>
+        <v>6108.669716191649</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>2387.036716216719</v>
+        <v>-1490.013591191649</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2706.297978909553</v>
+        <v>2879.452280499276</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2706.297978909553</v>
+        <v>2879.452280499276</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1791.13556592971</v>
+        <v>1617.981264339988</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2414.954209268974</v>
+        <v>2569.467759785543</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2173.803610416772</v>
+        <v>2328.317160933341</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>531.3320559085532</v>
+        <v>376.8185053919846</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>847.267982267697</v>
+        <v>901.4778648719804</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>847.267982267697</v>
+        <v>901.4778648719804</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-721.889146267697</v>
+        <v>-776.0990288719804</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>329.159626121167</v>
+        <v>350.2199105453936</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>329.159626121167</v>
+        <v>350.2199105453936</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133828.8254161212</v>
+        <v>-133849.8857005454</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>7.944380573063015</v>
+        <v>8.452677767389693</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>7.944380573063015</v>
+        <v>8.452677767389693</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-7.944380587824574</v>
+        <v>-8.45267778215125</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2835,13 +2835,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9374151355480113</v>
+        <v>0.9973928114582055</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9374151355480113</v>
+        <v>0.9973928114582055</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.19167110185863</v>
+        <v>13.13169342594843</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.6999750137878145</v>
+        <v>0.7447608007141757</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.6999750137878145</v>
+        <v>0.7447608007141757</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.6999750137878145</v>
+        <v>-0.7447608007141757</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2445126264094175</v>
+        <v>0.2601570282401615</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2445126264094175</v>
+        <v>0.2601570282401615</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.08686742071762242</v>
+        <v>0.07122301888687843</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2984,35 +2984,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>220002.4647086113</v>
+        <v>10.263802</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>220002.7079018081</v>
+        <v>2500.221225</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.2431931968307834</v>
+        <v>2489.957423</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.2431931968307834</v>
+        <v>0</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
@@ -3021,67 +3021,63 @@
         <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.2431931968307834</v>
+        <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>220002.4647086113</v>
+        <v>93.26238276666666</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0</v>
+        <v>0.2446595278613099</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2431931968307834</v>
+        <v>0.2446595278613099</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0</v>
+        <v>-0.2446595278613099</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>220002.4647086113</v>
+        <v>0</v>
       </c>
       <c r="R35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>10.263802</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>2500.221225</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>2489.957423</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
@@ -3090,30 +3086,34 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>93.26238276666666</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2299470598127855</v>
+        <v>0</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.2299470598127855</v>
+        <v>0.2431931968307834</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-0.2299470598127855</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>0</v>
+        <v>220002.4647086113</v>
       </c>
       <c r="R36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.05401275731740186</v>
+        <v>0.05746860044447624</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.05401275731740186</v>
+        <v>0.05746860044447624</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.05400689961772635</v>
+        <v>-0.05746274274480073</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0001419195217855251</v>
+        <v>0.0001509998137076369</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0001419195217855251</v>
+        <v>0.0001509998137076369</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>8.108047821447487e-05</v>
+        <v>7.200018629236305e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.559980566951038e-05</v>
+        <v>1.659791211480575e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.559980566951038e-05</v>
+        <v>1.659791211480575e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>3.40019433048962e-06</v>
+        <v>2.40208788519425e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.415540380380686e-05</v>
+        <v>1.506109455865725e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.415540380380686e-05</v>
+        <v>1.506109455865725e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.104895167772186e-05</v>
+        <v>-1.195464243257225e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>4.181645395209357e-06</v>
+        <v>4.449195344825439e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4.181645395209357e-06</v>
+        <v>4.449195344825439e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.816453952093573e-07</v>
+        <v>-4.491953448254389e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3.057691775254322e-06</v>
+        <v>3.253328947489928e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>3.057691775254322e-06</v>
+        <v>3.253328947489928e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-3.057691775254322e-06</v>
+        <v>-3.253328947489928e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.282498093460548e-06</v>
+        <v>1.364554860081935e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.282498093460548e-06</v>
+        <v>1.364554860081935e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-4.74043837765548e-07</v>
+        <v>-5.561006043869346e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>1.846637188834773e-07</v>
+        <v>1.964788691446149e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.846637188834773e-07</v>
+        <v>1.964788691446149e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.846637188834773e-07</v>
+        <v>-1.964788691446149e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9284001.665529964</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9264231.53101651</v>
+        <v>9296589.227745224</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9284001.665529964</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11700495.65151448</v>
+        <v>11732853.3482432</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9251643.968801251</v>
+        <v>-9284001.665529964</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>14288.01418348054</v>
+        <v>-18069.6825452326</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-13T18:32:08+00:00</t>
+          <t>2026-07-30T23:10:28+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3576251.285220429</v>
+        <v>3588521.945061722</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3576251.285220429</v>
+        <v>3588521.945061722</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-795303.2359128748</v>
+        <v>-807573.8957541676</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1733383.402130962</v>
+        <v>1739330.903132917</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1733383.402130962</v>
+        <v>1739330.903132917</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1442991.597869027</v>
+        <v>1437044.096867072</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>775376.4399363294</v>
+        <v>778036.8739451843</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>775376.4399363294</v>
+        <v>778036.8739451843</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-197864.3024993294</v>
+        <v>-200524.7365081843</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>672684.6941790461</v>
+        <v>674992.7772538647</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>672684.6941790461</v>
+        <v>674992.7772538647</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-205044.3426170461</v>
+        <v>-207352.4256918646</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>459318.2804458017</v>
+        <v>460894.2710372711</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>459318.2804458017</v>
+        <v>460894.2710372711</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>93793.75948653622</v>
+        <v>92217.76889506677</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>374872.8293329679</v>
+        <v>376159.0747910257</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>339690.1316934343</v>
+        <v>340976.3771514921</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>54975.98431556249</v>
+        <v>53689.73885750477</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>267280.0755967204</v>
+        <v>268197.1540200282</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>267280.0755967204</v>
+        <v>268197.1540200282</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>46931.7231702091</v>
+        <v>46014.64474690132</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>262334.8311397631</v>
+        <v>263234.941680301</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>262334.8311397631</v>
+        <v>263234.941680301</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-252765.8196945516</v>
+        <v>-253665.9302350894</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>262331.264533798</v>
+        <v>263231.3628367707</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>262331.264533798</v>
+        <v>263231.3628367707</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-216045.7894897981</v>
+        <v>-216945.8877927706</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>266886.0518012829</v>
+        <v>267801.7782692672</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>241838.1674789083</v>
+        <v>242753.8939468926</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>39139.46877392263</v>
+        <v>38223.74230593834</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198182.4309259814</v>
+        <v>198862.4248644563</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>179582.5431796668</v>
+        <v>180262.5371181418</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>29063.92077973047</v>
+        <v>28383.92684125549</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>167332.6213043536</v>
+        <v>167906.7648733089</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>167332.6213043536</v>
+        <v>167906.7648733089</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>37454.34367520444</v>
+        <v>36880.2001062491</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>149721.500472087</v>
+        <v>150235.2176179748</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>149721.500472087</v>
+        <v>150235.2176179748</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>19095.1381583747</v>
+        <v>18581.42101248692</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>132244.4846118347</v>
+        <v>132698.2354691263</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>132244.4846118347</v>
+        <v>132698.2354691263</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>40490.94312114381</v>
+        <v>40037.19226385223</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>42274.0510735028</v>
+        <v>42419.09974583188</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>42274.0510735028</v>
+        <v>42419.09974583188</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-42274.0510735028</v>
+        <v>-42419.09974583188</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>18637.17376814196</v>
+        <v>18701.120734245</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>18637.17376814196</v>
+        <v>18701.120734245</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-350.9903820123725</v>
+        <v>-414.9373481154101</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13116.73155903726</v>
+        <v>13161.73705175967</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13116.73155903726</v>
+        <v>13161.73705175967</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13116.73155903726</v>
+        <v>-13161.73705175967</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13111.09101067828</v>
+        <v>13156.07714982492</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13111.09101067828</v>
+        <v>13156.07714982492</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13111.09101067828</v>
+        <v>-13156.07714982492</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13083.74849136997</v>
+        <v>13128.64081419139</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13083.74849136997</v>
+        <v>13128.64081419139</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13083.74849136997</v>
+        <v>-13128.64081419139</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11704.44938214422</v>
+        <v>11744.60912080449</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11704.44938214422</v>
+        <v>11744.60912080449</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11704.44938214422</v>
+        <v>-11744.60912080449</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>7617.460107310435</v>
+        <v>7643.596766727437</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>7617.460107310435</v>
+        <v>7643.596766727437</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1928.964883006757</v>
+        <v>1902.828223589755</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6108.669716191649</v>
+        <v>6129.629487245761</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6108.669716191649</v>
+        <v>6129.629487245761</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-1490.013591191649</v>
+        <v>-1510.973362245762</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2879.452280499276</v>
+        <v>2889.332117413774</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2879.452280499276</v>
+        <v>2889.332117413774</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1617.981264339988</v>
+        <v>1608.10142742549</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2569.467759785543</v>
+        <v>2578.28399285725</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2328.317160933341</v>
+        <v>2337.133394005049</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>376.8185053919846</v>
+        <v>368.002272320277</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>901.4778648719804</v>
+        <v>904.5709719699111</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>901.4778648719804</v>
+        <v>904.5709719699111</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-776.0990288719804</v>
+        <v>-779.1921359699111</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>350.2199105453936</v>
+        <v>351.4215681050038</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>350.2199105453936</v>
+        <v>351.4215681050038</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133849.8857005454</v>
+        <v>-133851.087358105</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>8.452677767389693</v>
+        <v>8.481680185105791</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>8.452677767389693</v>
+        <v>8.481680185105791</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-8.45267778215125</v>
+        <v>-8.48168019986735</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2835,13 +2835,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9973928114582055</v>
+        <v>1.00081501726576</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9973928114582055</v>
+        <v>1.00081501726576</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.13169342594843</v>
+        <v>13.12827122014088</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.7447608007141757</v>
+        <v>0.7473161878276204</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.7447608007141757</v>
+        <v>0.7473161878276204</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.7447608007141757</v>
+        <v>-0.7473161878276204</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2601570282401615</v>
+        <v>0.261049666409087</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2601570282401615</v>
+        <v>0.261049666409087</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.07122301888687843</v>
+        <v>0.07033038071795293</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.2446595278613099</v>
+        <v>0.2454989917590858</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2446595278613099</v>
+        <v>0.2454989917590858</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.2446595278613099</v>
+        <v>-0.2454989917590858</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.05746860044447624</v>
+        <v>0.05766578391715995</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.05746860044447624</v>
+        <v>0.05766578391715995</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.05746274274480073</v>
+        <v>-0.05765992621748444</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0001509998137076369</v>
+        <v>0.0001515179169398573</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0001509998137076369</v>
+        <v>0.0001515179169398573</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>7.200018629236305e-05</v>
+        <v>7.148208306014267e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.659791211480575e-05</v>
+        <v>1.665486206529669e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.659791211480575e-05</v>
+        <v>1.665486206529669e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>2.40208788519425e-06</v>
+        <v>2.345137934703313e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.506109455865725e-05</v>
+        <v>1.511277145533691e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.506109455865725e-05</v>
+        <v>1.511277145533691e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.195464243257225e-05</v>
+        <v>-1.200631932925191e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>4.449195344825439e-06</v>
+        <v>4.46446120795688e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4.449195344825439e-06</v>
+        <v>4.46446120795688e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.491953448254389e-07</v>
+        <v>-4.644612079568803e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3.253328947489928e-06</v>
+        <v>3.264491611878602e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>3.253328947489928e-06</v>
+        <v>3.264491611878602e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-3.253328947489928e-06</v>
+        <v>-3.264491611878602e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.364554860081935e-06</v>
+        <v>1.369236854491009e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.364554860081935e-06</v>
+        <v>1.369236854491009e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-5.561006043869346e-07</v>
+        <v>-5.607825987960093e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>1.964788691446149e-07</v>
+        <v>1.971530179045857e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.964788691446149e-07</v>
+        <v>1.971530179045857e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.964788691446149e-07</v>
+        <v>-1.971530179045857e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.03686666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03688895040288687</v>
+        <v>0.0372972837362202</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03914088815949029</v>
+        <v>0.03927752915626952</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-11.45325778732615</v>
+        <v>-10.08684781953383</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>270879.1830035028</v>
+        <v>238521.4862747897</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9430564.941863894</v>
+        <v>9462922.638592608</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>270879.1830035028</v>
+        <v>238521.4862747897</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2977531.418973944</v>
+        <v>3009889.115702657</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9284001.665529964</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9264231.53101651</v>
+        <v>9296589.227745224</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11700495.65151448</v>
+        <v>11732853.3482432</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9284001.665529964</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>3</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0358</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03640156294576948</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>293920.6468481718</v>
+        <v>292533.0246183847</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>374578.727875959</v>
+        <v>373191.1056461719</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>3</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0358</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03640156294576948</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>303013.5166095516</v>
+        <v>301625.8943797646</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>382071.5092839777</v>
+        <v>380683.8870541907</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0358</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03640156294576948</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>303846.6151537827</v>
+        <v>302458.9929239957</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>382353.5908336217</v>
+        <v>380965.9686038347</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>3</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0358</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03640156294576948</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>303555.7943579851</v>
+        <v>302168.172128198</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>382870.6039957182</v>
+        <v>381482.9817659312</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>3</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0358</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03640156294576948</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>304323.1925158073</v>
+        <v>302935.5702860203</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>383831.3648336361</v>
+        <v>382443.742603849</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>3</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>308166.9803164455</v>
+        <v>310016.0538120978</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>383150.5056369744</v>
+        <v>384999.5791326266</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>306834.2616068879</v>
+        <v>308683.3351025401</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>384484.6224839138</v>
+        <v>386333.695979566</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>307368.671438415</v>
+        <v>309217.7449340671</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>381775.6535496546</v>
+        <v>383624.7270453068</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>307129.371464794</v>
+        <v>308978.4449604462</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>381733.1447470395</v>
+        <v>383582.2182426917</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>3</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>307119.447068205</v>
+        <v>308968.5205638573</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>381000.1725228651</v>
+        <v>382849.2460185173</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>3</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>306386.877799583</v>
+        <v>308235.9512952353</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>380101.5050144822</v>
+        <v>381950.5785101344</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>3</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>314300.6602107302</v>
+        <v>316149.7337063825</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>387863.3849071475</v>
+        <v>389712.4584027997</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>3</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>294465.9515593068</v>
+        <v>296083.9589105186</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>367652.0134779223</v>
+        <v>369270.020829134</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>3</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>294830.0953458483</v>
+        <v>296448.10269706</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>367769.9874829751</v>
+        <v>369387.9948341869</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>3</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>296067.7199726206</v>
+        <v>297685.7273238324</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>369052.5068981854</v>
+        <v>370670.5142493972</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>295617.1317991815</v>
+        <v>297235.1391503933</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>368789.9779535549</v>
+        <v>370407.9853047666</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>3</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>295436.3574166922</v>
+        <v>297054.3647679039</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>368422.8260497338</v>
+        <v>370040.8334009456</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>3</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>298237.619004383</v>
+        <v>299855.6263555947</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>371289.9860909391</v>
+        <v>372907.9934421509</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>303939.9251266263</v>
+        <v>305557.9324778381</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>376515.4807739933</v>
+        <v>378133.488125205</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>3</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>316446.0199044726</v>
+        <v>318064.0272556844</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>391876.2700847145</v>
+        <v>393494.2774359263</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>3</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>332245.705476784</v>
+        <v>333863.7128279958</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>411193.871491632</v>
+        <v>412811.8788428437</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>3</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03741368780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>334368.4188951939</v>
+        <v>335986.6213101486</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>414590.4869628215</v>
+        <v>416208.6893777762</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>3</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03741368780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>342969.0305834343</v>
+        <v>344587.2329983889</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>417067.874719601</v>
+        <v>418686.0771345557</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>3</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03741368780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>343446.9610639547</v>
+        <v>345065.1634789094</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>418043.8151805623</v>
+        <v>419662.0175955169</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>3</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03741368780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>341294.6051023981</v>
+        <v>342912.8075173529</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>415161.1900272233</v>
+        <v>416779.392442178</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>3</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03741368780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>345113.7443960527</v>
+        <v>346731.9468110075</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>420529.2631189993</v>
+        <v>422147.465533954</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>3</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>339352.8474959402</v>
+        <v>340277.6512890411</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>413159.5105374671</v>
+        <v>414084.3143305681</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>3</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>350421.6342753276</v>
+        <v>351346.4380684285</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>426718.2485197183</v>
+        <v>427643.0523128192</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>3</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>288380.0837877369</v>
+        <v>289304.8875808378</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>367095.8463379316</v>
+        <v>368020.6501310325</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>3</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>351965.0552675817</v>
+        <v>352889.8590606826</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>429751.7101215186</v>
+        <v>430676.5139146195</v>
       </c>
     </row>
     <row r="37">
@@ -6865,10 +6865,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9430564.941863894</v>
+        <v>9462922.638592608</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11700495.65151448</v>
+        <v>11732853.3482432</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9284001.665529964</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9296589.227745224</v>
+        <v>9303528.965772124</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9284001.665529964</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11732853.3482432</v>
+        <v>11739793.0862701</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9284001.665529964</v>
+        <v>-9290941.403556865</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>-18069.6825452326</v>
+        <v>-25009.42057213358</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-30T23:10:28+00:00</t>
+          <t>2026-07-31T00:19:42+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3588521.945061722</v>
+        <v>3591153.626958914</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3588521.945061722</v>
+        <v>3591153.626958914</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-807573.8957541676</v>
+        <v>-810205.5776513597</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1739330.903132917</v>
+        <v>1740606.460513108</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1739330.903132917</v>
+        <v>1740606.460513108</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1437044.096867072</v>
+        <v>1435768.539486881</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>778036.8739451843</v>
+        <v>778607.4558136683</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>778036.8739451843</v>
+        <v>778607.4558136683</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-200524.7365081843</v>
+        <v>-201095.3183766684</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>674992.7772538647</v>
+        <v>675487.7906047176</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>674992.7772538647</v>
+        <v>675487.7906047176</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-207352.4256918646</v>
+        <v>-207847.4390427176</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>460894.2710372711</v>
+        <v>461232.2729021552</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>460894.2710372711</v>
+        <v>461232.2729021552</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>92217.76889506677</v>
+        <v>91879.76703018267</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>376159.0747910257</v>
+        <v>376434.9351710783</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>340976.3771514921</v>
+        <v>341252.2375315447</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>53689.73885750477</v>
+        <v>53413.8784774521</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>268197.1540200282</v>
+        <v>268393.8393422635</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>268197.1540200282</v>
+        <v>268393.8393422635</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>46014.64474690132</v>
+        <v>45817.95942466601</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>263234.941680301</v>
+        <v>263427.9879097331</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>263234.941680301</v>
+        <v>263427.9879097331</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-253665.9302350894</v>
+        <v>-253858.9764645215</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>263231.3628367707</v>
+        <v>263424.4064416186</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>263231.3628367707</v>
+        <v>263424.4064416186</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-216945.8877927706</v>
+        <v>-217138.9313976186</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>267801.7782692672</v>
+        <v>267998.1736383625</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>242753.8939468926</v>
+        <v>242950.289315988</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>38223.74230593834</v>
+        <v>38027.34693684301</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198862.4248644563</v>
+        <v>199008.2628031842</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>180262.5371181418</v>
+        <v>180408.3750568696</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>28383.92684125549</v>
+        <v>28238.08890252763</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>167906.7648733089</v>
+        <v>168029.9011395205</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>167906.7648733089</v>
+        <v>168029.9011395205</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>36880.2001062491</v>
+        <v>36757.06384003753</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>150235.2176179748</v>
+        <v>150345.3942613335</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>150235.2176179748</v>
+        <v>150345.3942613335</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>18581.42101248692</v>
+        <v>18471.24436912821</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>132698.2354691263</v>
+        <v>132795.5511744277</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>132698.2354691263</v>
+        <v>132795.5511744277</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>40037.19226385223</v>
+        <v>39939.87655855077</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>42419.09974583188</v>
+        <v>42450.20825752704</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>42419.09974583188</v>
+        <v>42450.20825752704</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-42419.09974583188</v>
+        <v>-42450.20825752704</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>18701.120734245</v>
+        <v>18714.83540609234</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>18701.120734245</v>
+        <v>18714.83540609234</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-414.9373481154101</v>
+        <v>-428.6520199627547</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13161.73705175967</v>
+        <v>13171.38935587401</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13161.73705175967</v>
+        <v>13171.38935587401</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13161.73705175967</v>
+        <v>-13171.38935587401</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13156.07714982492</v>
+        <v>13165.72530318814</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13156.07714982492</v>
+        <v>13165.72530318814</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13156.07714982492</v>
+        <v>-13165.72530318814</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13128.64081419139</v>
+        <v>13138.26884681719</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13128.64081419139</v>
+        <v>13138.26884681719</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13128.64081419139</v>
+        <v>-13138.26884681719</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11744.60912080449</v>
+        <v>11753.2221586195</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11744.60912080449</v>
+        <v>11753.2221586195</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11744.60912080449</v>
+        <v>-11753.2221586195</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>7643.596766727437</v>
+        <v>7649.202282187114</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>7643.596766727437</v>
+        <v>7649.202282187114</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1902.828223589755</v>
+        <v>1897.222708130078</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6129.629487245761</v>
+        <v>6134.124718208548</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6129.629487245761</v>
+        <v>6134.124718208548</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-1510.973362245762</v>
+        <v>-1515.468593208548</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2889.332117413774</v>
+        <v>2891.451040788016</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2889.332117413774</v>
+        <v>2891.451040788016</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1608.10142742549</v>
+        <v>1605.982504051247</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2578.28399285725</v>
+        <v>2580.174805680385</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2337.133394005049</v>
+        <v>2339.024206828183</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>368.002272320277</v>
+        <v>366.1114594971424</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>904.5709719699111</v>
+        <v>905.2343490059453</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>904.5709719699111</v>
+        <v>905.2343490059453</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-779.1921359699111</v>
+        <v>-779.8555130059452</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>351.4215681050038</v>
+        <v>351.6792869634149</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>351.4215681050038</v>
+        <v>351.6792869634149</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133851.087358105</v>
+        <v>-133851.3450769634</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>8.481680185105791</v>
+        <v>8.487900318225398</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>8.481680185105791</v>
+        <v>8.487900318225398</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-8.48168019986735</v>
+        <v>-8.487900332986957</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2835,13 +2835,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>1.00081501726576</v>
+        <v>1.001548975927208</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1.00081501726576</v>
+        <v>1.001548975927208</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.12827122014088</v>
+        <v>13.12753726147943</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.7473161878276204</v>
+        <v>0.7478642403442537</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.7473161878276204</v>
+        <v>0.7478642403442537</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.7473161878276204</v>
+        <v>-0.7478642403442537</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.261049666409087</v>
+        <v>0.2612411100429492</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.261049666409087</v>
+        <v>0.2612411100429492</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.07033038071795293</v>
+        <v>0.07013893708409073</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.2454989917590858</v>
+        <v>0.2456790311352642</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2454989917590858</v>
+        <v>0.2456790311352642</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.2454989917590858</v>
+        <v>-0.2456790311352642</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.05766578391715995</v>
+        <v>0.05770807375178978</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.05766578391715995</v>
+        <v>0.05770807375178978</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.05765992621748444</v>
+        <v>-0.05770221605211427</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0001515179169398573</v>
+        <v>0.0001516290342648216</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0001515179169398573</v>
+        <v>0.0001516290342648216</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>7.148208306014267e-05</v>
+        <v>7.137096573517839e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.665486206529669e-05</v>
+        <v>1.666707609092297e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.665486206529669e-05</v>
+        <v>1.666707609092297e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>2.345137934703313e-06</v>
+        <v>2.332923909077027e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.511277145533691e-05</v>
+        <v>1.512385457191368e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.511277145533691e-05</v>
+        <v>1.512385457191368e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.200631932925191e-05</v>
+        <v>-1.201740244582868e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>4.46446120795688e-06</v>
+        <v>4.467735269512465e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4.46446120795688e-06</v>
+        <v>4.467735269512465e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.644612079568803e-07</v>
+        <v>-4.677352695124644e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3.264491611878602e-06</v>
+        <v>3.26688566257971e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>3.264491611878602e-06</v>
+        <v>3.26688566257971e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-3.264491611878602e-06</v>
+        <v>-3.26688566257971e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.369236854491009e-06</v>
+        <v>1.370240999344545e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.369236854491009e-06</v>
+        <v>1.370240999344545e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-5.607825987960093e-07</v>
+        <v>-5.617867436495447e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>1.971530179045857e-07</v>
+        <v>1.972976022309851e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.971530179045857e-07</v>
+        <v>1.972976022309851e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.971530179045857e-07</v>
+        <v>-1.972976022309851e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03686666666666667</v>
+        <v>0.03696666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.0372972837362202</v>
+        <v>0.03738478373622021</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03927752915626952</v>
+        <v>0.03930680936986507</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-10.08684781953383</v>
+        <v>-9.79404568357833</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>238521.4862747897</v>
+        <v>231581.7482478888</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9462922.638592608</v>
+        <v>9469862.376619508</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>238521.4862747897</v>
+        <v>231581.7482478888</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3009889.115702657</v>
+        <v>3016828.853729559</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9284001.665529964</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9296589.227745224</v>
+        <v>9303528.965772124</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11732853.3482432</v>
+        <v>11739793.0862701</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9284001.665529964</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="32">
@@ -5413,16 +5413,16 @@
         <v>3</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.037</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>292533.0246183847</v>
+        <v>295307.5686209331</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>373191.1056461719</v>
+        <v>375965.6496487203</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>3</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.037</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>301625.8943797646</v>
+        <v>304400.4383823129</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>380683.8870541907</v>
+        <v>383458.4310567391</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>302458.9929239957</v>
+        <v>305464.6225049944</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>380965.9686038347</v>
+        <v>383971.5981848335</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>3</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>302168.172128198</v>
+        <v>305173.8017091968</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>381482.9817659312</v>
+        <v>384488.61134693</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>3</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.0371</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03640156294576948</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>302935.5702860203</v>
+        <v>305941.1998670191</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>382443.742603849</v>
+        <v>385449.3721848478</v>
       </c>
     </row>
     <row r="11">
@@ -5707,16 +5707,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0372</v>
+        <v>0.0371</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>308683.3351025401</v>
+        <v>308452.2689580997</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>386333.695979566</v>
+        <v>386102.6298351255</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>309217.7449340671</v>
+        <v>308524.4881951632</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>383624.7270453068</v>
+        <v>382931.4703064028</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0372</v>
+        <v>0.0368</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03727656294576948</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>308978.4449604462</v>
+        <v>308054.0637648579</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>383582.2182426917</v>
+        <v>382657.8370471034</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>3</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>308968.5205638573</v>
+        <v>308275.2638249533</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>382849.2460185173</v>
+        <v>382155.9892796133</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>3</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>308235.9512952353</v>
+        <v>307542.6945563313</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>381950.5785101344</v>
+        <v>381257.3217712304</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>3</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0372</v>
+        <v>0.0369</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03762656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>316149.7337063825</v>
+        <v>315456.4769674785</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>389712.4584027997</v>
+        <v>389019.2016638957</v>
       </c>
     </row>
     <row r="18">
@@ -6148,16 +6148,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>297235.1391503933</v>
+        <v>297004.0535719429</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>370407.9853047666</v>
+        <v>370176.8997263162</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>3</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>297054.3647679039</v>
+        <v>296823.2791894535</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>370040.8334009456</v>
+        <v>369809.7478224952</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>3</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>299855.6263555947</v>
+        <v>299624.5407771443</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>372907.9934421509</v>
+        <v>372676.9078637005</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>305557.9324778381</v>
+        <v>305326.8468993877</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>378133.488125205</v>
+        <v>377902.4025467546</v>
       </c>
     </row>
     <row r="25">
@@ -6393,16 +6393,16 @@
         <v>3</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03753906294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>333863.7128279958</v>
+        <v>333401.5222335323</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>412811.8788428437</v>
+        <v>412349.6882483802</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>3</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>335986.6213101486</v>
+        <v>335524.3750066921</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>416208.6893777762</v>
+        <v>415746.4430743197</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>3</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>344587.2329983889</v>
+        <v>344124.9866949325</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>418686.0771345557</v>
+        <v>418223.8308310992</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>3</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>345065.1634789094</v>
+        <v>344602.9171754529</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>419662.0175955169</v>
+        <v>419199.7712920604</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>3</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>342912.8075173529</v>
+        <v>342450.5612138964</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>416779.392442178</v>
+        <v>416317.1461387215</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>3</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03741368780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>346731.9468110075</v>
+        <v>346269.700507551</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>422147.465533954</v>
+        <v>421685.2192304975</v>
       </c>
     </row>
     <row r="32">
@@ -6865,10 +6865,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9462922.638592608</v>
+        <v>9469862.376619508</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11732853.3482432</v>
+        <v>11739793.0862701</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9264231.53101651</v>
+        <v>9303528.965772124</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11700495.65151448</v>
+        <v>11739793.0862701</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9251643.968801251</v>
+        <v>-9290941.403556865</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>14288.01418348054</v>
+        <v>-25009.42057213358</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-13T18:32:08+00:00</t>
+          <t>2026-07-31T00:19:42+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3576251.285220429</v>
+        <v>3591153.626958914</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3576251.285220429</v>
+        <v>3591153.626958914</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-795303.2359128748</v>
+        <v>-810205.5776513597</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1733383.402130962</v>
+        <v>1740606.460513108</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1733383.402130962</v>
+        <v>1740606.460513108</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1442991.597869027</v>
+        <v>1435768.539486881</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>775376.4399363294</v>
+        <v>778607.4558136683</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>775376.4399363294</v>
+        <v>778607.4558136683</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-197864.3024993294</v>
+        <v>-201095.3183766684</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>672684.6941790461</v>
+        <v>675487.7906047176</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>672684.6941790461</v>
+        <v>675487.7906047176</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-205044.3426170461</v>
+        <v>-207847.4390427176</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>459318.2804458017</v>
+        <v>461232.2729021552</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>459318.2804458017</v>
+        <v>461232.2729021552</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>93793.75948653622</v>
+        <v>91879.76703018267</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>78177410.48970658</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>374872.8293329679</v>
+        <v>376434.9351710783</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>339690.1316934343</v>
+        <v>341252.2375315447</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>54975.98431556249</v>
+        <v>53413.8784774521</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>267280.0755967204</v>
+        <v>268393.8393422635</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>267280.0755967204</v>
+        <v>268393.8393422635</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>46931.7231702091</v>
+        <v>45817.95942466601</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>48760833.18343966</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>262334.8311397631</v>
+        <v>263427.9879097331</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>262334.8311397631</v>
+        <v>263427.9879097331</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-252765.8196945516</v>
+        <v>-253858.9764645215</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>262331.264533798</v>
+        <v>263424.4064416186</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>262331.264533798</v>
+        <v>263424.4064416186</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-216045.7894897981</v>
+        <v>-217138.9313976186</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>266886.0518012829</v>
+        <v>267998.1736383625</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>241838.1674789083</v>
+        <v>242950.289315988</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>39139.46877392263</v>
+        <v>38027.34693684301</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198182.4309259814</v>
+        <v>199008.2628031842</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>179582.5431796668</v>
+        <v>180408.3750568696</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>29063.92077973047</v>
+        <v>28238.08890252763</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>167332.6213043536</v>
+        <v>168029.9011395205</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>167332.6213043536</v>
+        <v>168029.9011395205</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>37454.34367520444</v>
+        <v>36757.06384003753</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>149721.500472087</v>
+        <v>150345.3942613335</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>149721.500472087</v>
+        <v>150345.3942613335</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>19095.1381583747</v>
+        <v>18471.24436912821</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>132244.4846118347</v>
+        <v>132795.5511744277</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>132244.4846118347</v>
+        <v>132795.5511744277</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>40490.94312114381</v>
+        <v>39939.87655855077</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>42274.0510735028</v>
+        <v>42450.20825752704</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>42274.0510735028</v>
+        <v>42450.20825752704</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-42274.0510735028</v>
+        <v>-42450.20825752704</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>18637.17376814196</v>
+        <v>18714.83540609234</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>18637.17376814196</v>
+        <v>18714.83540609234</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-350.9903820123725</v>
+        <v>-428.6520199627547</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13116.73155903726</v>
+        <v>13171.38935587401</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>13116.73155903726</v>
+        <v>13171.38935587401</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-13116.73155903726</v>
+        <v>-13171.38935587401</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>13111.09101067828</v>
+        <v>13165.72530318814</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>13111.09101067828</v>
+        <v>13165.72530318814</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-13111.09101067828</v>
+        <v>-13165.72530318814</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>13083.74849136997</v>
+        <v>13138.26884681719</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>13083.74849136997</v>
+        <v>13138.26884681719</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-13083.74849136997</v>
+        <v>-13138.26884681719</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11704.44938214422</v>
+        <v>11753.2221586195</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11704.44938214422</v>
+        <v>11753.2221586195</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11704.44938214422</v>
+        <v>-11753.2221586195</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>7617.460107310435</v>
+        <v>7649.202282187114</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>7617.460107310435</v>
+        <v>7649.202282187114</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1928.964883006757</v>
+        <v>1897.222708130078</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>6108.669716191649</v>
+        <v>6134.124718208548</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>6108.669716191649</v>
+        <v>6134.124718208548</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-1490.013591191649</v>
+        <v>-1515.468593208548</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2879.452280499276</v>
+        <v>2891.451040788016</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2879.452280499276</v>
+        <v>2891.451040788016</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>1617.981264339988</v>
+        <v>1605.982504051247</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2569.467759785543</v>
+        <v>2580.174805680385</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2328.317160933341</v>
+        <v>2339.024206828183</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>376.8185053919846</v>
+        <v>366.1114594971424</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>901.4778648719804</v>
+        <v>905.2343490059453</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>901.4778648719804</v>
+        <v>905.2343490059453</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-776.0990288719804</v>
+        <v>-779.8555130059452</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>350.2199105453936</v>
+        <v>351.6792869634149</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>350.2199105453936</v>
+        <v>351.6792869634149</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-133849.8857005454</v>
+        <v>-133851.3450769634</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>8.452677767389693</v>
+        <v>8.487900318225398</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>8.452677767389693</v>
+        <v>8.487900318225398</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-8.45267778215125</v>
+        <v>-8.487900332986957</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2835,13 +2835,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.9973928114582055</v>
+        <v>1.001548975927208</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.9973928114582055</v>
+        <v>1.001548975927208</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>13.13169342594843</v>
+        <v>13.12753726147943</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.7447608007141757</v>
+        <v>0.7478642403442537</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.7447608007141757</v>
+        <v>0.7478642403442537</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.7447608007141757</v>
+        <v>-0.7478642403442537</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.2601570282401615</v>
+        <v>0.2612411100429492</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.2601570282401615</v>
+        <v>0.2612411100429492</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.07122301888687843</v>
+        <v>0.07013893708409073</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.2446595278613099</v>
+        <v>0.2456790311352642</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.2446595278613099</v>
+        <v>0.2456790311352642</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.2446595278613099</v>
+        <v>-0.2456790311352642</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.05746860044447624</v>
+        <v>0.05770807375178978</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.05746860044447624</v>
+        <v>0.05770807375178978</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-0.05746274274480073</v>
+        <v>-0.05770221605211427</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0001509998137076369</v>
+        <v>0.0001516290342648216</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0001509998137076369</v>
+        <v>0.0001516290342648216</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>7.200018629236305e-05</v>
+        <v>7.137096573517839e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.659791211480575e-05</v>
+        <v>1.666707609092297e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.659791211480575e-05</v>
+        <v>1.666707609092297e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>2.40208788519425e-06</v>
+        <v>2.332923909077027e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.506109455865725e-05</v>
+        <v>1.512385457191368e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.506109455865725e-05</v>
+        <v>1.512385457191368e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.195464243257225e-05</v>
+        <v>-1.201740244582868e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>4.449195344825439e-06</v>
+        <v>4.467735269512465e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>4.449195344825439e-06</v>
+        <v>4.467735269512465e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-4.491953448254389e-07</v>
+        <v>-4.677352695124644e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3.253328947489928e-06</v>
+        <v>3.26688566257971e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>3.253328947489928e-06</v>
+        <v>3.26688566257971e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-3.253328947489928e-06</v>
+        <v>-3.26688566257971e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.364554860081935e-06</v>
+        <v>1.370240999344545e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.364554860081935e-06</v>
+        <v>1.370240999344545e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-5.561006043869346e-07</v>
+        <v>-5.617867436495447e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>1.964788691446149e-07</v>
+        <v>1.972976022309851e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1.964788691446149e-07</v>
+        <v>1.972976022309851e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.964788691446149e-07</v>
+        <v>-1.972976022309851e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.03696666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03688895040288687</v>
+        <v>0.03738478373622021</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03914088815949029</v>
+        <v>0.03930680936986507</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-11.45325778732615</v>
+        <v>-9.79404568357833</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>270879.1830035028</v>
+        <v>231581.7482478888</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9430564.941863894</v>
+        <v>9469862.376619508</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>270879.1830035028</v>
+        <v>231581.7482478888</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2977531.418973944</v>
+        <v>3016828.853729559</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9264231.53101651</v>
+        <v>9303528.965772124</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11700495.65151448</v>
+        <v>11739793.0862701</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9251643.968801251</v>
+        <v>9290941.403556865</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>3</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>293920.6468481718</v>
+        <v>295307.5686209331</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>374578.727875959</v>
+        <v>375965.6496487203</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>3</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>303013.5166095516</v>
+        <v>304400.4383823129</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>382071.5092839777</v>
+        <v>383458.4310567391</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>303846.6151537827</v>
+        <v>305464.6225049944</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>382353.5908336217</v>
+        <v>383971.5981848335</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>3</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>303555.7943579851</v>
+        <v>305173.8017091968</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>382870.6039957182</v>
+        <v>384488.61134693</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>3</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>304323.1925158073</v>
+        <v>305941.1998670191</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>383831.3648336361</v>
+        <v>385449.3721848478</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>3</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03762656294576947</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>308166.9803164455</v>
+        <v>310016.0538120978</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>383150.5056369744</v>
+        <v>384999.5791326266</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>306834.2616068879</v>
+        <v>308452.2689580997</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>384484.6224839138</v>
+        <v>386102.6298351255</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>3</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>307368.671438415</v>
+        <v>308524.4881951632</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>381775.6535496546</v>
+        <v>382931.4703064028</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03727656294576948</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>307129.371464794</v>
+        <v>308054.0637648579</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>381733.1447470395</v>
+        <v>382657.8370471034</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>3</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>307119.447068205</v>
+        <v>308275.2638249533</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>381000.1725228651</v>
+        <v>382155.9892796133</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>3</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>306386.877799583</v>
+        <v>307542.6945563313</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>380101.5050144822</v>
+        <v>381257.3217712304</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>3</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>314300.6602107302</v>
+        <v>315456.4769674785</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>387863.3849071475</v>
+        <v>389019.2016638957</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>3</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>294465.9515593068</v>
+        <v>296083.9589105186</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>367652.0134779223</v>
+        <v>369270.020829134</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>3</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>294830.0953458483</v>
+        <v>296448.10269706</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>367769.9874829751</v>
+        <v>369387.9948341869</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>3</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>296067.7199726206</v>
+        <v>297685.7273238324</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>369052.5068981854</v>
+        <v>370670.5142493972</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>295617.1317991815</v>
+        <v>297004.0535719429</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>368789.9779535549</v>
+        <v>370176.8997263162</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>3</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>295436.3574166922</v>
+        <v>296823.2791894535</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>368422.8260497338</v>
+        <v>369809.7478224952</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>3</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>298237.619004383</v>
+        <v>299624.5407771443</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>371289.9860909391</v>
+        <v>372676.9078637005</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03745156294576948</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>303939.9251266263</v>
+        <v>305326.8468993877</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>376515.4807739933</v>
+        <v>377902.4025467546</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>3</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0371</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03753906294576947</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>316446.0199044726</v>
+        <v>318064.0272556844</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>391876.2700847145</v>
+        <v>393494.2774359263</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>3</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03692656294576947</v>
+        <v>0.03736406294576947</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>332245.705476784</v>
+        <v>333401.5222335323</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>411193.871491632</v>
+        <v>412349.6882483802</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>3</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>334368.4188951939</v>
+        <v>335524.3750066921</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>414590.4869628215</v>
+        <v>415746.4430743197</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>3</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>342969.0305834343</v>
+        <v>344124.9866949325</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>417067.874719601</v>
+        <v>418223.8308310992</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>3</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>343446.9610639547</v>
+        <v>344602.9171754529</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>418043.8151805623</v>
+        <v>419199.7712920604</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>3</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>341294.6051023981</v>
+        <v>342450.5612138964</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>415161.1900272233</v>
+        <v>416317.1461387215</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>3</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03723868780282747</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>345113.7443960527</v>
+        <v>346269.700507551</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>420529.2631189993</v>
+        <v>421685.2192304975</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>3</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>339352.8474959402</v>
+        <v>340277.6512890411</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>413159.5105374671</v>
+        <v>414084.3143305681</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>3</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>350421.6342753276</v>
+        <v>351346.4380684285</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>426718.2485197183</v>
+        <v>427643.0523128192</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>3</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>288380.0837877369</v>
+        <v>289304.8875808378</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>367095.8463379316</v>
+        <v>368020.6501310325</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>3</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03680118780282747</v>
+        <v>0.03715118780282747</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>351965.0552675817</v>
+        <v>352889.8590606826</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>429751.7101215186</v>
+        <v>430676.5139146195</v>
       </c>
     </row>
     <row r="37">
@@ -6865,10 +6865,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9430564.941863894</v>
+        <v>9469862.376619508</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11700495.65151448</v>
+        <v>11739793.0862701</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1506065.38</v>
+        <v>1504172.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>12180216.63759718</v>
+        <v>12178324.22759718</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
+++ b/settlements/spark/2026-04/spark_settlement_april_2026.xlsx
@@ -4677,7 +4677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -4896,7 +4896,7 @@
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+          <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
